--- a/outputs/rules_engine_system_test_uat_plan.xlsx
+++ b/outputs/rules_engine_system_test_uat_plan.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="Rc5ec6b288c98487e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Tests" sheetId="2" r:id="R55269c82145b4c70"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UAT Tests" sheetId="3" r:id="Rc6b44332b86c4463"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Results Log" sheetId="4" r:id="R7d793bdb4dcd4afa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defect Log" sheetId="5" r:id="Rd7764656941a4bbf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sign-Off" sheetId="6" r:id="Rd2b4fb8cc1c94a5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="Rffb3757f70054642"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Tests" sheetId="2" r:id="Rdd1cf577a3b946d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UAT Tests" sheetId="3" r:id="Rcc7bd45c47e6426b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Results Log" sheetId="4" r:id="R1a06cb29c1bd4740"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defect Log" sheetId="5" r:id="R9e4d30d2241246c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sign-Off" sheetId="6" r:id="R4316368af395443c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -21,9 +21,6 @@
     <x:t xml:space="preserve">Purpose</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Provide a structured system test and UAT plan for validating the rules engine before deployment. The workbook supports technical execution, business acceptance, evidence capture, defect tracking, and release sign-off.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Metric</x:t>
   </x:si>
   <x:si>
@@ -39,18 +36,12 @@
     <x:t xml:space="preserve">Out of Scope</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Security penetration testing, production-scale load testing, downstream BI model certification, and domain-specific business rule design approval unless explicitly added by the project team.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">UAT Tests Planned</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Primary Release Risk</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Incorrect ruleset publication, function metadata setup, or runtime evaluation could assign wrong rule outcomes to business records or make production jobs load the wrong ruleset version.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Results Executed</x:t>
   </x:si>
   <x:si>
@@ -1056,9 +1047,6 @@
     <x:t xml:space="preserve">D-100</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">UAT and Release Sign-Off</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Role</x:t>
   </x:si>
   <x:si>
@@ -1075,27 +1063,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Signature or Approval Reference</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Business Owner</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Engineering Lead</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Data Engineering Owner</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Rules Authoring Owner</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QA / UAT Coordinator</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Release Manager</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Operations Support Owner</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1578,7 +1545,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="SystemTestPlan" displayName="SystemTestPlan" ref="A3:I70" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="SystemTestPlan" displayName="SystemTestPlan" ref="A3:I65" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Test ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -1595,7 +1562,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="UATTestPlan" displayName="UATTestPlan" ref="A3:I27" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="UATTestPlan" displayName="UATTestPlan" ref="A3:I22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Test ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -1652,8 +1619,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="SignOff" displayName="SignOff" ref="A3:F10">
-  <x:autoFilter ref="A3:F10"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="26" name="SignOff" displayName="SignOff" ref="A3:F7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A3:F7"/>
   <x:tableColumns count="6">
     <x:tableColumn id="1" name="Role"/>
     <x:tableColumn id="2" name="Name"/>
@@ -1839,54 +1806,53 @@
       <x:c r="A3" s="1" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B3" s="2" t="s">
+      <x:c r="B3" s="2" t="str">
+        <x:v>Provide a structured system and user-acceptance test plan for the current rules-engine contract, with evidence capture and defect tracking.</x:v>
+      </x:c>
+      <x:c r="D3" s="3" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D3" s="3" t="s">
+      <x:c r="E3" s="3" t="s">
         <x:v>3</x:v>
-      </x:c>
-      <x:c r="E3" s="3" t="s">
-        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="42" customHeight="1">
       <x:c r="A4" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B4" s="2" t="str">
+        <x:v>Disposable metadata storage, function registration, strict YAML compilation, semantic and Spark validation, publish/lifecycle behavior, typed row evaluation, assignment chaining, compact/full-audit output, date functions, semantic diffs, coverage diagnostics, and business-facing UAT workflows.</x:v>
+      </x:c>
+      <x:c r="D4" s="4" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B4" s="2" t="str">
-        <x:v>Installed-wheel provenance, disposable schema/table setup, standard/custom function registration, YAML compilation, semantic and Spark validation, expected-case publish gates, lifecycle, typed Spark execution, audit levels and identity, date functions, semantic diffs, coverage diagnostics, and business-facing UAT workflows.</x:v>
-      </x:c>
-      <x:c r="D4" s="4" t="s">
-        <x:v>6</x:v>
-      </x:c>
       <x:c r="E4" s="5" t="n">
-        <x:v>67</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="42" customHeight="1">
       <x:c r="A5" s="1" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B5" s="2" t="str">
+        <x:v>Security penetration testing, production-scale load testing, downstream BI model certification, and domain-specific business rule approval unless explicitly added by the project team.</x:v>
+      </x:c>
+      <x:c r="D5" s="4" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B5" s="2" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D5" s="4" t="s">
-        <x:v>9</x:v>
-      </x:c>
       <x:c r="E5" s="5" t="n">
-        <x:f>COUNTA('UAT Tests'!A4:A250)</x:f>
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="42" customHeight="1">
       <x:c r="A6" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B6" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B6" s="2" t="str">
+        <x:v>Incorrect publication or runtime evaluation could assign wrong outcomes to business records or load the wrong ruleset version.</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E6" s="5" t="n">
         <x:f>COUNTIFS('Results Log'!G4:G203,"&lt;&gt;Not Run",'Results Log'!G4:G203,"&lt;&gt;")</x:f>
@@ -1895,13 +1861,13 @@
     </x:row>
     <x:row r="7" ht="42" customHeight="1">
       <x:c r="A7" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B7" s="2" t="str">
-        <x:v>Versioned wheel deployed to the test cluster, repository fixtures synchronized, a catalog.schema whose schema name contains test/scratch/tmp, and permission to create and mutate metadata tables in that disposable target.</x:v>
+        <x:v>The current package and repository fixtures are available on a test cluster, and the target catalog.schema visibly identifies a disposable test/scratch/tmp location.</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E7" s="5" t="n">
         <x:f>COUNTIF('Results Log'!G4:G203,"Pass")</x:f>
@@ -1910,13 +1876,13 @@
     </x:row>
     <x:row r="8" ht="42" customHeight="1">
       <x:c r="A8" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B8" s="2" t="str">
-        <x:v>All Critical and High system tests pass, pytest passes against the installed wheel, UAT sign-off is recorded, and every open defect has an owner-approved disposition.</x:v>
+        <x:v>All Critical and High system tests pass, the current pytest suite passes, UAT approval is recorded, and every open defect has an owner-approved disposition.</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E8" s="5" t="n">
         <x:f>COUNTIFS('Defect Log'!H4:H103,"&lt;&gt;Closed",'Defect Log'!H4:H103,"&lt;&gt;")</x:f>
@@ -1925,18 +1891,18 @@
     </x:row>
     <x:row r="9" ht="42" customHeight="1">
       <x:c r="A9" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B9" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="42" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1962,7 +1928,7 @@
   <x:sheetData>
     <x:row r="1" ht="18" customHeight="1">
       <x:c r="A1" s="15" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B1" s="16"/>
       <x:c r="C1" s="16"/>
@@ -2007,7 +1973,7 @@
         <x:v>ST-001</x:v>
       </x:c>
       <x:c r="B4" s="28" t="str">
-        <x:v>Deployment setup</x:v>
+        <x:v>Metadata storage</x:v>
       </x:c>
       <x:c r="C4" s="28" t="str">
         <x:v>Critical</x:v>
@@ -2016,17 +1982,17 @@
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E4" s="29" t="str">
-        <x:v>Setup notebook creates the target schema before table creation</x:v>
+        <x:v>Test harness creates the target schema before table creation</x:v>
       </x:c>
       <x:c r="F4" s="29" t="str">
-        <x:v>Run the setup notebook against a clean test catalog/schema. Use CREATE SCHEMA IF NOT EXISTS before service.create_tables.</x:v>
+        <x:v>Run the system notebook against a clean disposable catalog/schema. Use CREATE SCHEMA IF NOT EXISTS before service.create_tables.</x:v>
       </x:c>
       <x:c r="G4" s="29" t="str">
         <x:v>The schema exists and the notebook proceeds to table creation without manual pre-work.</x:v>
       </x:c>
       <x:c r="H4" s="29"/>
       <x:c r="I4" s="29" t="str">
-        <x:v>Notebook run URL and SHOW SCHEMAS/SHOW DATABASES output.</x:v>
+        <x:v>Notebook assertions and relevant metadata-table query output.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="48" hidden="0" customHeight="1">
@@ -2034,7 +2000,7 @@
         <x:v>ST-002</x:v>
       </x:c>
       <x:c r="B5" s="28" t="str">
-        <x:v>Deployment setup</x:v>
+        <x:v>Metadata storage</x:v>
       </x:c>
       <x:c r="C5" s="28" t="str">
         <x:v>Critical</x:v>
@@ -2053,7 +2019,7 @@
       </x:c>
       <x:c r="H5" s="29"/>
       <x:c r="I5" s="29" t="str">
-        <x:v>SHOW TABLES output and notebook rerun evidence.</x:v>
+        <x:v>Notebook assertions and relevant metadata-table query output.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="60" hidden="0" customHeight="1">
@@ -2061,7 +2027,7 @@
         <x:v>ST-003</x:v>
       </x:c>
       <x:c r="B6" s="28" t="str">
-        <x:v>Deployment setup</x:v>
+        <x:v>Metadata storage</x:v>
       </x:c>
       <x:c r="C6" s="28" t="str">
         <x:v>High</x:v>
@@ -2080,7 +2046,7 @@
       </x:c>
       <x:c r="H6" s="29"/>
       <x:c r="I6" s="29" t="str">
-        <x:v>Notebook output showing service.table_names and SHOW TABLES output.</x:v>
+        <x:v>Notebook assertions and relevant metadata-table query output.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="84" hidden="0" customHeight="1">
@@ -2088,7 +2054,7 @@
         <x:v>ST-004</x:v>
       </x:c>
       <x:c r="B7" s="28" t="str">
-        <x:v>Deployment setup</x:v>
+        <x:v>Metadata storage</x:v>
       </x:c>
       <x:c r="C7" s="28" t="str">
         <x:v>Critical</x:v>
@@ -2100,14 +2066,14 @@
         <x:v>Metadata table DDL preserves NOT NULL columns</x:v>
       </x:c>
       <x:c r="F7" s="29" t="str">
-        <x:v>After table creation, DESCRIBE TABLE EXTENDED or catalog inspection is run for both metadata tables.</x:v>
+        <x:v>After table creation, inspect both metadata tables.</x:v>
       </x:c>
       <x:c r="G7" s="29" t="str">
         <x:v>Required columns such as ruleset_id, ruleset_name, version, status, effective_start_date, effective_end_date, payload_json, content_hash, rule_count, function_name, implementation_reference, and active_flag are marked NOT NULL where expected.</x:v>
       </x:c>
       <x:c r="H7" s="29"/>
       <x:c r="I7" s="29" t="str">
-        <x:v>DESCRIBE TABLE output for both tables.</x:v>
+        <x:v>Notebook assertions and relevant metadata-table query output.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="48" hidden="0" customHeight="1">
@@ -2115,7 +2081,7 @@
         <x:v>ST-005</x:v>
       </x:c>
       <x:c r="B8" s="28" t="str">
-        <x:v>Deployment setup</x:v>
+        <x:v>Metadata storage</x:v>
       </x:c>
       <x:c r="C8" s="28" t="str">
         <x:v>High</x:v>
@@ -2127,14 +2093,14 @@
         <x:v>Overwrite mode is restricted to disposable environments</x:v>
       </x:c>
       <x:c r="F8" s="29" t="str">
-        <x:v>Run setup in a disposable/dev schema using mode='overwrite'. Verify project guidance blocks or avoids overwrite for production-like schemas.</x:v>
+        <x:v>Run with mode='overwrite' only after explicitly approving a disposable schema.</x:v>
       </x:c>
       <x:c r="G8" s="29" t="str">
-        <x:v>Overwrite recreates tables only in disposable schemas. Production setup uses mode='ignore' or 'error'.</x:v>
+        <x:v>Overwrite recreates tables only when a disposable schema is explicitly approved.</x:v>
       </x:c>
       <x:c r="H8" s="29"/>
       <x:c r="I8" s="29" t="str">
-        <x:v>Notebook parameters and execution log.</x:v>
+        <x:v>Notebook assertions and relevant metadata-table query output.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="48" hidden="0" customHeight="1">
@@ -2161,7 +2127,7 @@
       </x:c>
       <x:c r="H9" s="29"/>
       <x:c r="I9" s="29" t="str">
-        <x:v>Query output ordered by function_name.</x:v>
+        <x:v>Notebook assertions and relevant metadata-table query output.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="48" hidden="0" customHeight="1">
@@ -2188,7 +2154,7 @@
       </x:c>
       <x:c r="H10" s="29"/>
       <x:c r="I10" s="29" t="str">
-        <x:v>Before/after function_registry row counts and sample row values.</x:v>
+        <x:v>Notebook assertions and relevant metadata-table query output.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="48" hidden="0" customHeight="1">
@@ -2215,7 +2181,7 @@
       </x:c>
       <x:c r="H11" s="29"/>
       <x:c r="I11" s="29" t="str">
-        <x:v>MERGE/job output and post-refresh query.</x:v>
+        <x:v>Notebook assertions and relevant metadata-table query output.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="60" hidden="0" customHeight="1">
@@ -2242,7 +2208,7 @@
       </x:c>
       <x:c r="H12" s="29"/>
       <x:c r="I12" s="29" t="str">
-        <x:v>Notebook output showing successful validation/evaluation using a standard function.</x:v>
+        <x:v>Notebook assertions and relevant metadata-table query output.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="36" hidden="0" customHeight="1">
@@ -2269,7 +2235,7 @@
       </x:c>
       <x:c r="H13" s="29"/>
       <x:c r="I13" s="29" t="str">
-        <x:v>function_registry query for standard and custom rows.</x:v>
+        <x:v>Notebook assertions and relevant metadata-table query output.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="48" hidden="0" customHeight="1">
@@ -2296,7 +2262,7 @@
       </x:c>
       <x:c r="H14" s="29"/>
       <x:c r="I14" s="29" t="str">
-        <x:v>Notebook output showing compiled metadata and rule count.</x:v>
+        <x:v>Notebook assertions and validation or exception output.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="24" hidden="0" customHeight="1">
@@ -2323,7 +2289,7 @@
       </x:c>
       <x:c r="H15" s="29"/>
       <x:c r="I15" s="29" t="str">
-        <x:v>Notebook output and compiled ruleset summary.</x:v>
+        <x:v>Notebook assertions and validation or exception output.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="36" hidden="0" customHeight="1">
@@ -2334,23 +2300,23 @@
         <x:v>YAML compilation</x:v>
       </x:c>
       <x:c r="C16" s="28" t="str">
-        <x:v>High</x:v>
+        <x:v>Critical</x:v>
       </x:c>
       <x:c r="D16" s="28" t="str">
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E16" s="29" t="str">
-        <x:v>Unsupported legacy aliases are rejected clearly</x:v>
+        <x:v>Required top-level ruleset metadata is enforced</x:v>
       </x:c>
       <x:c r="F16" s="29" t="str">
-        <x:v>Compile YAML using unsupported keys such as assignments or operand value.</x:v>
+        <x:v>Compile YAML missing ruleset_id, ruleset_name, version, or rules list.</x:v>
       </x:c>
       <x:c r="G16" s="29" t="str">
-        <x:v>Compilation fails with a clear message identifying the unsupported key and canonical replacement.</x:v>
+        <x:v>Compilation fails before validation or persistence. Error identifies the missing or malformed field.</x:v>
       </x:c>
       <x:c r="H16" s="29"/>
       <x:c r="I16" s="29" t="str">
-        <x:v>Expected exception output.</x:v>
+        <x:v>Notebook assertions and validation or exception output.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="36" hidden="0" customHeight="1">
@@ -2361,23 +2327,23 @@
         <x:v>YAML compilation</x:v>
       </x:c>
       <x:c r="C17" s="28" t="str">
-        <x:v>Critical</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="D17" s="28" t="str">
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E17" s="29" t="str">
-        <x:v>Required top-level ruleset metadata is enforced</x:v>
+        <x:v>Condition group logical operator shape is enforced</x:v>
       </x:c>
       <x:c r="F17" s="29" t="str">
-        <x:v>Compile YAML missing ruleset_id, ruleset_name, version, or rules list.</x:v>
+        <x:v>Compile YAML with missing or multiple logical operator keys in a condition group.</x:v>
       </x:c>
       <x:c r="G17" s="29" t="str">
-        <x:v>Compilation fails before validation or persistence. Error identifies the missing or malformed field.</x:v>
+        <x:v>Compilation fails and identifies that exactly one logical operator is required.</x:v>
       </x:c>
       <x:c r="H17" s="29"/>
       <x:c r="I17" s="29" t="str">
-        <x:v>Expected exception output.</x:v>
+        <x:v>Notebook assertions and validation or exception output.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="24" hidden="0" customHeight="1">
@@ -2385,26 +2351,26 @@
         <x:v>ST-015</x:v>
       </x:c>
       <x:c r="B18" s="28" t="str">
-        <x:v>YAML compilation</x:v>
+        <x:v>Semantic validation</x:v>
       </x:c>
       <x:c r="C18" s="28" t="str">
-        <x:v>High</x:v>
+        <x:v>Critical</x:v>
       </x:c>
       <x:c r="D18" s="28" t="str">
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E18" s="29" t="str">
-        <x:v>Condition group logical operator shape is enforced</x:v>
+        <x:v>Valid simple row-level rule passes validation</x:v>
       </x:c>
       <x:c r="F18" s="29" t="str">
-        <x:v>Compile YAML with missing or multiple logical operator keys in a condition group.</x:v>
+        <x:v>Compile a simple ruleset using field/literal comparison and assignment, then run service.validator.validate.</x:v>
       </x:c>
       <x:c r="G18" s="29" t="str">
-        <x:v>Compilation fails and identifies that exactly one logical operator is required.</x:v>
+        <x:v>Validation passes with no error-severity issues.</x:v>
       </x:c>
       <x:c r="H18" s="29"/>
       <x:c r="I18" s="29" t="str">
-        <x:v>Expected exception output.</x:v>
+        <x:v>Notebook assertions and validation or exception output.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="36" hidden="0" customHeight="1">
@@ -2421,17 +2387,17 @@
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E19" s="29" t="str">
-        <x:v>Valid simple row-level rule passes validation</x:v>
+        <x:v>Owner and owner_department are required before publish</x:v>
       </x:c>
       <x:c r="F19" s="29" t="str">
-        <x:v>Compile a simple ruleset using field/literal comparison and assignment, then run service.validator.validate.</x:v>
+        <x:v>Validate a ruleset missing owner or owner_department.</x:v>
       </x:c>
       <x:c r="G19" s="29" t="str">
-        <x:v>Validation passes with no error-severity issues.</x:v>
+        <x:v>Validation returns error-severity issues and publish is blocked.</x:v>
       </x:c>
       <x:c r="H19" s="29"/>
       <x:c r="I19" s="29" t="str">
-        <x:v>validation.to_text output.</x:v>
+        <x:v>Notebook assertions and validation or exception output.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="24" hidden="0" customHeight="1">
@@ -2442,23 +2408,23 @@
         <x:v>Semantic validation</x:v>
       </x:c>
       <x:c r="C20" s="28" t="str">
-        <x:v>Critical</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="D20" s="28" t="str">
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E20" s="29" t="str">
-        <x:v>Owner and owner_department are required before publish</x:v>
+        <x:v>Duplicate condition_id values are rejected</x:v>
       </x:c>
       <x:c r="F20" s="29" t="str">
-        <x:v>Validate a ruleset missing owner or owner_department.</x:v>
+        <x:v>Validate a ruleset with duplicate condition IDs across rules or nested groups.</x:v>
       </x:c>
       <x:c r="G20" s="29" t="str">
-        <x:v>Validation returns error-severity issues and publish is blocked.</x:v>
+        <x:v>Validation returns a duplicate condition ID error.</x:v>
       </x:c>
       <x:c r="H20" s="29"/>
       <x:c r="I20" s="29" t="str">
-        <x:v>Validation output and failed publish evidence.</x:v>
+        <x:v>Notebook assertions and validation or exception output.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="24" hidden="0" customHeight="1">
@@ -2475,17 +2441,17 @@
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E21" s="29" t="str">
-        <x:v>Duplicate condition_id values are rejected</x:v>
+        <x:v>Duplicate condition_group_id values are rejected</x:v>
       </x:c>
       <x:c r="F21" s="29" t="str">
-        <x:v>Validate a ruleset with duplicate condition IDs across rules or nested groups.</x:v>
+        <x:v>Validate a ruleset with duplicate group IDs.</x:v>
       </x:c>
       <x:c r="G21" s="29" t="str">
-        <x:v>Validation returns a duplicate condition ID error.</x:v>
+        <x:v>Validation returns a duplicate condition group ID error.</x:v>
       </x:c>
       <x:c r="H21" s="29"/>
       <x:c r="I21" s="29" t="str">
-        <x:v>Validation output.</x:v>
+        <x:v>Notebook assertions and validation or exception output.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="24" hidden="0" customHeight="1">
@@ -2502,17 +2468,17 @@
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E22" s="29" t="str">
-        <x:v>Duplicate condition_group_id values are rejected</x:v>
+        <x:v>Custom-function argument contracts are enforced</x:v>
       </x:c>
       <x:c r="F22" s="29" t="str">
-        <x:v>Validate a ruleset with duplicate group IDs.</x:v>
+        <x:v>Validate a rule with missing, extra, or misspelled function arguments.</x:v>
       </x:c>
       <x:c r="G22" s="29" t="str">
-        <x:v>Validation returns a duplicate condition group ID error.</x:v>
+        <x:v>Validation reports the registered contract mismatch.</x:v>
       </x:c>
       <x:c r="H22" s="29"/>
       <x:c r="I22" s="29" t="str">
-        <x:v>Validation output.</x:v>
+        <x:v>Notebook assertions and validation or exception output.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="36" hidden="0" customHeight="1">
@@ -2520,26 +2486,26 @@
         <x:v>ST-020</x:v>
       </x:c>
       <x:c r="B23" s="28" t="str">
-        <x:v>YAML compilation</x:v>
+        <x:v>Semantic validation</x:v>
       </x:c>
       <x:c r="C23" s="28" t="str">
-        <x:v>Critical</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="D23" s="28" t="str">
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E23" s="29" t="str">
-        <x:v>Aggregate operands are rejected</x:v>
+        <x:v>Operator arity and literal collection requirements are enforced</x:v>
       </x:c>
       <x:c r="F23" s="29" t="str">
-        <x:v>Compile YAML containing an `aggregate` operand.</x:v>
+        <x:v>Validate operators such as is_null, between, in, and not_in with invalid right operands.</x:v>
       </x:c>
       <x:c r="G23" s="29" t="str">
-        <x:v>Compilation fails with guidance to precompute aggregate values upstream and reference them as fields.</x:v>
+        <x:v>Validation identifies missing, extra, or malformed operands.</x:v>
       </x:c>
       <x:c r="H23" s="29"/>
       <x:c r="I23" s="29" t="str">
-        <x:v>Validation output.</x:v>
+        <x:v>Notebook assertions and validation or exception output.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="24" hidden="0" customHeight="1">
@@ -2547,26 +2513,26 @@
         <x:v>ST-021</x:v>
       </x:c>
       <x:c r="B24" s="28" t="str">
-        <x:v>YAML compilation</x:v>
+        <x:v>Semantic validation</x:v>
       </x:c>
       <x:c r="C24" s="28" t="str">
-        <x:v>High</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="D24" s="28" t="str">
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E24" s="29" t="str">
-        <x:v>Precomputed aggregate facts compile as fields</x:v>
+        <x:v>Operand null defaults must be concrete values</x:v>
       </x:c>
       <x:c r="F24" s="29" t="str">
-        <x:v>Compile a ruleset that references a column such as `account_amount_sum`.</x:v>
+        <x:v>Compile an operand with `default_if_null: null`.</x:v>
       </x:c>
       <x:c r="G24" s="29" t="str">
-        <x:v>The field operand compiles and evaluates like any other row-level field.</x:v>
+        <x:v>Compilation rejects the null fallback and explains that the option should be omitted when no substitution is wanted.</x:v>
       </x:c>
       <x:c r="H24" s="29"/>
       <x:c r="I24" s="29" t="str">
-        <x:v>Validation output.</x:v>
+        <x:v>Notebook assertions and validation or exception output.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="24" hidden="0" customHeight="1">
@@ -2574,26 +2540,26 @@
         <x:v>ST-022</x:v>
       </x:c>
       <x:c r="B25" s="28" t="str">
-        <x:v>Semantic validation</x:v>
+        <x:v>Spark compatibility</x:v>
       </x:c>
       <x:c r="C25" s="28" t="str">
-        <x:v>High</x:v>
+        <x:v>Critical</x:v>
       </x:c>
       <x:c r="D25" s="28" t="str">
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E25" s="29" t="str">
-        <x:v>Custom-function argument contracts are enforced</x:v>
+        <x:v>Spark validator accepts supported rulesets</x:v>
       </x:c>
       <x:c r="F25" s="29" t="str">
-        <x:v>Validate a rule with missing, extra, or misspelled function arguments.</x:v>
+        <x:v>Run SparkRulesetCompatibilityValidator through service.validator on representative supported rulesets.</x:v>
       </x:c>
       <x:c r="G25" s="29" t="str">
-        <x:v>Validation reports the registered contract mismatch.</x:v>
+        <x:v>Validation passes and no Spark-specific unsupported-operation issues are present.</x:v>
       </x:c>
       <x:c r="H25" s="29"/>
       <x:c r="I25" s="29" t="str">
-        <x:v>Validation output.</x:v>
+        <x:v>Notebook assertions and validation or exception output.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="24" hidden="0" customHeight="1">
@@ -2601,7 +2567,7 @@
         <x:v>ST-023</x:v>
       </x:c>
       <x:c r="B26" s="28" t="str">
-        <x:v>Semantic validation</x:v>
+        <x:v>Spark compatibility</x:v>
       </x:c>
       <x:c r="C26" s="28" t="str">
         <x:v>High</x:v>
@@ -2610,17 +2576,17 @@
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E26" s="29" t="str">
-        <x:v>Operator arity and literal collection requirements are enforced</x:v>
+        <x:v>Spark validator follows the supported row-level contract</x:v>
       </x:c>
       <x:c r="F26" s="29" t="str">
-        <x:v>Validate operators such as is_null, between, in, and not_in with invalid right operands.</x:v>
+        <x:v>Validate rulesets with fields, literals, and registered custom functions.</x:v>
       </x:c>
       <x:c r="G26" s="29" t="str">
-        <x:v>Validation identifies missing, extra, or malformed operands.</x:v>
+        <x:v>Validation passes for supported row-level rules and rejects base semantic errors.</x:v>
       </x:c>
       <x:c r="H26" s="29"/>
       <x:c r="I26" s="29" t="str">
-        <x:v>Validation output.</x:v>
+        <x:v>Notebook assertions and validation or exception output.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="24" hidden="0" customHeight="1">
@@ -2628,26 +2594,26 @@
         <x:v>ST-024</x:v>
       </x:c>
       <x:c r="B27" s="28" t="str">
-        <x:v>Semantic validation</x:v>
+        <x:v>Publishing</x:v>
       </x:c>
       <x:c r="C27" s="28" t="str">
-        <x:v>Medium</x:v>
+        <x:v>Critical</x:v>
       </x:c>
       <x:c r="D27" s="28" t="str">
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E27" s="29" t="str">
-        <x:v>Null handling modes require default values when configured</x:v>
+        <x:v>Publish YAML path compiles, normalizes, validates, and writes metadata</x:v>
       </x:c>
       <x:c r="F27" s="29" t="str">
-        <x:v>Validate null_result_mode=default without null_default_value.</x:v>
+        <x:v>Call service.publish_yaml_path on a valid YAML artifact.</x:v>
       </x:c>
       <x:c r="G27" s="29" t="str">
-        <x:v>Validation returns a default-value requirement error.</x:v>
+        <x:v>One published ruleset_versions row is written with status published, content_hash, payload_json, counts, owner, published_by, and published_at.</x:v>
       </x:c>
       <x:c r="H27" s="29"/>
       <x:c r="I27" s="29" t="str">
-        <x:v>Validation output.</x:v>
+        <x:v>Notebook assertions and relevant metadata-table query output.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="36" hidden="0" customHeight="1">
@@ -2655,7 +2621,7 @@
         <x:v>ST-025</x:v>
       </x:c>
       <x:c r="B28" s="28" t="str">
-        <x:v>Spark compatibility</x:v>
+        <x:v>Publishing</x:v>
       </x:c>
       <x:c r="C28" s="28" t="str">
         <x:v>Critical</x:v>
@@ -2664,17 +2630,17 @@
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E28" s="29" t="str">
-        <x:v>Spark validator accepts supported rulesets</x:v>
+        <x:v>Direct publish of a compiled ruleset works</x:v>
       </x:c>
       <x:c r="F28" s="29" t="str">
-        <x:v>Run SparkRulesetCompatibilityValidator through service.validator on representative supported rulesets.</x:v>
+        <x:v>Compile YAML, validate it, then call service.publish(ruleset, published_by=...).</x:v>
       </x:c>
       <x:c r="G28" s="29" t="str">
-        <x:v>Validation passes and no Spark-specific unsupported-operation issues are present.</x:v>
+        <x:v>The compiled ruleset is persisted and loadable by name/version.</x:v>
       </x:c>
       <x:c r="H28" s="29"/>
       <x:c r="I28" s="29" t="str">
-        <x:v>Validation output.</x:v>
+        <x:v>Notebook assertions and relevant metadata-table query output.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="24" hidden="0" customHeight="1">
@@ -2682,26 +2648,26 @@
         <x:v>ST-026</x:v>
       </x:c>
       <x:c r="B29" s="28" t="str">
-        <x:v>Spark compatibility</x:v>
+        <x:v>Publishing</x:v>
       </x:c>
       <x:c r="C29" s="28" t="str">
-        <x:v>High</x:v>
+        <x:v>Critical</x:v>
       </x:c>
       <x:c r="D29" s="28" t="str">
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E29" s="29" t="str">
-        <x:v>Spark validator follows the supported row-level contract</x:v>
+        <x:v>Publish rejects non-published lifecycle status</x:v>
       </x:c>
       <x:c r="F29" s="29" t="str">
-        <x:v>Validate rulesets with fields, literals, and registered custom functions.</x:v>
+        <x:v>Attempt to publish a compiled ruleset with status retired.</x:v>
       </x:c>
       <x:c r="G29" s="29" t="str">
-        <x:v>Validation passes for supported row-level rules and rejects base semantic errors.</x:v>
+        <x:v>Publish fails before persistence with a clear status requirement message.</x:v>
       </x:c>
       <x:c r="H29" s="29"/>
       <x:c r="I29" s="29" t="str">
-        <x:v>Validation output.</x:v>
+        <x:v>Notebook assertions and relevant metadata-table query output.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="48" hidden="0" customHeight="1">
@@ -2718,17 +2684,17 @@
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E30" s="29" t="str">
-        <x:v>Publish YAML path compiles, normalizes, validates, and writes metadata</x:v>
+        <x:v>Duplicate ruleset_name and version cannot be published twice</x:v>
       </x:c>
       <x:c r="F30" s="29" t="str">
-        <x:v>Call service.publish_yaml_path on a valid YAML artifact.</x:v>
+        <x:v>Publish a ruleset, then attempt to publish another ruleset with the same ruleset_name and version.</x:v>
       </x:c>
       <x:c r="G30" s="29" t="str">
-        <x:v>One published ruleset_versions row is written with status published, content_hash, payload_json, counts, owner, published_by, and published_at.</x:v>
+        <x:v>Second publish fails and does not overwrite the original row.</x:v>
       </x:c>
       <x:c r="H30" s="29"/>
       <x:c r="I30" s="29" t="str">
-        <x:v>ruleset_versions query for the published row.</x:v>
+        <x:v>Notebook assertions and relevant metadata-table query output.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="24" hidden="0" customHeight="1">
@@ -2739,23 +2705,23 @@
         <x:v>Publishing</x:v>
       </x:c>
       <x:c r="C31" s="28" t="str">
-        <x:v>Critical</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="D31" s="28" t="str">
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E31" s="29" t="str">
-        <x:v>Direct publish of a compiled ruleset works</x:v>
+        <x:v>Multiple published versions for the same ruleset_name are allowed</x:v>
       </x:c>
       <x:c r="F31" s="29" t="str">
-        <x:v>Compile YAML, validate it, then call service.publish(ruleset, published_by=...).</x:v>
+        <x:v>Publish version 1 and version 2 for the same ruleset_name.</x:v>
       </x:c>
       <x:c r="G31" s="29" t="str">
-        <x:v>The compiled ruleset is persisted and loadable by name/version.</x:v>
+        <x:v>Both rows have status published. Neither publish requires retiring the other version.</x:v>
       </x:c>
       <x:c r="H31" s="29"/>
       <x:c r="I31" s="29" t="str">
-        <x:v>Notebook output and load_published confirmation.</x:v>
+        <x:v>Notebook assertions and relevant metadata-table query output.</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="24" hidden="0" customHeight="1">
@@ -2766,23 +2732,23 @@
         <x:v>Publishing</x:v>
       </x:c>
       <x:c r="C32" s="28" t="str">
-        <x:v>Critical</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="D32" s="28" t="str">
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E32" s="29" t="str">
-        <x:v>Publish rejects non-published lifecycle status</x:v>
+        <x:v>Loading by name without version is rejected when ambiguous</x:v>
       </x:c>
       <x:c r="F32" s="29" t="str">
-        <x:v>Attempt to publish a compiled ruleset with status retired.</x:v>
+        <x:v>With two published versions for the same ruleset_name, call service.load_published(ruleset_name) without version.</x:v>
       </x:c>
       <x:c r="G32" s="29" t="str">
-        <x:v>Publish fails before persistence with a clear status requirement message.</x:v>
+        <x:v>Repository raises an error asking the caller to specify version.</x:v>
       </x:c>
       <x:c r="H32" s="29"/>
       <x:c r="I32" s="29" t="str">
-        <x:v>Expected exception output and unchanged table row count.</x:v>
+        <x:v>Notebook assertions and relevant metadata-table query output.</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="36" hidden="0" customHeight="1">
@@ -2799,17 +2765,17 @@
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E33" s="29" t="str">
-        <x:v>Duplicate ruleset_name and version cannot be published twice</x:v>
+        <x:v>Loading by name and version requires one immutable metadata row</x:v>
       </x:c>
       <x:c r="F33" s="29" t="str">
-        <x:v>Publish a ruleset, then attempt to publish another ruleset with the same ruleset_name and version.</x:v>
+        <x:v>Load and evaluate a uniquely published version, append a duplicate of that exact metadata row, then load the same explicit version again.</x:v>
       </x:c>
       <x:c r="G33" s="29" t="str">
-        <x:v>Second publish fails and does not overwrite the original row.</x:v>
+        <x:v>The unique row reconstructs and evaluates correctly; the duplicate immutable version fails loudly instead of selecting an arbitrary row.</x:v>
       </x:c>
       <x:c r="H33" s="29"/>
       <x:c r="I33" s="29" t="str">
-        <x:v>Exception output and original row content_hash comparison.</x:v>
+        <x:v>Notebook assertions and relevant metadata-table query output.</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="24" hidden="0" customHeight="1">
@@ -2817,26 +2783,26 @@
         <x:v>ST-031</x:v>
       </x:c>
       <x:c r="B34" s="28" t="str">
-        <x:v>Publishing</x:v>
+        <x:v>Lifecycle</x:v>
       </x:c>
       <x:c r="C34" s="28" t="str">
-        <x:v>High</x:v>
+        <x:v>Critical</x:v>
       </x:c>
       <x:c r="D34" s="28" t="str">
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E34" s="29" t="str">
-        <x:v>Multiple published versions for the same ruleset_name are allowed</x:v>
+        <x:v>Retirement makes a version unavailable to load_published</x:v>
       </x:c>
       <x:c r="F34" s="29" t="str">
-        <x:v>Publish version 1 and version 2 for the same ruleset_name.</x:v>
+        <x:v>Publish a ruleset, call service.retire(ruleset_id, version), then attempt load_published by name/version.</x:v>
       </x:c>
       <x:c r="G34" s="29" t="str">
-        <x:v>Both rows have status published. Neither publish requires retiring the other version.</x:v>
+        <x:v>The row status is retired and load_published no longer returns it.</x:v>
       </x:c>
       <x:c r="H34" s="29"/>
       <x:c r="I34" s="29" t="str">
-        <x:v>ruleset_versions query showing both versions.</x:v>
+        <x:v>Notebook assertions and relevant metadata-table query output.</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="48" hidden="0" customHeight="1">
@@ -2844,7 +2810,7 @@
         <x:v>ST-032</x:v>
       </x:c>
       <x:c r="B35" s="28" t="str">
-        <x:v>Publishing</x:v>
+        <x:v>Lifecycle</x:v>
       </x:c>
       <x:c r="C35" s="28" t="str">
         <x:v>High</x:v>
@@ -2853,17 +2819,17 @@
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E35" s="29" t="str">
-        <x:v>Loading by name without version is rejected when ambiguous</x:v>
+        <x:v>Retirement stamps retired_by and retired_at</x:v>
       </x:c>
       <x:c r="F35" s="29" t="str">
-        <x:v>With two published versions for the same ruleset_name, call service.load_published(ruleset_name) without version.</x:v>
+        <x:v>Retire a published version with retired_by populated.</x:v>
       </x:c>
       <x:c r="G35" s="29" t="str">
-        <x:v>Repository raises an error asking the caller to specify version.</x:v>
+        <x:v>retired_by and retired_at are populated and status is retired.</x:v>
       </x:c>
       <x:c r="H35" s="29"/>
       <x:c r="I35" s="29" t="str">
-        <x:v>Expected exception output.</x:v>
+        <x:v>Notebook assertions and relevant metadata-table query output.</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="48" hidden="0" customHeight="1">
@@ -2871,26 +2837,26 @@
         <x:v>ST-033</x:v>
       </x:c>
       <x:c r="B36" s="28" t="str">
-        <x:v>Publishing</x:v>
+        <x:v>Lifecycle</x:v>
       </x:c>
       <x:c r="C36" s="28" t="str">
-        <x:v>Critical</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="D36" s="28" t="str">
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E36" s="29" t="str">
-        <x:v>Loading by name and version requires one immutable metadata row</x:v>
+        <x:v>Retiring a missing ruleset version fails safely</x:v>
       </x:c>
       <x:c r="F36" s="29" t="str">
-        <x:v>Load and evaluate a uniquely published version, append a duplicate of that exact metadata row, then load the same explicit version again.</x:v>
+        <x:v>Call service.retire for a ruleset_id/version that does not exist.</x:v>
       </x:c>
       <x:c r="G36" s="29" t="str">
-        <x:v>The unique row reconstructs and evaluates correctly; the duplicate immutable version fails loudly instead of selecting an arbitrary row.</x:v>
+        <x:v>Repository raises a clear not-found error and no rows are changed.</x:v>
       </x:c>
       <x:c r="H36" s="29"/>
       <x:c r="I36" s="29" t="str">
-        <x:v>Notebook output comparing name, version, rule count, and content hash context.</x:v>
+        <x:v>Notebook assertions and relevant metadata-table query output.</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="36" hidden="0" customHeight="1">
@@ -2901,23 +2867,23 @@
         <x:v>Lifecycle</x:v>
       </x:c>
       <x:c r="C37" s="28" t="str">
-        <x:v>Critical</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="D37" s="28" t="str">
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E37" s="29" t="str">
-        <x:v>Retirement makes a version unavailable to load_published</x:v>
+        <x:v>Retiring an already retired version does not silently succeed</x:v>
       </x:c>
       <x:c r="F37" s="29" t="str">
-        <x:v>Publish a ruleset, call service.retire(ruleset_id, version), then attempt load_published by name/version.</x:v>
+        <x:v>Retire a version, then attempt to retire it again.</x:v>
       </x:c>
       <x:c r="G37" s="29" t="str">
-        <x:v>The row status is retired and load_published no longer returns it.</x:v>
+        <x:v>The first retirement succeeds. A second retirement raises RepositoryError and does not overwrite the original retirement metadata.</x:v>
       </x:c>
       <x:c r="H37" s="29"/>
       <x:c r="I37" s="29" t="str">
-        <x:v>ruleset_versions query and expected load failure.</x:v>
+        <x:v>Notebook assertions and relevant metadata-table query output.</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="24" hidden="0" customHeight="1">
@@ -2925,26 +2891,26 @@
         <x:v>ST-035</x:v>
       </x:c>
       <x:c r="B38" s="28" t="str">
-        <x:v>Lifecycle</x:v>
+        <x:v>Runtime Spark</x:v>
       </x:c>
       <x:c r="C38" s="28" t="str">
-        <x:v>High</x:v>
+        <x:v>Critical</x:v>
       </x:c>
       <x:c r="D38" s="28" t="str">
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E38" s="29" t="str">
-        <x:v>Retirement stamps retired_by and retired_at</x:v>
+        <x:v>Spark runtime evaluates simple row-level rules correctly</x:v>
       </x:c>
       <x:c r="F38" s="29" t="str">
-        <x:v>Retire a published version with retired_by populated.</x:v>
+        <x:v>Evaluate representative Spark rows with a published ruleset through service.evaluate_dataframe with full audit enabled.</x:v>
       </x:c>
       <x:c r="G38" s="29" t="str">
-        <x:v>retired_by and retired_at are populated and status is retired.</x:v>
+        <x:v>Matched flags, matched rule IDs, assignments, detailed matched-rule traces, and errors match expected outcomes.</x:v>
       </x:c>
       <x:c r="H38" s="29"/>
       <x:c r="I38" s="29" t="str">
-        <x:v>ruleset_versions lifecycle column output.</x:v>
+        <x:v>Notebook assertions, Spark schema, and representative result rows.</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="24" hidden="0" customHeight="1">
@@ -2952,7 +2918,7 @@
         <x:v>ST-036</x:v>
       </x:c>
       <x:c r="B39" s="28" t="str">
-        <x:v>Lifecycle</x:v>
+        <x:v>Runtime Spark</x:v>
       </x:c>
       <x:c r="C39" s="28" t="str">
         <x:v>High</x:v>
@@ -2961,17 +2927,17 @@
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E39" s="29" t="str">
-        <x:v>Retiring a missing ruleset version fails safely</x:v>
+        <x:v>Spark runtime honors rule_order and stop_on_match</x:v>
       </x:c>
       <x:c r="F39" s="29" t="str">
-        <x:v>Call service.retire for a ruleset_id/version that does not exist.</x:v>
+        <x:v>Evaluate rows where multiple rules can match and the first rule has stop_on_match configured.</x:v>
       </x:c>
       <x:c r="G39" s="29" t="str">
-        <x:v>Repository raises a clear not-found error and no rows are changed.</x:v>
+        <x:v>Assignments and matched rule IDs reflect ordered evaluation and stop behavior.</x:v>
       </x:c>
       <x:c r="H39" s="29"/>
       <x:c r="I39" s="29" t="str">
-        <x:v>Expected exception output.</x:v>
+        <x:v>Notebook assertions, Spark schema, and representative result rows.</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="48" hidden="0" customHeight="1">
@@ -2979,7 +2945,7 @@
         <x:v>ST-037</x:v>
       </x:c>
       <x:c r="B40" s="28" t="str">
-        <x:v>Lifecycle</x:v>
+        <x:v>Runtime Spark</x:v>
       </x:c>
       <x:c r="C40" s="28" t="str">
         <x:v>High</x:v>
@@ -2988,17 +2954,17 @@
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E40" s="29" t="str">
-        <x:v>Retiring an already retired version does not silently succeed</x:v>
+        <x:v>Spark row evaluator applies operand-level null defaults and condition errors correctly</x:v>
       </x:c>
       <x:c r="F40" s="29" t="str">
-        <x:v>Retire a version, then attempt to retire it again.</x:v>
+        <x:v>Evaluate null numeric and string fields with no fallback, `default_if_null`, and `error_on_null: true`.</x:v>
       </x:c>
       <x:c r="G40" s="29" t="str">
-        <x:v>The first retirement succeeds. A second retirement raises RepositoryError and does not overwrite the original retirement metadata.</x:v>
+        <x:v>Unresolved nulls do not match by default, typed fallbacks are compared, full audit shows substitution, and errors occur only when explicitly requested.</x:v>
       </x:c>
       <x:c r="H40" s="29"/>
       <x:c r="I40" s="29" t="str">
-        <x:v>Expected exception output.</x:v>
+        <x:v>Notebook assertions, Spark schema, and representative result rows.</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="36" hidden="0" customHeight="1">
@@ -3015,17 +2981,17 @@
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E41" s="29" t="str">
-        <x:v>Spark runtime evaluates simple row-level rules correctly</x:v>
+        <x:v>Spark runtime evaluates a published ruleset against a DataFrame</x:v>
       </x:c>
       <x:c r="F41" s="29" t="str">
-        <x:v>Evaluate representative Spark rows with a published ruleset through service.evaluate_dataframe.</x:v>
+        <x:v>Load a published ruleset by name/version and call service.evaluate_dataframe on a Spark DataFrame.</x:v>
       </x:c>
       <x:c r="G41" s="29" t="str">
-        <x:v>Matched flags, matched rule IDs, assignments, winning-rule trace, and errors match expected outcomes.</x:v>
+        <x:v>Output DataFrame contains error, matched, matched_rule_ids, assign, ruleset identity, and engine version columns with expected values.</x:v>
       </x:c>
       <x:c r="H41" s="29"/>
       <x:c r="I41" s="29" t="str">
-        <x:v>Actual vs expected output table.</x:v>
+        <x:v>Notebook assertions, Spark schema, and representative result rows.</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="36" hidden="0" customHeight="1">
@@ -3042,17 +3008,17 @@
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E42" s="29" t="str">
-        <x:v>Spark runtime honors rule_order and stop_on_match</x:v>
+        <x:v>Spark runtime fail_on_error behavior is enforced</x:v>
       </x:c>
       <x:c r="F42" s="29" t="str">
-        <x:v>Evaluate rows where multiple rules can match and the first rule has stop_on_match configured.</x:v>
+        <x:v>Evaluate a ruleset/input combination that triggers a runtime error with fail_on_error=True and False.</x:v>
       </x:c>
       <x:c r="G42" s="29" t="str">
-        <x:v>Assignments and matched rule IDs reflect ordered evaluation and stop behavior.</x:v>
+        <x:v>fail_on_error=True fails the job. fail_on_error=False records errors in output rows.</x:v>
       </x:c>
       <x:c r="H42" s="29"/>
       <x:c r="I42" s="29" t="str">
-        <x:v>Actual vs expected output table.</x:v>
+        <x:v>Notebook assertions, Spark schema, and representative result rows.</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="48" hidden="0" customHeight="1">
@@ -3069,17 +3035,17 @@
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E43" s="29" t="str">
-        <x:v>Spark row evaluator applies null_input_mode and null_result_mode correctly</x:v>
+        <x:v>Spark runtime supports standard custom functions used in rules</x:v>
       </x:c>
       <x:c r="F43" s="29" t="str">
-        <x:v>Evaluate rows containing null fields across propagate, zero, input-error, result-null, result-default, and result-error modes where applicable.</x:v>
+        <x:v>Publish and evaluate a ruleset that uses standard functions such as upper, trim, regex_extract, or to_number.</x:v>
       </x:c>
       <x:c r="G43" s="29" t="str">
-        <x:v>Results match documented null semantics and errors are emitted only where expected.</x:v>
+        <x:v>Evaluation succeeds and outputs match expected transformed values.</x:v>
       </x:c>
       <x:c r="H43" s="29"/>
       <x:c r="I43" s="29" t="str">
-        <x:v>Actual vs expected output table.</x:v>
+        <x:v>Notebook assertions, Spark schema, and representative result rows.</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="24" hidden="0" customHeight="1">
@@ -3090,23 +3056,23 @@
         <x:v>Runtime Spark</x:v>
       </x:c>
       <x:c r="C44" s="28" t="str">
-        <x:v>High</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="D44" s="28" t="str">
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E44" s="29" t="str">
-        <x:v>Spark runtime handles precomputed aggregate facts as fields</x:v>
+        <x:v>Spark runtime emits native assignment and trace structs</x:v>
       </x:c>
       <x:c r="F44" s="29" t="str">
-        <x:v>Evaluate a ruleset with upstream aggregate columns over representative records.</x:v>
+        <x:v>Evaluate a supported ruleset with full audit and inspect `rules_engine_assign` and `rules_engine_matched_rules`.</x:v>
       </x:c>
       <x:c r="G44" s="29" t="str">
-        <x:v>Comparisons and assignments match manually calculated expected values.</x:v>
+        <x:v>Matched flags, assignments, and each detailed matched-rule trace are emitted as Spark-native structs.</x:v>
       </x:c>
       <x:c r="H44" s="29"/>
       <x:c r="I44" s="29" t="str">
-        <x:v>Input data, expected calculations, and output table.</x:v>
+        <x:v>Notebook assertions, Spark schema, and representative result rows.</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="36" hidden="0" customHeight="1">
@@ -3114,7 +3080,7 @@
         <x:v>ST-042</x:v>
       </x:c>
       <x:c r="B45" s="28" t="str">
-        <x:v>Runtime Spark</x:v>
+        <x:v>Auditability</x:v>
       </x:c>
       <x:c r="C45" s="28" t="str">
         <x:v>Critical</x:v>
@@ -3123,17 +3089,17 @@
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E45" s="29" t="str">
-        <x:v>Spark runtime evaluates a published ruleset against a DataFrame</x:v>
+        <x:v>Payload JSON excludes mutable lifecycle fields and reconstructs ruleset content</x:v>
       </x:c>
       <x:c r="F45" s="29" t="str">
-        <x:v>Load a published ruleset by name/version and call service.evaluate_dataframe on a Spark DataFrame.</x:v>
+        <x:v>Inspect payload_json for a published row and deserialize/load the row.</x:v>
       </x:c>
       <x:c r="G45" s="29" t="str">
-        <x:v>Output DataFrame contains matched, matched_rule_ids, assign, winning_rule, and error columns with expected values.</x:v>
+        <x:v>payload_json contains canonical ruleset content but not lifecycle status. Loading reconstructs the expected ruleset.</x:v>
       </x:c>
       <x:c r="H45" s="29"/>
       <x:c r="I45" s="29" t="str">
-        <x:v>Displayed output DataFrame and schema.</x:v>
+        <x:v>Rendered output, immutable hashes, and representative diagnostic rows.</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="36" hidden="0" customHeight="1">
@@ -3141,7 +3107,7 @@
         <x:v>ST-043</x:v>
       </x:c>
       <x:c r="B46" s="28" t="str">
-        <x:v>Runtime Spark</x:v>
+        <x:v>Auditability</x:v>
       </x:c>
       <x:c r="C46" s="28" t="str">
         <x:v>High</x:v>
@@ -3150,17 +3116,17 @@
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E46" s="29" t="str">
-        <x:v>Spark runtime fail_on_error behavior is enforced</x:v>
+        <x:v>Content hash is deterministic and reproducible</x:v>
       </x:c>
       <x:c r="F46" s="29" t="str">
-        <x:v>Evaluate a ruleset/input combination that triggers a runtime error with fail_on_error=True and False.</x:v>
+        <x:v>Publish or serialize the same ruleset content twice in a controlled test and recompute SHA-256 from payload_json.</x:v>
       </x:c>
       <x:c r="G46" s="29" t="str">
-        <x:v>fail_on_error=True fails the job. fail_on_error=False records errors in output rows.</x:v>
+        <x:v>content_hash is stable and equals SHA-256 of payload_json bytes.</x:v>
       </x:c>
       <x:c r="H46" s="29"/>
       <x:c r="I46" s="29" t="str">
-        <x:v>Notebook output for both runs.</x:v>
+        <x:v>Rendered output, immutable hashes, and representative diagnostic rows.</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="36" hidden="0" customHeight="1">
@@ -3168,26 +3134,26 @@
         <x:v>ST-044</x:v>
       </x:c>
       <x:c r="B47" s="28" t="str">
-        <x:v>Runtime Spark</x:v>
+        <x:v>Auditability</x:v>
       </x:c>
       <x:c r="C47" s="28" t="str">
-        <x:v>High</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="D47" s="28" t="str">
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E47" s="29" t="str">
-        <x:v>Spark runtime supports standard custom functions used in rules</x:v>
+        <x:v>Summary count columns match the published ruleset content</x:v>
       </x:c>
       <x:c r="F47" s="29" t="str">
-        <x:v>Publish and evaluate a ruleset that uses standard functions such as upper, trim, regex_extract, or to_number.</x:v>
+        <x:v>Compare rule_count, condition_count, assignment_count, and custom_function_count to the compiled ruleset.</x:v>
       </x:c>
       <x:c r="G47" s="29" t="str">
-        <x:v>Evaluation succeeds and outputs match expected transformed values.</x:v>
+        <x:v>Persisted counts match the model counts.</x:v>
       </x:c>
       <x:c r="H47" s="29"/>
       <x:c r="I47" s="29" t="str">
-        <x:v>Actual vs expected output table.</x:v>
+        <x:v>Rendered output, immutable hashes, and representative diagnostic rows.</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="36" hidden="0" customHeight="1">
@@ -3198,23 +3164,23 @@
         <x:v>Runtime Spark</x:v>
       </x:c>
       <x:c r="C48" s="28" t="str">
-        <x:v>Medium</x:v>
+        <x:v>Critical</x:v>
       </x:c>
       <x:c r="D48" s="28" t="str">
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E48" s="29" t="str">
-        <x:v>Spark runtime emits native assignment and winning-rule structs</x:v>
+        <x:v>Spark runtime emits condition-level traceability values</x:v>
       </x:c>
       <x:c r="F48" s="29" t="str">
-        <x:v>Evaluate a supported ruleset and inspect rules_engine_assign and rules_engine_winning_rule output.</x:v>
+        <x:v>Publish a ruleset that combines a numeric field, a standard upper() function, and a string field condition; evaluate matched and unmatched rows with full audit; verify each `matched_rules` trace includes source columns, original and effective operand values, comparison results, pass/fail state, assignments, and an author-facing explanation.</x:v>
       </x:c>
       <x:c r="G48" s="29" t="str">
-        <x:v>Matched flags, assignments, and winning-rule trace are emitted as Spark-native structs.</x:v>
+        <x:v>`matched_rules` exposes complete row-specific traces for every match.</x:v>
       </x:c>
       <x:c r="H48" s="29"/>
       <x:c r="I48" s="29" t="str">
-        <x:v>Cross-runtime comparison table.</x:v>
+        <x:v>Notebook assertions, Spark schema, and representative result rows.</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="36" hidden="0" customHeight="1">
@@ -3225,23 +3191,23 @@
         <x:v>Auditability</x:v>
       </x:c>
       <x:c r="C49" s="28" t="str">
-        <x:v>Critical</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="D49" s="28" t="str">
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E49" s="29" t="str">
-        <x:v>Payload JSON excludes mutable lifecycle fields and reconstructs ruleset content</x:v>
+        <x:v>Service describes published rules in human-readable form</x:v>
       </x:c>
       <x:c r="F49" s="29" t="str">
-        <x:v>Inspect payload_json for a published row and deserialize/load the row.</x:v>
+        <x:v>Publish a ruleset with nested boolean logic and a custom-function condition; call service.describe_rules by ruleset name and version; verify each returned audit row has readable rule logic and match payload text.</x:v>
       </x:c>
       <x:c r="G49" s="29" t="str">
-        <x:v>payload_json contains canonical ruleset content but not lifecycle status. Loading reconstructs the expected ruleset.</x:v>
+        <x:v>describe_rules returns one readable row per rule with rule logic and match payload details.</x:v>
       </x:c>
       <x:c r="H49" s="29"/>
       <x:c r="I49" s="29" t="str">
-        <x:v>payload_json sample and load output.</x:v>
+        <x:v>Rendered output, immutable hashes, and representative diagnostic rows.</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="36" hidden="0" customHeight="1">
@@ -3249,26 +3215,26 @@
         <x:v>ST-047</x:v>
       </x:c>
       <x:c r="B50" s="28" t="str">
-        <x:v>Auditability</x:v>
+        <x:v>Runtime Spark</x:v>
       </x:c>
       <x:c r="C50" s="28" t="str">
-        <x:v>High</x:v>
+        <x:v>Critical</x:v>
       </x:c>
       <x:c r="D50" s="28" t="str">
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E50" s="29" t="str">
-        <x:v>Content hash is deterministic and reproducible</x:v>
+        <x:v>Spark runtime preserves expected output columns</x:v>
       </x:c>
       <x:c r="F50" s="29" t="str">
-        <x:v>Publish or serialize the same ruleset content twice in a controlled test and recompute SHA-256 from payload_json.</x:v>
+        <x:v>Publishes a simple ruleset and evaluates matched and unmatched rows; verifies original input columns plus the documented compact runtime columns are present and retain their semantics.</x:v>
       </x:c>
       <x:c r="G50" s="29" t="str">
-        <x:v>content_hash is stable and equals SHA-256 of payload_json bytes.</x:v>
+        <x:v>Spark runtime input columns and native output columns remain present and usable.</x:v>
       </x:c>
       <x:c r="H50" s="29"/>
       <x:c r="I50" s="29" t="str">
-        <x:v>Hash calculation output.</x:v>
+        <x:v>Notebook assertions, Spark schema, and representative result rows.</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="48" hidden="0" customHeight="1">
@@ -3276,26 +3242,26 @@
         <x:v>ST-048</x:v>
       </x:c>
       <x:c r="B51" s="28" t="str">
-        <x:v>Auditability</x:v>
+        <x:v>Runtime Spark</x:v>
       </x:c>
       <x:c r="C51" s="28" t="str">
-        <x:v>Medium</x:v>
+        <x:v>Critical</x:v>
       </x:c>
       <x:c r="D51" s="28" t="str">
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E51" s="29" t="str">
-        <x:v>Summary count columns match the published ruleset content</x:v>
+        <x:v>Spark runtime emits mapping literal assignments as nested structs</x:v>
       </x:c>
       <x:c r="F51" s="29" t="str">
-        <x:v>Compare rule_count, condition_count, assignment_count, and custom_function_count to the compiled ruleset.</x:v>
+        <x:v>Publishes a ruleset that assigns a literal struct such as non_modeled.market_value/book_value; evaluates a matching row; verifies rules_engine_assign contains a nested Spark struct with selectable boolean child fields.</x:v>
       </x:c>
       <x:c r="G51" s="29" t="str">
-        <x:v>Persisted counts match the model counts.</x:v>
+        <x:v>Mapping literal assignments are emitted as nested Spark structs without stringifying the struct payload.</x:v>
       </x:c>
       <x:c r="H51" s="29"/>
       <x:c r="I51" s="29" t="str">
-        <x:v>Query output and model count output.</x:v>
+        <x:v>Notebook assertions, Spark schema, and representative result rows.</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="36" hidden="0" customHeight="1">
@@ -3303,7 +3269,7 @@
         <x:v>ST-049</x:v>
       </x:c>
       <x:c r="B52" s="28" t="str">
-        <x:v>Pipeline notebooks</x:v>
+        <x:v>Runtime Spark</x:v>
       </x:c>
       <x:c r="C52" s="28" t="str">
         <x:v>Critical</x:v>
@@ -3312,17 +3278,17 @@
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E52" s="29" t="str">
-        <x:v>Publish notebook re-instantiates service against existing setup tables</x:v>
+        <x:v>Spark runtime match-trace explanations use service-style boolean logic</x:v>
       </x:c>
       <x:c r="F52" s="29" t="str">
-        <x:v>Run notebook 2 after notebook 1 using the same schema or custom table parameters.</x:v>
+        <x:v>Publishes a ruleset with nested all/any condition groups; evaluates a row with full audit where multiple nested branches pass; verifies the nested trace explanation matches RulesEngineService.describe_rules syntax while the trace retains evaluated operand values.</x:v>
       </x:c>
       <x:c r="G52" s="29" t="str">
-        <x:v>Notebook 2 compiles, validates, publishes, and verifies the ruleset without recreating setup objects.</x:v>
+        <x:v>Match-trace explanations use author-facing service syntax with AND/OR and parentheses, while trace structs retain evaluated values.</x:v>
       </x:c>
       <x:c r="H52" s="29"/>
       <x:c r="I52" s="29" t="str">
-        <x:v>Notebook 2 run URL and ruleset_versions query.</x:v>
+        <x:v>Notebook assertions, Spark schema, and representative result rows.</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="60" hidden="0" customHeight="1">
@@ -3330,26 +3296,26 @@
         <x:v>ST-050</x:v>
       </x:c>
       <x:c r="B53" s="28" t="str">
-        <x:v>Pipeline notebooks</x:v>
+        <x:v>Runtime Spark</x:v>
       </x:c>
       <x:c r="C53" s="28" t="str">
-        <x:v>High</x:v>
+        <x:v>Critical</x:v>
       </x:c>
       <x:c r="D53" s="28" t="str">
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E53" s="29" t="str">
-        <x:v>Notebook verification checks are present after setup and publish</x:v>
+        <x:v>Spark runtime ignores inactive rule assignment schemas</x:v>
       </x:c>
       <x:c r="F53" s="29" t="str">
-        <x:v>Review notebooks for assertions that tables exist, standard functions are registered, published row count equals one for target name/version, and load_published succeeds.</x:v>
+        <x:v>Publishes a ruleset where an active rule assigns a nested struct and an inactive rule assigns an incompatible value to the same target plus an inactive-only target.</x:v>
       </x:c>
       <x:c r="G53" s="29" t="str">
-        <x:v>Both notebooks fail fast when expected deployment or publish verification conditions are not met.</x:v>
+        <x:v>Inactive rules do not alter active assignment struct fields or types.</x:v>
       </x:c>
       <x:c r="H53" s="29"/>
       <x:c r="I53" s="29" t="str">
-        <x:v>Notebook source review and run output.</x:v>
+        <x:v>Notebook assertions, Spark schema, and representative result rows.</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="132" hidden="0" customHeight="1">
@@ -3360,19 +3326,19 @@
         <x:v>Runtime Spark</x:v>
       </x:c>
       <x:c r="C54" s="30" t="str">
-        <x:v>Critical</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="D54" s="30" t="str">
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E54" s="30" t="str">
-        <x:v>Spark runtime emits condition-level traceability values</x:v>
+        <x:v>Spark runtime merges continued multi-match assignments</x:v>
       </x:c>
       <x:c r="F54" s="30" t="str">
-        <x:v>Publishes a ruleset that combines a precomputed aggregate field, a standard upper() function, and a row-level field condition; evaluates matched and unmatched rows; verifies winning_rule includes source columns, evaluated operand values, comparison results, pass/fail state, assignments, and the author-facing winning-rule explanation.</x:v>
+        <x:v>Publish a ruleset with two matching rules where both use stop_on_match=false and assign the same compatible target; separately validate an incompatible variant.</x:v>
       </x:c>
       <x:c r="G54" s="30" t="str">
-        <x:v>winning_rule exposes source columns, evaluated operand values, comparison results, and readable author-facing winning-rule output.</x:v>
+        <x:v>Compatible assignments keep all matched IDs and use last-writer-wins; incompatible same-target types fail Spark compatibility validation without a string fallback.</x:v>
       </x:c>
       <x:c r="H54" s="30"/>
       <x:c r="I54" s="30" t="str">
@@ -3384,7 +3350,7 @@
         <x:v>ST-052</x:v>
       </x:c>
       <x:c r="B55" s="30" t="str">
-        <x:v>Auditability</x:v>
+        <x:v>Runtime Spark</x:v>
       </x:c>
       <x:c r="C55" s="30" t="str">
         <x:v>High</x:v>
@@ -3393,17 +3359,17 @@
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E55" s="30" t="str">
-        <x:v>Service describes published rules in human-readable form</x:v>
+        <x:v>Spark runtime serializes only required source fields</x:v>
       </x:c>
       <x:c r="F55" s="30" t="str">
-        <x:v>Publishes a ruleset with nested boolean logic, precomputed aggregate fields, and a custom-function condition; calls service.describe_rules by ruleset name and version; verifies each returned audit row has readable rule logic and match payload text.</x:v>
+        <x:v>Compiles a ruleset with a dotted condition field, a field-backed assignment, an inactive condition field, and an unrelated wide input field; verifies required_source_columns reports only active dependencies and runtime output preserves both evaluation and unrelated source data.</x:v>
       </x:c>
       <x:c r="G55" s="30" t="str">
-        <x:v>describe_rules returns one readable row per rule with rule logic and match payload details.</x:v>
+        <x:v>Required source dependencies are deterministic, dotted fields evaluate correctly, inactive and unrelated values are not serialized into the UDF, and original input columns remain present.</x:v>
       </x:c>
       <x:c r="H55" s="30"/>
       <x:c r="I55" s="30" t="str">
-        <x:v>Rendered report/output plus content hashes and representative diagnostic rows.</x:v>
+        <x:v>Notebook assertions, Spark schema, and representative result rows.</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="132" hidden="0" customHeight="1">
@@ -3414,19 +3380,19 @@
         <x:v>Runtime Spark</x:v>
       </x:c>
       <x:c r="C56" s="30" t="str">
-        <x:v>Critical</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="D56" s="30" t="str">
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E56" s="30" t="str">
-        <x:v>Spark runtime preserves expected output columns</x:v>
+        <x:v>Full-audit evaluation preserves matched-rule traces and row errors without duplicate evaluation</x:v>
       </x:c>
       <x:c r="F56" s="30" t="str">
-        <x:v>Publishes a simple ruleset and evaluates matched and unmatched rows; verifies original input columns plus rules_engine_matched, rules_engine_matched_rule_ids, rules_engine_assign, rules_engine_winning_rule, and rules_engine_error columns are present and retain their documented semantics.</x:v>
+        <x:v>Evaluates a ruleset where a losing ALL rule has a false first condition and a later `error_on_null` condition, followed by a matching rule; verifies a valid row receives only the matched rule's complete trace while the null row records the later losing-rule error.</x:v>
       </x:c>
       <x:c r="G56" s="30" t="str">
-        <x:v>Spark runtime input columns and native output columns remain present and usable.</x:v>
+        <x:v>Every reached active condition is evaluated once, losing rules emit no trace, and every matching rule retains its complete trace and assignment.</x:v>
       </x:c>
       <x:c r="H56" s="30"/>
       <x:c r="I56" s="30" t="str">
@@ -3447,13 +3413,13 @@
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E57" s="30" t="str">
-        <x:v>Spark runtime emits mapping literal assignments as nested structs</x:v>
+        <x:v>Financial types cross the real worker boundary exactly</x:v>
       </x:c>
       <x:c r="F57" s="30" t="str">
-        <x:v>Publishes a ruleset that assigns a literal struct such as non_modeled.market_value/book_value; evaluates a matching row; verifies rules_engine_assign contains a nested Spark struct with selectable boolean child fields.</x:v>
+        <x:v>Evaluate Decimal assignments and `to_number` outputs alongside Date, Timestamp, array, and struct assignments on each supported Databricks Runtime.</x:v>
       </x:c>
       <x:c r="G57" s="30" t="str">
-        <x:v>Mapping literal assignments are emitted as nested Spark structs without stringifying the struct payload.</x:v>
+        <x:v>Values and declared Spark types remain exact; no Decimal-to-double or timestamp-representation coercion occurs.</x:v>
       </x:c>
       <x:c r="H57" s="30"/>
       <x:c r="I57" s="30" t="str">
@@ -3468,19 +3434,19 @@
         <x:v>Runtime Spark</x:v>
       </x:c>
       <x:c r="C58" s="30" t="str">
-        <x:v>Critical</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="D58" s="30" t="str">
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E58" s="30" t="str">
-        <x:v>Spark runtime winning-rule explanations use service-style boolean logic</x:v>
+        <x:v>Fail-fast evaluation is lazy and uses one Python UDF</x:v>
       </x:c>
       <x:c r="F58" s="30" t="str">
-        <x:v>Publishes a ruleset with nested all/any condition groups; evaluates a row where multiple nested branches pass; verifies rules_engine_winning_rule_explanation matches RulesEngineService.describe_rules syntax while winning_rule retains evaluated operand values.</x:v>
+        <x:v>Build output with `fail_on_error=True`, verify one UDF is constructed without starting a job, then exercise clean and failing data.</x:v>
       </x:c>
       <x:c r="G58" s="30" t="str">
-        <x:v>Winning-rule explanations use author-facing service syntax with AND/OR and parentheses, while trace structs retain evaluated values.</x:v>
+        <x:v>Clean output remains lazy until the caller action; a bad row fails that action from the worker without a separate validation scan.</x:v>
       </x:c>
       <x:c r="H58" s="30"/>
       <x:c r="I58" s="30" t="str">
@@ -3495,19 +3461,19 @@
         <x:v>Runtime Spark</x:v>
       </x:c>
       <x:c r="C59" s="30" t="str">
-        <x:v>Critical</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="D59" s="30" t="str">
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E59" s="30" t="str">
-        <x:v>Spark runtime ignores inactive rule assignment schemas</x:v>
+        <x:v>Custom implementations are worker-serializable</x:v>
       </x:c>
       <x:c r="F59" s="30" t="str">
-        <x:v>Publishes a ruleset where an active rule assigns a nested struct and an inactive rule assigns an incompatible value to the same target plus an inactive-only target.</x:v>
+        <x:v>Register one approved top-level callable and one implementation capturing an unsupported object.</x:v>
       </x:c>
       <x:c r="G59" s="30" t="str">
-        <x:v>Inactive rules do not alter active assignment struct fields or types.</x:v>
+        <x:v>The approved callable evaluates; the unsupported closure fails serialization preflight before job submission with a focused validation error.</x:v>
       </x:c>
       <x:c r="H59" s="30"/>
       <x:c r="I59" s="30" t="str">
@@ -3519,26 +3485,26 @@
         <x:v>ST-057</x:v>
       </x:c>
       <x:c r="B60" s="30" t="str">
-        <x:v>Runtime Spark</x:v>
+        <x:v>Standard functions</x:v>
       </x:c>
       <x:c r="C60" s="30" t="str">
-        <x:v>High</x:v>
+        <x:v>Critical</x:v>
       </x:c>
       <x:c r="D60" s="30" t="str">
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E60" s="30" t="str">
-        <x:v>Spark runtime merges continued multi-match assignments</x:v>
+        <x:v>Standard date functions support loan-tape calendar semantics</x:v>
       </x:c>
       <x:c r="F60" s="30" t="str">
-        <x:v>Publish a ruleset with two matching rules where both use stop_on_match=false and assign the same compatible target; separately validate an incompatible variant.</x:v>
+        <x:v>Evaluate month-end addition, leap-year handling, date differences, typed date/integer assignments, and authored assignment expressions through a real Spark worker.</x:v>
       </x:c>
       <x:c r="G60" s="30" t="str">
-        <x:v>Compatible assignments keep all matched IDs and use last-writer-wins; incompatible same-target types fail Spark compatibility validation without a string fallback.</x:v>
+        <x:v>Month-end and leap-year calculations remain calendar-safe and produce typed assignments with self-contained authored expressions.</x:v>
       </x:c>
       <x:c r="H60" s="30"/>
       <x:c r="I60" s="30" t="str">
-        <x:v>Notebook assertions, Spark schema, and representative result rows.</x:v>
+        <x:v>Notebook assertions and validation or exception output.</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="105.5999984741211" hidden="0" customHeight="1">
@@ -3546,26 +3512,26 @@
         <x:v>ST-058</x:v>
       </x:c>
       <x:c r="B61" s="30" t="str">
-        <x:v>Runtime Spark</x:v>
+        <x:v>Publishing</x:v>
       </x:c>
       <x:c r="C61" s="30" t="str">
-        <x:v>High</x:v>
+        <x:v>Critical</x:v>
       </x:c>
       <x:c r="D61" s="30" t="str">
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E61" s="30" t="str">
-        <x:v>Spark runtime serializes only required source fields</x:v>
+        <x:v>Embedded expected cases are a hard publication gate</x:v>
       </x:c>
       <x:c r="F61" s="30" t="str">
-        <x:v>Compiles a ruleset with a dotted condition field, a field-backed assignment, an inactive condition field, and an unrelated wide input field; verifies required_source_columns reports only active dependencies and runtime output preserves both evaluation and unrelated source data.</x:v>
+        <x:v>Publish a ruleset whose named cases pass, then attempt publication with a deliberately incorrect expected assignment.</x:v>
       </x:c>
       <x:c r="G61" s="30" t="str">
-        <x:v>Required source dependencies are deterministic, dotted fields evaluate correctly, inactive and unrelated values are not serialized into the UDF, and original input columns remain present.</x:v>
+        <x:v>Passing cases publish; failing cases raise before any Delta repository row is written.</x:v>
       </x:c>
       <x:c r="H61" s="30"/>
       <x:c r="I61" s="30" t="str">
-        <x:v>Notebook assertions, Spark schema, and representative result rows.</x:v>
+        <x:v>Notebook assertions and relevant metadata-table query output.</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="92.4000015258789" hidden="0" customHeight="1">
@@ -3573,26 +3539,26 @@
         <x:v>ST-059</x:v>
       </x:c>
       <x:c r="B62" s="30" t="str">
-        <x:v>Runtime Spark</x:v>
+        <x:v>Auditability</x:v>
       </x:c>
       <x:c r="C62" s="30" t="str">
-        <x:v>High</x:v>
+        <x:v>Critical</x:v>
       </x:c>
       <x:c r="D62" s="30" t="str">
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E62" s="30" t="str">
-        <x:v>Match-only evaluation preserves winning trace and row errors</x:v>
+        <x:v>Compact and full-audit outputs retain immutable execution identity</x:v>
       </x:c>
       <x:c r="F62" s="30" t="str">
-        <x:v>Evaluates a ruleset where a losing ALL rule has a false first condition and a later null-result error condition, followed by a winning rule; verifies a valid row receives the complete winning-rule trace while the null row still records the later losing-rule error.</x:v>
+        <x:v>Evaluate the same row with `full_audit=False` and `True`, then inspect schema ordering and identity values without coupling the test to packaged-wheel metadata.</x:v>
       </x:c>
       <x:c r="G62" s="30" t="str">
-        <x:v>Losing rules avoid output trace construction without short-circuiting observable errors, and the first matching rule retains its complete trace and assignment.</x:v>
+        <x:v>Each mode emits only its documented detail while retaining the ruleset struct and a non-empty engine version.</x:v>
       </x:c>
       <x:c r="H62" s="30"/>
       <x:c r="I62" s="30" t="str">
-        <x:v>Notebook assertions, Spark schema, and representative result rows.</x:v>
+        <x:v>Rendered output, immutable hashes, and representative diagnostic rows.</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="66" hidden="0" customHeight="1">
@@ -3600,26 +3566,26 @@
         <x:v>ST-060</x:v>
       </x:c>
       <x:c r="B63" s="30" t="str">
-        <x:v>Runtime Spark</x:v>
+        <x:v>Change control</x:v>
       </x:c>
       <x:c r="C63" s="30" t="str">
-        <x:v>Critical</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="D63" s="30" t="str">
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E63" s="30" t="str">
-        <x:v>Financial types cross the real worker boundary exactly</x:v>
+        <x:v>Semantic diffs compare immutable published versions</x:v>
       </x:c>
       <x:c r="F63" s="30" t="str">
-        <x:v>Evaluate Decimal assignments and `to_number` outputs alongside Date, Timestamp, array, and struct assignments on each supported Databricks Runtime.</x:v>
+        <x:v>Publish two versions with a threshold and assignment change, then call `diff_versions`.</x:v>
       </x:c>
       <x:c r="G63" s="30" t="str">
-        <x:v>Values and declared Spark types remain exact; no Decimal-to-double or timestamp-representation coercion occurs.</x:v>
+        <x:v>The rendered diff identifies both authored changes and carries distinct baseline/candidate content hashes.</x:v>
       </x:c>
       <x:c r="H63" s="30"/>
       <x:c r="I63" s="30" t="str">
-        <x:v>Notebook assertions, Spark schema, and representative result rows.</x:v>
+        <x:v>Rendered output, immutable hashes, and representative diagnostic rows.</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="52.79999923706055" hidden="0" customHeight="1">
@@ -3627,7 +3593,7 @@
         <x:v>ST-061</x:v>
       </x:c>
       <x:c r="B64" s="30" t="str">
-        <x:v>Runtime Spark</x:v>
+        <x:v>Change control</x:v>
       </x:c>
       <x:c r="C64" s="30" t="str">
         <x:v>High</x:v>
@@ -3636,17 +3602,17 @@
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E64" s="30" t="str">
-        <x:v>Fail-fast evaluation is lazy and single pass</x:v>
+        <x:v>Coverage reports dead, broad, and closest rules</x:v>
       </x:c>
       <x:c r="F64" s="30" t="str">
-        <x:v>Build output with `fail_on_error=True`, confirm no job starts until a write/count/collect action, and exercise clean and failing data.</x:v>
+        <x:v>Analyze representative loan rows containing first matches and a clean no-match row, then materialize its closest-rule diagnostic.</x:v>
       </x:c>
       <x:c r="G64" s="30" t="str">
-        <x:v>Clean output is evaluated once during the caller action; a bad row fails that action from the worker without a separate validation scan.</x:v>
+        <x:v>Counts, dead/broad rule IDs, closest rule, and failed condition IDs match the hand-verified fixture.</x:v>
       </x:c>
       <x:c r="H64" s="30"/>
       <x:c r="I64" s="30" t="str">
-        <x:v>Notebook assertions, Spark schema, and representative result rows.</x:v>
+        <x:v>Rendered output, immutable hashes, and representative diagnostic rows.</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="52.79999923706055" hidden="0" customHeight="1">
@@ -3657,19 +3623,19 @@
         <x:v>Runtime Spark</x:v>
       </x:c>
       <x:c r="C65" s="30" t="str">
-        <x:v>High</x:v>
+        <x:v>Critical</x:v>
       </x:c>
       <x:c r="D65" s="30" t="str">
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E65" s="30" t="str">
-        <x:v>Custom implementations are worker-serializable</x:v>
+        <x:v>Later rules consume explicit prior assignment results</x:v>
       </x:c>
       <x:c r="F65" s="30" t="str">
-        <x:v>Register one approved top-level callable and one implementation capturing an unsupported object.</x:v>
+        <x:v>Evaluate a producer/consumer chain, a missing-producer row with a fallback, original-row and assigned reads of the same name, and two sibling assignments that would differ under sequential mutation.</x:v>
       </x:c>
       <x:c r="G65" s="30" t="str">
-        <x:v>The approved callable evaluates; the unsupported closure fails serialization preflight before job submission with a focused validation error.</x:v>
+        <x:v>Later rules see lower-order commits, field operands retain original-row semantics, missing commits follow null defaults, sibling assignments read one pre-rule snapshot, and full audit identifies the producing rule and assignment.</x:v>
       </x:c>
       <x:c r="H65" s="30"/>
       <x:c r="I65" s="30" t="str">
@@ -3677,139 +3643,70 @@
       </x:c>
     </x:row>
     <x:row r="66" ht="66" hidden="0" customHeight="1">
-      <x:c r="A66" s="30" t="str">
-        <x:v>ST-063</x:v>
-      </x:c>
-      <x:c r="B66" s="30" t="str">
-        <x:v>Standard functions</x:v>
-      </x:c>
-      <x:c r="C66" s="30" t="str">
-        <x:v>Critical</x:v>
-      </x:c>
-      <x:c r="D66" s="30" t="str">
-        <x:v>Engineering</x:v>
-      </x:c>
-      <x:c r="E66" s="30" t="str">
-        <x:v>Standard date functions support loan-tape calendar semantics</x:v>
-      </x:c>
-      <x:c r="F66" s="30" t="str">
-        <x:v>Evaluate month-end addition, leap-year handling, date differences, typed date/integer assignments, and authored assignment expressions through a real Spark worker.</x:v>
-      </x:c>
-      <x:c r="G66" s="30" t="str">
-        <x:v>Month-end and leap-year calculations remain calendar-safe and produce typed assignments with self-contained authored expressions.</x:v>
-      </x:c>
-      <x:c r="H66" s="30"/>
-      <x:c r="I66" s="30" t="str">
-        <x:v>Notebook assertions, Spark schema, and representative result rows.</x:v>
-      </x:c>
+      <x:c r="A66"/>
+      <x:c r="B66"/>
+      <x:c r="C66"/>
+      <x:c r="D66"/>
+      <x:c r="E66"/>
+      <x:c r="F66"/>
+      <x:c r="G66"/>
+      <x:c r="H66"/>
+      <x:c r="I66"/>
     </x:row>
     <x:row r="67" ht="52.79999923706055" hidden="0" customHeight="1">
-      <x:c r="A67" s="30" t="str">
-        <x:v>ST-064</x:v>
-      </x:c>
-      <x:c r="B67" s="30" t="str">
-        <x:v>Publishing</x:v>
-      </x:c>
-      <x:c r="C67" s="30" t="str">
-        <x:v>Critical</x:v>
-      </x:c>
-      <x:c r="D67" s="30" t="str">
-        <x:v>Engineering</x:v>
-      </x:c>
-      <x:c r="E67" s="30" t="str">
-        <x:v>Embedded expected cases are a hard publication gate</x:v>
-      </x:c>
-      <x:c r="F67" s="30" t="str">
-        <x:v>Publish a ruleset whose named cases pass, then attempt publication with a deliberately incorrect expected assignment.</x:v>
-      </x:c>
-      <x:c r="G67" s="30" t="str">
-        <x:v>Passing cases publish; failing cases raise before any Delta repository row is written.</x:v>
-      </x:c>
-      <x:c r="H67" s="30"/>
-      <x:c r="I67" s="30" t="str">
-        <x:v>Notebook output plus the matching ruleset_versions query result.</x:v>
-      </x:c>
+      <x:c r="A67"/>
+      <x:c r="B67"/>
+      <x:c r="C67"/>
+      <x:c r="D67"/>
+      <x:c r="E67"/>
+      <x:c r="F67"/>
+      <x:c r="G67"/>
+      <x:c r="H67"/>
+      <x:c r="I67"/>
     </x:row>
     <x:row r="68" ht="52.79999923706055" hidden="0" customHeight="1">
-      <x:c r="A68" s="30" t="str">
-        <x:v>ST-065</x:v>
-      </x:c>
-      <x:c r="B68" s="30" t="str">
-        <x:v>Auditability</x:v>
-      </x:c>
-      <x:c r="C68" s="30" t="str">
-        <x:v>Critical</x:v>
-      </x:c>
-      <x:c r="D68" s="30" t="str">
-        <x:v>Engineering</x:v>
-      </x:c>
-      <x:c r="E68" s="30" t="str">
-        <x:v>Audit levels retain immutable execution identity</x:v>
-      </x:c>
-      <x:c r="F68" s="30" t="str">
-        <x:v>Evaluate the same row with minimal, standard, and full audit levels and inspect their schemas and identity values.</x:v>
-      </x:c>
-      <x:c r="G68" s="30" t="str">
-        <x:v>Each level emits only its documented detail while retaining ruleset ID, version, content hash, and engine version.</x:v>
-      </x:c>
-      <x:c r="H68" s="30"/>
-      <x:c r="I68" s="30" t="str">
-        <x:v>Rendered report/output plus content hashes and representative diagnostic rows.</x:v>
-      </x:c>
+      <x:c r="A68"/>
+      <x:c r="B68"/>
+      <x:c r="C68"/>
+      <x:c r="D68"/>
+      <x:c r="E68"/>
+      <x:c r="F68"/>
+      <x:c r="G68"/>
+      <x:c r="H68"/>
+      <x:c r="I68"/>
     </x:row>
     <x:row r="69" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A69" s="30" t="str">
-        <x:v>ST-066</x:v>
-      </x:c>
-      <x:c r="B69" s="30" t="str">
-        <x:v>Change control</x:v>
-      </x:c>
-      <x:c r="C69" s="30" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="D69" s="30" t="str">
-        <x:v>Engineering</x:v>
-      </x:c>
-      <x:c r="E69" s="30" t="str">
-        <x:v>Semantic diffs compare immutable published versions</x:v>
-      </x:c>
-      <x:c r="F69" s="30" t="str">
-        <x:v>Publish two versions with a threshold and assignment change, then call `diff_versions`.</x:v>
-      </x:c>
-      <x:c r="G69" s="30" t="str">
-        <x:v>The rendered diff identifies both authored changes and carries distinct baseline/candidate content hashes.</x:v>
-      </x:c>
-      <x:c r="H69" s="30"/>
-      <x:c r="I69" s="30" t="str">
-        <x:v>Rendered report/output plus content hashes and representative diagnostic rows.</x:v>
-      </x:c>
+      <x:c r="A69"/>
+      <x:c r="B69"/>
+      <x:c r="C69"/>
+      <x:c r="D69"/>
+      <x:c r="E69"/>
+      <x:c r="F69"/>
+      <x:c r="G69"/>
+      <x:c r="H69"/>
+      <x:c r="I69"/>
     </x:row>
     <x:row r="70" ht="52.79999923706055" hidden="0" customHeight="1">
-      <x:c r="A70" s="30" t="str">
-        <x:v>ST-067</x:v>
-      </x:c>
-      <x:c r="B70" s="30" t="str">
-        <x:v>Change control</x:v>
-      </x:c>
-      <x:c r="C70" s="30" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="D70" s="30" t="str">
-        <x:v>Engineering</x:v>
-      </x:c>
-      <x:c r="E70" s="30" t="str">
-        <x:v>Coverage reports dead, broad, and closest rules</x:v>
-      </x:c>
-      <x:c r="F70" s="30" t="str">
-        <x:v>Analyze representative loan rows containing first matches and a clean no-match row, then materialize its closest-rule diagnostic.</x:v>
-      </x:c>
-      <x:c r="G70" s="30" t="str">
-        <x:v>Counts, dead/broad rule IDs, closest rule, and failed condition IDs match the hand-verified fixture.</x:v>
-      </x:c>
-      <x:c r="H70" s="30"/>
-      <x:c r="I70" s="30" t="str">
-        <x:v>Rendered report/output plus content hashes and representative diagnostic rows.</x:v>
-      </x:c>
+      <x:c r="A70"/>
+      <x:c r="B70"/>
+      <x:c r="C70"/>
+      <x:c r="D70"/>
+      <x:c r="E70"/>
+      <x:c r="F70"/>
+      <x:c r="G70"/>
+      <x:c r="H70"/>
+      <x:c r="I70"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71"/>
+      <x:c r="B71"/>
+      <x:c r="C71"/>
+      <x:c r="D71"/>
+      <x:c r="E71"/>
+      <x:c r="F71"/>
+      <x:c r="G71"/>
+      <x:c r="H71"/>
+      <x:c r="I71"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -3828,7 +3725,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5686b3eb2aad4481"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47e45440a0764f9a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3849,7 +3746,7 @@
   <x:sheetData>
     <x:row r="1" ht="18" customHeight="1">
       <x:c r="A1" s="13" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B1" s="14"/>
       <x:c r="C1" s="14"/>
@@ -3913,7 +3810,7 @@
       </x:c>
       <x:c r="H4" s="34"/>
       <x:c r="I4" s="33" t="str">
-        <x:v>Business confirmation notes or screenshot.</x:v>
+        <x:v>Review notes and supporting evidence.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="87.94999694824219" customHeight="1">
@@ -3940,7 +3837,7 @@
       </x:c>
       <x:c r="H5" s="34"/>
       <x:c r="I5" s="33" t="str">
-        <x:v>Marked-up YAML or review notes.</x:v>
+        <x:v>Review notes and supporting evidence.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="87.94999694824219" customHeight="1">
@@ -3967,7 +3864,7 @@
       </x:c>
       <x:c r="H6" s="34"/>
       <x:c r="I6" s="33" t="str">
-        <x:v>Assignment review checklist.</x:v>
+        <x:v>Review notes and supporting evidence.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="87.94999694824219" customHeight="1">
@@ -3990,11 +3887,11 @@
         <x:v>Review scenarios where multiple rules could match the same record.</x:v>
       </x:c>
       <x:c r="G7" s="33" t="str">
-        <x:v>The chosen rule order and stop behavior produce the intended winning assignment.</x:v>
+        <x:v>The chosen rule order and stop behavior produce the intended combined assignments.</x:v>
       </x:c>
       <x:c r="H7" s="34"/>
       <x:c r="I7" s="33" t="str">
-        <x:v>Scenario notes and expected outcome table.</x:v>
+        <x:v>Review notes and supporting evidence.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="87.94999694824219" customHeight="1">
@@ -4021,7 +3918,7 @@
       </x:c>
       <x:c r="H8" s="34"/>
       <x:c r="I8" s="33" t="str">
-        <x:v>Tester comments on error clarity.</x:v>
+        <x:v>Review notes and supporting evidence.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="87.94999694824219" customHeight="1">
@@ -4048,7 +3945,7 @@
       </x:c>
       <x:c r="H9" s="34"/>
       <x:c r="I9" s="33" t="str">
-        <x:v>Validation output and approval note.</x:v>
+        <x:v>Review notes and supporting evidence.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="87.94999694824219" customHeight="1">
@@ -4075,7 +3972,7 @@
       </x:c>
       <x:c r="H10" s="34"/>
       <x:c r="I10" s="33" t="str">
-        <x:v>Published metadata screenshot.</x:v>
+        <x:v>Review notes and supporting evidence.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="87.94999694824219" customHeight="1">
@@ -4102,7 +3999,7 @@
       </x:c>
       <x:c r="H11" s="34"/>
       <x:c r="I11" s="33" t="str">
-        <x:v>ruleset_versions screenshot showing both versions.</x:v>
+        <x:v>Review notes and supporting evidence.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="87.94999694824219" customHeight="1">
@@ -4129,7 +4026,7 @@
       </x:c>
       <x:c r="H12" s="34"/>
       <x:c r="I12" s="33" t="str">
-        <x:v>Notebook output.</x:v>
+        <x:v>Review notes and supporting evidence.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="87.94999694824219" customHeight="1">
@@ -4156,7 +4053,7 @@
       </x:c>
       <x:c r="H13" s="34"/>
       <x:c r="I13" s="33" t="str">
-        <x:v>Actual vs expected UAT results workbook/table.</x:v>
+        <x:v>Review notes and supporting evidence.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="87.94999694824219" customHeight="1">
@@ -4183,7 +4080,7 @@
       </x:c>
       <x:c r="H14" s="34"/>
       <x:c r="I14" s="33" t="str">
-        <x:v>Actual vs expected output table.</x:v>
+        <x:v>Review notes and supporting evidence.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="87.94999694824219" customHeight="1">
@@ -4210,7 +4107,7 @@
       </x:c>
       <x:c r="H15" s="34"/>
       <x:c r="I15" s="33" t="str">
-        <x:v>Boundary scenario result table.</x:v>
+        <x:v>Review notes and supporting evidence.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="87.94999694824219" customHeight="1">
@@ -4218,26 +4115,26 @@
         <x:v>UAT-013</x:v>
       </x:c>
       <x:c r="B16" s="33" t="str">
-        <x:v>Runtime results</x:v>
+        <x:v>Custom functions</x:v>
       </x:c>
       <x:c r="C16" s="33" t="str">
-        <x:v>High</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="D16" s="33" t="str">
         <x:v>Business Owner</x:v>
       </x:c>
       <x:c r="E16" s="33" t="str">
-        <x:v>Precomputed aggregate business rules match manual calculations</x:v>
+        <x:v>Standard text, number, and date transformations produce recognizable business outcomes</x:v>
       </x:c>
       <x:c r="F16" s="33" t="str">
-        <x:v>For rules using upstream aggregate columns, compare engine outputs to manually reviewed aggregate calculations.</x:v>
+        <x:v>Review trim, case, regex, numeric conversion, month-end/leap-year date addition, and date-difference rules on representative records.</x:v>
       </x:c>
       <x:c r="G16" s="33" t="str">
-        <x:v>Engine results agree with manual calculations for sampled groups or datasets.</x:v>
+        <x:v>Function-driven outcomes and calendar semantics match what business users expect from the source data.</x:v>
       </x:c>
       <x:c r="H16" s="34"/>
       <x:c r="I16" s="33" t="str">
-        <x:v>Manual calculation sheet and output screenshot.</x:v>
+        <x:v>Review notes and supporting evidence.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="87.94999694824219" customHeight="1">
@@ -4245,26 +4142,26 @@
         <x:v>UAT-014</x:v>
       </x:c>
       <x:c r="B17" s="33" t="str">
-        <x:v>Custom functions</x:v>
+        <x:v>Operational workflow</x:v>
       </x:c>
       <x:c r="C17" s="33" t="str">
-        <x:v>Medium</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="D17" s="33" t="str">
-        <x:v>Business Owner</x:v>
+        <x:v>UAT Tester</x:v>
       </x:c>
       <x:c r="E17" s="33" t="str">
-        <x:v>Standard text, number, and date transformations produce recognizable business outcomes</x:v>
+        <x:v>Retirement workflow removes a version from runtime eligibility</x:v>
       </x:c>
       <x:c r="F17" s="33" t="str">
-        <x:v>Review trim, case, regex, numeric conversion, month-end/leap-year date addition, and date-difference rules on representative records.</x:v>
+        <x:v>Retire a test version that should no longer be used.</x:v>
       </x:c>
       <x:c r="G17" s="33" t="str">
-        <x:v>Function-driven outcomes and calendar semantics match what business users expect from the source data.</x:v>
+        <x:v>The version status changes to retired and cannot be loaded through published-only load calls.</x:v>
       </x:c>
       <x:c r="H17" s="34"/>
       <x:c r="I17" s="33" t="str">
-        <x:v>Before/after sample output.</x:v>
+        <x:v>Review notes and supporting evidence.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="87.94999694824219" customHeight="1">
@@ -4275,23 +4172,23 @@
         <x:v>Operational workflow</x:v>
       </x:c>
       <x:c r="C18" s="33" t="str">
-        <x:v>High</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="D18" s="33" t="str">
-        <x:v>UAT Tester</x:v>
+        <x:v>Business Owner</x:v>
       </x:c>
       <x:c r="E18" s="33" t="str">
-        <x:v>Setup notebook can be rerun safely before publishing</x:v>
+        <x:v>Release evidence is sufficient for audit review</x:v>
       </x:c>
       <x:c r="F18" s="33" t="str">
-        <x:v>Rerun setup notebook after tables and function metadata already exist.</x:v>
+        <x:v>Review publish metadata, content hash, payload_json, expected-case results, semantic diff, coverage output, and notebook run links.</x:v>
       </x:c>
       <x:c r="G18" s="33" t="str">
-        <x:v>Notebook succeeds, refreshes package-owned standard metadata to the installed versions, and creates no duplicate rows.</x:v>
+        <x:v>Release evidence is complete enough to support approval and later audit.</x:v>
       </x:c>
       <x:c r="H18" s="34"/>
       <x:c r="I18" s="33" t="str">
-        <x:v>Notebook rerun output and function count comparison.</x:v>
+        <x:v>Review notes and supporting evidence.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="87.94999694824219" customHeight="1">
@@ -4299,26 +4196,26 @@
         <x:v>UAT-016</x:v>
       </x:c>
       <x:c r="B19" s="33" t="str">
-        <x:v>Operational workflow</x:v>
+        <x:v>Downstream readiness</x:v>
       </x:c>
       <x:c r="C19" s="33" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="D19" s="33" t="str">
-        <x:v>UAT Tester</x:v>
+        <x:v>Data Consumer</x:v>
       </x:c>
       <x:c r="E19" s="33" t="str">
-        <x:v>Publish notebook can be rerun safely for same candidate and handles duplicate publish clearly</x:v>
+        <x:v>Output DataFrame schema is usable by downstream jobs</x:v>
       </x:c>
       <x:c r="F19" s="33" t="str">
-        <x:v>Rerun publish notebook for an already-published ruleset_name/version.</x:v>
+        <x:v>Review compact/full-audit schemas and immutable identity columns with a downstream consumer or integration owner.</x:v>
       </x:c>
       <x:c r="G19" s="33" t="str">
-        <x:v>Notebook fails or stops with a clear duplicate version message and does not overwrite the original published row.</x:v>
+        <x:v>The chosen audit mode, native fields, match/error outputs, and ruleset/engine identity columns are understood and usable.</x:v>
       </x:c>
       <x:c r="H19" s="34"/>
       <x:c r="I19" s="33" t="str">
-        <x:v>Notebook output and original row evidence.</x:v>
+        <x:v>Review notes and supporting evidence.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="87.94999694824219" customHeight="1">
@@ -4326,26 +4223,26 @@
         <x:v>UAT-017</x:v>
       </x:c>
       <x:c r="B20" s="33" t="str">
-        <x:v>Operational workflow</x:v>
+        <x:v>Downstream readiness</x:v>
       </x:c>
       <x:c r="C20" s="33" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="D20" s="33" t="str">
-        <x:v>Release Manager</x:v>
+        <x:v>Data Consumer</x:v>
       </x:c>
       <x:c r="E20" s="33" t="str">
-        <x:v>Retirement workflow removes a version from runtime eligibility</x:v>
+        <x:v>Assignment struct can be consumed by downstream Spark consumers</x:v>
       </x:c>
       <x:c r="F20" s="33" t="str">
-        <x:v>Retire a test version that should no longer be used.</x:v>
+        <x:v>Consume the assign struct using downstream expected field access.</x:v>
       </x:c>
       <x:c r="G20" s="33" t="str">
-        <x:v>The version status changes to retired and cannot be loaded through published-only load calls.</x:v>
+        <x:v>Assignments can be consumed without manual JSON parsing.</x:v>
       </x:c>
       <x:c r="H20" s="34"/>
       <x:c r="I20" s="33" t="str">
-        <x:v>Lifecycle row screenshot and load failure output.</x:v>
+        <x:v>Review notes and supporting evidence.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="87.94999694824219" customHeight="1">
@@ -4353,26 +4250,26 @@
         <x:v>UAT-018</x:v>
       </x:c>
       <x:c r="B21" s="33" t="str">
-        <x:v>Operational workflow</x:v>
+        <x:v>Exception handling</x:v>
       </x:c>
       <x:c r="C21" s="33" t="str">
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="D21" s="33" t="str">
-        <x:v>Release Manager</x:v>
+        <x:v>UAT Tester</x:v>
       </x:c>
       <x:c r="E21" s="33" t="str">
-        <x:v>Release evidence is sufficient for audit review</x:v>
+        <x:v>Runtime error handling is acceptable for business operations</x:v>
       </x:c>
       <x:c r="F21" s="33" t="str">
-        <x:v>Review publish metadata, content hash, payload_json, expected-case results, semantic diff, coverage output, and notebook run links.</x:v>
+        <x:v>Review behavior when fail_on_error is true and false using a controlled bad input scenario.</x:v>
       </x:c>
       <x:c r="G21" s="33" t="str">
-        <x:v>Release evidence is complete enough to support approval and later audit.</x:v>
+        <x:v>The team agrees which mode is appropriate for production and how errors will be monitored.</x:v>
       </x:c>
       <x:c r="H21" s="34"/>
       <x:c r="I21" s="33" t="str">
-        <x:v>Evidence package checklist.</x:v>
+        <x:v>Review notes and supporting evidence.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="87.94999694824219" customHeight="1">
@@ -4380,162 +4277,82 @@
         <x:v>UAT-019</x:v>
       </x:c>
       <x:c r="B22" s="33" t="str">
-        <x:v>Downstream readiness</x:v>
+        <x:v>Sign-off</x:v>
       </x:c>
       <x:c r="C22" s="33" t="str">
-        <x:v>High</x:v>
+        <x:v>Critical</x:v>
       </x:c>
       <x:c r="D22" s="33" t="str">
-        <x:v>Data Consumer</x:v>
+        <x:v>Business Owner</x:v>
       </x:c>
       <x:c r="E22" s="33" t="str">
-        <x:v>Output DataFrame schema is usable by downstream jobs</x:v>
+        <x:v>Business owner approves the published candidate version</x:v>
       </x:c>
       <x:c r="F22" s="33" t="str">
-        <x:v>Review minimal/standard/full schemas and immutable identity columns with a downstream consumer or integration owner.</x:v>
+        <x:v>Review validation output, UAT outputs, and open defects.</x:v>
       </x:c>
       <x:c r="G22" s="33" t="str">
-        <x:v>The chosen audit level, native fields, match/error outputs, and ruleset/engine identity columns are understood and usable.</x:v>
+        <x:v>Business owner records approve/defer/reject decision with comments.</x:v>
       </x:c>
       <x:c r="H22" s="34"/>
       <x:c r="I22" s="33" t="str">
-        <x:v>Consumer sign-off notes.</x:v>
+        <x:v>Review notes and supporting evidence.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="87.94999694824219" customHeight="1">
-      <x:c r="A23" s="33" t="str">
-        <x:v>UAT-020</x:v>
-      </x:c>
-      <x:c r="B23" s="33" t="str">
-        <x:v>Downstream readiness</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="D23" s="33" t="str">
-        <x:v>Data Consumer</x:v>
-      </x:c>
-      <x:c r="E23" s="33" t="str">
-        <x:v>Assignment struct can be consumed by downstream Spark consumers</x:v>
-      </x:c>
-      <x:c r="F23" s="33" t="str">
-        <x:v>Consume the assign struct using downstream expected field access.</x:v>
-      </x:c>
-      <x:c r="G23" s="33" t="str">
-        <x:v>Assignments can be consumed without manual JSON parsing.</x:v>
-      </x:c>
-      <x:c r="H23" s="34"/>
-      <x:c r="I23" s="33" t="str">
-        <x:v>Parsed output screenshot.</x:v>
-      </x:c>
+      <x:c r="A23"/>
+      <x:c r="B23"/>
+      <x:c r="C23"/>
+      <x:c r="D23"/>
+      <x:c r="E23"/>
+      <x:c r="F23"/>
+      <x:c r="G23"/>
+      <x:c r="H23"/>
+      <x:c r="I23"/>
     </x:row>
     <x:row r="24" ht="87.94999694824219" customHeight="1">
-      <x:c r="A24" s="33" t="str">
-        <x:v>UAT-021</x:v>
-      </x:c>
-      <x:c r="B24" s="33" t="str">
-        <x:v>Exception handling</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="D24" s="33" t="str">
-        <x:v>UAT Tester</x:v>
-      </x:c>
-      <x:c r="E24" s="33" t="str">
-        <x:v>Runtime error handling is acceptable for business operations</x:v>
-      </x:c>
-      <x:c r="F24" s="33" t="str">
-        <x:v>Review behavior when fail_on_error is true and false using a controlled bad input scenario.</x:v>
-      </x:c>
-      <x:c r="G24" s="33" t="str">
-        <x:v>The team agrees which mode is appropriate for production and how errors will be monitored.</x:v>
-      </x:c>
-      <x:c r="H24" s="34"/>
-      <x:c r="I24" s="33" t="str">
-        <x:v>Decision notes.</x:v>
-      </x:c>
+      <x:c r="A24"/>
+      <x:c r="B24"/>
+      <x:c r="C24"/>
+      <x:c r="D24"/>
+      <x:c r="E24"/>
+      <x:c r="F24"/>
+      <x:c r="G24"/>
+      <x:c r="H24"/>
+      <x:c r="I24"/>
     </x:row>
     <x:row r="25" ht="87.94999694824219" customHeight="1">
-      <x:c r="A25" s="33" t="str">
-        <x:v>UAT-022</x:v>
-      </x:c>
-      <x:c r="B25" s="33" t="str">
-        <x:v>Documentation</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="D25" s="33" t="str">
-        <x:v>UAT Tester</x:v>
-      </x:c>
-      <x:c r="E25" s="33" t="str">
-        <x:v>Notebook instructions are clear enough for a new operator</x:v>
-      </x:c>
-      <x:c r="F25" s="33" t="str">
-        <x:v>Ask a tester who did not write the notebooks to run setup and publish in UAT.</x:v>
-      </x:c>
-      <x:c r="G25" s="33" t="str">
-        <x:v>Tester can complete the process using notebook instructions and parameters without engineering intervention.</x:v>
-      </x:c>
-      <x:c r="H25" s="34"/>
-      <x:c r="I25" s="33" t="str">
-        <x:v>Tester feedback.</x:v>
-      </x:c>
+      <x:c r="A25"/>
+      <x:c r="B25"/>
+      <x:c r="C25"/>
+      <x:c r="D25"/>
+      <x:c r="E25"/>
+      <x:c r="F25"/>
+      <x:c r="G25"/>
+      <x:c r="H25"/>
+      <x:c r="I25"/>
     </x:row>
     <x:row r="26" ht="87.94999694824219" customHeight="1">
-      <x:c r="A26" s="33" t="str">
-        <x:v>UAT-023</x:v>
-      </x:c>
-      <x:c r="B26" s="33" t="str">
-        <x:v>Sign-off</x:v>
-      </x:c>
-      <x:c r="C26" s="33" t="str">
-        <x:v>Critical</x:v>
-      </x:c>
-      <x:c r="D26" s="33" t="str">
-        <x:v>Business Owner</x:v>
-      </x:c>
-      <x:c r="E26" s="33" t="str">
-        <x:v>Business owner approves the published candidate version</x:v>
-      </x:c>
-      <x:c r="F26" s="33" t="str">
-        <x:v>Review validation output, UAT outputs, and open defects.</x:v>
-      </x:c>
-      <x:c r="G26" s="33" t="str">
-        <x:v>Business owner records approve/defer/reject decision with comments.</x:v>
-      </x:c>
-      <x:c r="H26" s="34"/>
-      <x:c r="I26" s="33" t="str">
-        <x:v>Sign-Off tab entry or approval reference.</x:v>
-      </x:c>
+      <x:c r="A26"/>
+      <x:c r="B26"/>
+      <x:c r="C26"/>
+      <x:c r="D26"/>
+      <x:c r="E26"/>
+      <x:c r="F26"/>
+      <x:c r="G26"/>
+      <x:c r="H26"/>
+      <x:c r="I26"/>
     </x:row>
     <x:row r="27" ht="87.94999694824219" customHeight="1">
-      <x:c r="A27" s="33" t="str">
-        <x:v>UAT-024</x:v>
-      </x:c>
-      <x:c r="B27" s="33" t="str">
-        <x:v>Sign-off</x:v>
-      </x:c>
-      <x:c r="C27" s="33" t="str">
-        <x:v>Critical</x:v>
-      </x:c>
-      <x:c r="D27" s="33" t="str">
-        <x:v>Release Manager</x:v>
-      </x:c>
-      <x:c r="E27" s="33" t="str">
-        <x:v>Release manager confirms deployment readiness</x:v>
-      </x:c>
-      <x:c r="F27" s="33" t="str">
-        <x:v>Review system test status, UAT status, defect disposition, and rollback/retirement plan.</x:v>
-      </x:c>
-      <x:c r="G27" s="33" t="str">
-        <x:v>Release manager signs off or records conditions for release.</x:v>
-      </x:c>
-      <x:c r="H27" s="34"/>
-      <x:c r="I27" s="33" t="str">
-        <x:v>Sign-Off tab entry or release approval link.</x:v>
-      </x:c>
+      <x:c r="A27"/>
+      <x:c r="B27"/>
+      <x:c r="C27"/>
+      <x:c r="D27"/>
+      <x:c r="E27"/>
+      <x:c r="F27"/>
+      <x:c r="G27"/>
+      <x:c r="H27"/>
+      <x:c r="I27"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -4554,7 +4371,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2cbbe2a12cd44b58"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c3cd6414ae540ea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4577,7 +4394,7 @@
   <x:sheetData>
     <x:row r="1" ht="18" customHeight="1">
       <x:c r="A1" s="7" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B1" s="8"/>
       <x:c r="C1" s="8"/>
@@ -4593,45 +4410,45 @@
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
       <x:c r="A3" s="3" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B3" s="3" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D3" s="3" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B3" s="3" t="s">
+      <x:c r="E3" s="3" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C3" s="3" t="s">
+      <x:c r="F3" s="3" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="D3" s="3" t="s">
+      <x:c r="G3" s="3" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="E3" s="3" t="s">
+      <x:c r="H3" s="3" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="F3" s="3" t="s">
+      <x:c r="I3" s="3" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="G3" s="3" t="s">
+      <x:c r="J3" s="3" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="H3" s="3" t="s">
+      <x:c r="K3" s="3" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="I3" s="3" t="s">
+      <x:c r="L3" s="3" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="J3" s="3" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="K3" s="3" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="L3" s="3" t="s">
-        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="51.95000076293945" customHeight="1">
       <x:c r="A4" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B4" s="2"/>
       <x:c r="C4" s="2"/>
@@ -4639,7 +4456,7 @@
       <x:c r="E4" s="2"/>
       <x:c r="F4" s="2"/>
       <x:c r="G4" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H4" s="2"/>
       <x:c r="I4" s="2"/>
@@ -4649,7 +4466,7 @@
     </x:row>
     <x:row r="5" ht="51.95000076293945" customHeight="1">
       <x:c r="A5" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B5" s="2"/>
       <x:c r="C5" s="2"/>
@@ -4657,7 +4474,7 @@
       <x:c r="E5" s="2"/>
       <x:c r="F5" s="2"/>
       <x:c r="G5" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H5" s="2"/>
       <x:c r="I5" s="2"/>
@@ -4667,7 +4484,7 @@
     </x:row>
     <x:row r="6" ht="51.95000076293945" customHeight="1">
       <x:c r="A6" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B6" s="2"/>
       <x:c r="C6" s="2"/>
@@ -4675,7 +4492,7 @@
       <x:c r="E6" s="2"/>
       <x:c r="F6" s="2"/>
       <x:c r="G6" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H6" s="2"/>
       <x:c r="I6" s="2"/>
@@ -4685,7 +4502,7 @@
     </x:row>
     <x:row r="7" ht="51.95000076293945" customHeight="1">
       <x:c r="A7" s="2" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B7" s="2"/>
       <x:c r="C7" s="2"/>
@@ -4693,7 +4510,7 @@
       <x:c r="E7" s="2"/>
       <x:c r="F7" s="2"/>
       <x:c r="G7" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H7" s="2"/>
       <x:c r="I7" s="2"/>
@@ -4703,7 +4520,7 @@
     </x:row>
     <x:row r="8" ht="51.95000076293945" customHeight="1">
       <x:c r="A8" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B8" s="2"/>
       <x:c r="C8" s="2"/>
@@ -4711,7 +4528,7 @@
       <x:c r="E8" s="2"/>
       <x:c r="F8" s="2"/>
       <x:c r="G8" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H8" s="2"/>
       <x:c r="I8" s="2"/>
@@ -4721,7 +4538,7 @@
     </x:row>
     <x:row r="9" ht="51.95000076293945" customHeight="1">
       <x:c r="A9" s="2" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B9" s="2"/>
       <x:c r="C9" s="2"/>
@@ -4729,7 +4546,7 @@
       <x:c r="E9" s="2"/>
       <x:c r="F9" s="2"/>
       <x:c r="G9" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H9" s="2"/>
       <x:c r="I9" s="2"/>
@@ -4739,7 +4556,7 @@
     </x:row>
     <x:row r="10" ht="51.95000076293945" customHeight="1">
       <x:c r="A10" s="2" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B10" s="2"/>
       <x:c r="C10" s="2"/>
@@ -4747,7 +4564,7 @@
       <x:c r="E10" s="2"/>
       <x:c r="F10" s="2"/>
       <x:c r="G10" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H10" s="2"/>
       <x:c r="I10" s="2"/>
@@ -4757,7 +4574,7 @@
     </x:row>
     <x:row r="11" ht="51.95000076293945" customHeight="1">
       <x:c r="A11" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B11" s="2"/>
       <x:c r="C11" s="2"/>
@@ -4765,7 +4582,7 @@
       <x:c r="E11" s="2"/>
       <x:c r="F11" s="2"/>
       <x:c r="G11" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H11" s="2"/>
       <x:c r="I11" s="2"/>
@@ -4775,7 +4592,7 @@
     </x:row>
     <x:row r="12" ht="51.95000076293945" customHeight="1">
       <x:c r="A12" s="2" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B12" s="2"/>
       <x:c r="C12" s="2"/>
@@ -4783,7 +4600,7 @@
       <x:c r="E12" s="2"/>
       <x:c r="F12" s="2"/>
       <x:c r="G12" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H12" s="2"/>
       <x:c r="I12" s="2"/>
@@ -4793,7 +4610,7 @@
     </x:row>
     <x:row r="13" ht="51.95000076293945" customHeight="1">
       <x:c r="A13" s="2" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B13" s="2"/>
       <x:c r="C13" s="2"/>
@@ -4801,7 +4618,7 @@
       <x:c r="E13" s="2"/>
       <x:c r="F13" s="2"/>
       <x:c r="G13" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H13" s="2"/>
       <x:c r="I13" s="2"/>
@@ -4811,7 +4628,7 @@
     </x:row>
     <x:row r="14" ht="51.95000076293945" customHeight="1">
       <x:c r="A14" s="2" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B14" s="2"/>
       <x:c r="C14" s="2"/>
@@ -4819,7 +4636,7 @@
       <x:c r="E14" s="2"/>
       <x:c r="F14" s="2"/>
       <x:c r="G14" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H14" s="2"/>
       <x:c r="I14" s="2"/>
@@ -4829,7 +4646,7 @@
     </x:row>
     <x:row r="15" ht="51.95000076293945" customHeight="1">
       <x:c r="A15" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B15" s="2"/>
       <x:c r="C15" s="2"/>
@@ -4837,7 +4654,7 @@
       <x:c r="E15" s="2"/>
       <x:c r="F15" s="2"/>
       <x:c r="G15" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H15" s="2"/>
       <x:c r="I15" s="2"/>
@@ -4847,7 +4664,7 @@
     </x:row>
     <x:row r="16" ht="51.95000076293945" customHeight="1">
       <x:c r="A16" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B16" s="2"/>
       <x:c r="C16" s="2"/>
@@ -4855,7 +4672,7 @@
       <x:c r="E16" s="2"/>
       <x:c r="F16" s="2"/>
       <x:c r="G16" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H16" s="2"/>
       <x:c r="I16" s="2"/>
@@ -4865,7 +4682,7 @@
     </x:row>
     <x:row r="17" ht="51.95000076293945" customHeight="1">
       <x:c r="A17" s="2" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B17" s="2"/>
       <x:c r="C17" s="2"/>
@@ -4873,7 +4690,7 @@
       <x:c r="E17" s="2"/>
       <x:c r="F17" s="2"/>
       <x:c r="G17" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H17" s="2"/>
       <x:c r="I17" s="2"/>
@@ -4883,7 +4700,7 @@
     </x:row>
     <x:row r="18" ht="51.95000076293945" customHeight="1">
       <x:c r="A18" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B18" s="2"/>
       <x:c r="C18" s="2"/>
@@ -4891,7 +4708,7 @@
       <x:c r="E18" s="2"/>
       <x:c r="F18" s="2"/>
       <x:c r="G18" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H18" s="2"/>
       <x:c r="I18" s="2"/>
@@ -4901,7 +4718,7 @@
     </x:row>
     <x:row r="19" ht="51.95000076293945" customHeight="1">
       <x:c r="A19" s="2" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B19" s="2"/>
       <x:c r="C19" s="2"/>
@@ -4909,7 +4726,7 @@
       <x:c r="E19" s="2"/>
       <x:c r="F19" s="2"/>
       <x:c r="G19" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H19" s="2"/>
       <x:c r="I19" s="2"/>
@@ -4919,7 +4736,7 @@
     </x:row>
     <x:row r="20" ht="51.95000076293945" customHeight="1">
       <x:c r="A20" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B20" s="2"/>
       <x:c r="C20" s="2"/>
@@ -4927,7 +4744,7 @@
       <x:c r="E20" s="2"/>
       <x:c r="F20" s="2"/>
       <x:c r="G20" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H20" s="2"/>
       <x:c r="I20" s="2"/>
@@ -4937,7 +4754,7 @@
     </x:row>
     <x:row r="21" ht="51.95000076293945" customHeight="1">
       <x:c r="A21" s="2" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B21" s="2"/>
       <x:c r="C21" s="2"/>
@@ -4945,7 +4762,7 @@
       <x:c r="E21" s="2"/>
       <x:c r="F21" s="2"/>
       <x:c r="G21" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H21" s="2"/>
       <x:c r="I21" s="2"/>
@@ -4955,7 +4772,7 @@
     </x:row>
     <x:row r="22" ht="51.95000076293945" customHeight="1">
       <x:c r="A22" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B22" s="2"/>
       <x:c r="C22" s="2"/>
@@ -4963,7 +4780,7 @@
       <x:c r="E22" s="2"/>
       <x:c r="F22" s="2"/>
       <x:c r="G22" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H22" s="2"/>
       <x:c r="I22" s="2"/>
@@ -4973,7 +4790,7 @@
     </x:row>
     <x:row r="23" ht="51.95000076293945" customHeight="1">
       <x:c r="A23" s="2" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B23" s="2"/>
       <x:c r="C23" s="2"/>
@@ -4981,7 +4798,7 @@
       <x:c r="E23" s="2"/>
       <x:c r="F23" s="2"/>
       <x:c r="G23" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H23" s="2"/>
       <x:c r="I23" s="2"/>
@@ -4991,7 +4808,7 @@
     </x:row>
     <x:row r="24" ht="51.95000076293945" customHeight="1">
       <x:c r="A24" s="2" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B24" s="2"/>
       <x:c r="C24" s="2"/>
@@ -4999,7 +4816,7 @@
       <x:c r="E24" s="2"/>
       <x:c r="F24" s="2"/>
       <x:c r="G24" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H24" s="2"/>
       <x:c r="I24" s="2"/>
@@ -5009,7 +4826,7 @@
     </x:row>
     <x:row r="25" ht="51.95000076293945" customHeight="1">
       <x:c r="A25" s="2" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B25" s="2"/>
       <x:c r="C25" s="2"/>
@@ -5017,7 +4834,7 @@
       <x:c r="E25" s="2"/>
       <x:c r="F25" s="2"/>
       <x:c r="G25" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H25" s="2"/>
       <x:c r="I25" s="2"/>
@@ -5027,7 +4844,7 @@
     </x:row>
     <x:row r="26" ht="51.95000076293945" customHeight="1">
       <x:c r="A26" s="2" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B26" s="2"/>
       <x:c r="C26" s="2"/>
@@ -5035,7 +4852,7 @@
       <x:c r="E26" s="2"/>
       <x:c r="F26" s="2"/>
       <x:c r="G26" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H26" s="2"/>
       <x:c r="I26" s="2"/>
@@ -5045,7 +4862,7 @@
     </x:row>
     <x:row r="27" ht="51.95000076293945" customHeight="1">
       <x:c r="A27" s="2" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B27" s="2"/>
       <x:c r="C27" s="2"/>
@@ -5053,7 +4870,7 @@
       <x:c r="E27" s="2"/>
       <x:c r="F27" s="2"/>
       <x:c r="G27" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H27" s="2"/>
       <x:c r="I27" s="2"/>
@@ -5063,7 +4880,7 @@
     </x:row>
     <x:row r="28" ht="51.95000076293945" customHeight="1">
       <x:c r="A28" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B28" s="2"/>
       <x:c r="C28" s="2"/>
@@ -5071,7 +4888,7 @@
       <x:c r="E28" s="2"/>
       <x:c r="F28" s="2"/>
       <x:c r="G28" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H28" s="2"/>
       <x:c r="I28" s="2"/>
@@ -5081,7 +4898,7 @@
     </x:row>
     <x:row r="29" ht="51.95000076293945" customHeight="1">
       <x:c r="A29" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B29" s="2"/>
       <x:c r="C29" s="2"/>
@@ -5089,7 +4906,7 @@
       <x:c r="E29" s="2"/>
       <x:c r="F29" s="2"/>
       <x:c r="G29" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H29" s="2"/>
       <x:c r="I29" s="2"/>
@@ -5099,7 +4916,7 @@
     </x:row>
     <x:row r="30" ht="51.95000076293945" customHeight="1">
       <x:c r="A30" s="2" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B30" s="2"/>
       <x:c r="C30" s="2"/>
@@ -5107,7 +4924,7 @@
       <x:c r="E30" s="2"/>
       <x:c r="F30" s="2"/>
       <x:c r="G30" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H30" s="2"/>
       <x:c r="I30" s="2"/>
@@ -5117,7 +4934,7 @@
     </x:row>
     <x:row r="31" ht="51.95000076293945" customHeight="1">
       <x:c r="A31" s="2" t="s">
-        <x:v>64</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B31" s="2"/>
       <x:c r="C31" s="2"/>
@@ -5125,7 +4942,7 @@
       <x:c r="E31" s="2"/>
       <x:c r="F31" s="2"/>
       <x:c r="G31" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H31" s="2"/>
       <x:c r="I31" s="2"/>
@@ -5135,7 +4952,7 @@
     </x:row>
     <x:row r="32" ht="51.95000076293945" customHeight="1">
       <x:c r="A32" s="2" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B32" s="2"/>
       <x:c r="C32" s="2"/>
@@ -5143,7 +4960,7 @@
       <x:c r="E32" s="2"/>
       <x:c r="F32" s="2"/>
       <x:c r="G32" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H32" s="2"/>
       <x:c r="I32" s="2"/>
@@ -5153,7 +4970,7 @@
     </x:row>
     <x:row r="33" ht="51.95000076293945" customHeight="1">
       <x:c r="A33" s="2" t="s">
-        <x:v>66</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B33" s="2"/>
       <x:c r="C33" s="2"/>
@@ -5161,7 +4978,7 @@
       <x:c r="E33" s="2"/>
       <x:c r="F33" s="2"/>
       <x:c r="G33" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H33" s="2"/>
       <x:c r="I33" s="2"/>
@@ -5171,7 +4988,7 @@
     </x:row>
     <x:row r="34" ht="51.95000076293945" customHeight="1">
       <x:c r="A34" s="2" t="s">
-        <x:v>67</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B34" s="2"/>
       <x:c r="C34" s="2"/>
@@ -5179,7 +4996,7 @@
       <x:c r="E34" s="2"/>
       <x:c r="F34" s="2"/>
       <x:c r="G34" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H34" s="2"/>
       <x:c r="I34" s="2"/>
@@ -5189,7 +5006,7 @@
     </x:row>
     <x:row r="35" ht="51.95000076293945" customHeight="1">
       <x:c r="A35" s="2" t="s">
-        <x:v>68</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B35" s="2"/>
       <x:c r="C35" s="2"/>
@@ -5197,7 +5014,7 @@
       <x:c r="E35" s="2"/>
       <x:c r="F35" s="2"/>
       <x:c r="G35" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H35" s="2"/>
       <x:c r="I35" s="2"/>
@@ -5207,7 +5024,7 @@
     </x:row>
     <x:row r="36" ht="51.95000076293945" customHeight="1">
       <x:c r="A36" s="2" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B36" s="2"/>
       <x:c r="C36" s="2"/>
@@ -5215,7 +5032,7 @@
       <x:c r="E36" s="2"/>
       <x:c r="F36" s="2"/>
       <x:c r="G36" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H36" s="2"/>
       <x:c r="I36" s="2"/>
@@ -5225,7 +5042,7 @@
     </x:row>
     <x:row r="37" ht="51.95000076293945" customHeight="1">
       <x:c r="A37" s="2" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B37" s="2"/>
       <x:c r="C37" s="2"/>
@@ -5233,7 +5050,7 @@
       <x:c r="E37" s="2"/>
       <x:c r="F37" s="2"/>
       <x:c r="G37" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H37" s="2"/>
       <x:c r="I37" s="2"/>
@@ -5243,7 +5060,7 @@
     </x:row>
     <x:row r="38" ht="51.95000076293945" customHeight="1">
       <x:c r="A38" s="2" t="s">
-        <x:v>71</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B38" s="2"/>
       <x:c r="C38" s="2"/>
@@ -5251,7 +5068,7 @@
       <x:c r="E38" s="2"/>
       <x:c r="F38" s="2"/>
       <x:c r="G38" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H38" s="2"/>
       <x:c r="I38" s="2"/>
@@ -5261,7 +5078,7 @@
     </x:row>
     <x:row r="39" ht="51.95000076293945" customHeight="1">
       <x:c r="A39" s="2" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B39" s="2"/>
       <x:c r="C39" s="2"/>
@@ -5269,7 +5086,7 @@
       <x:c r="E39" s="2"/>
       <x:c r="F39" s="2"/>
       <x:c r="G39" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H39" s="2"/>
       <x:c r="I39" s="2"/>
@@ -5279,7 +5096,7 @@
     </x:row>
     <x:row r="40" ht="51.95000076293945" customHeight="1">
       <x:c r="A40" s="2" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B40" s="2"/>
       <x:c r="C40" s="2"/>
@@ -5287,7 +5104,7 @@
       <x:c r="E40" s="2"/>
       <x:c r="F40" s="2"/>
       <x:c r="G40" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H40" s="2"/>
       <x:c r="I40" s="2"/>
@@ -5297,7 +5114,7 @@
     </x:row>
     <x:row r="41" ht="51.95000076293945" customHeight="1">
       <x:c r="A41" s="2" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B41" s="2"/>
       <x:c r="C41" s="2"/>
@@ -5305,7 +5122,7 @@
       <x:c r="E41" s="2"/>
       <x:c r="F41" s="2"/>
       <x:c r="G41" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H41" s="2"/>
       <x:c r="I41" s="2"/>
@@ -5315,7 +5132,7 @@
     </x:row>
     <x:row r="42" ht="51.95000076293945" customHeight="1">
       <x:c r="A42" s="2" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B42" s="2"/>
       <x:c r="C42" s="2"/>
@@ -5323,7 +5140,7 @@
       <x:c r="E42" s="2"/>
       <x:c r="F42" s="2"/>
       <x:c r="G42" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H42" s="2"/>
       <x:c r="I42" s="2"/>
@@ -5333,7 +5150,7 @@
     </x:row>
     <x:row r="43" ht="51.95000076293945" customHeight="1">
       <x:c r="A43" s="2" t="s">
-        <x:v>76</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B43" s="2"/>
       <x:c r="C43" s="2"/>
@@ -5341,7 +5158,7 @@
       <x:c r="E43" s="2"/>
       <x:c r="F43" s="2"/>
       <x:c r="G43" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H43" s="2"/>
       <x:c r="I43" s="2"/>
@@ -5351,7 +5168,7 @@
     </x:row>
     <x:row r="44" ht="51.95000076293945" customHeight="1">
       <x:c r="A44" s="2" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B44" s="2"/>
       <x:c r="C44" s="2"/>
@@ -5359,7 +5176,7 @@
       <x:c r="E44" s="2"/>
       <x:c r="F44" s="2"/>
       <x:c r="G44" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H44" s="2"/>
       <x:c r="I44" s="2"/>
@@ -5369,7 +5186,7 @@
     </x:row>
     <x:row r="45" ht="51.95000076293945" customHeight="1">
       <x:c r="A45" s="2" t="s">
-        <x:v>78</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B45" s="2"/>
       <x:c r="C45" s="2"/>
@@ -5377,7 +5194,7 @@
       <x:c r="E45" s="2"/>
       <x:c r="F45" s="2"/>
       <x:c r="G45" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H45" s="2"/>
       <x:c r="I45" s="2"/>
@@ -5387,7 +5204,7 @@
     </x:row>
     <x:row r="46" ht="51.95000076293945" customHeight="1">
       <x:c r="A46" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B46" s="2"/>
       <x:c r="C46" s="2"/>
@@ -5395,7 +5212,7 @@
       <x:c r="E46" s="2"/>
       <x:c r="F46" s="2"/>
       <x:c r="G46" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H46" s="2"/>
       <x:c r="I46" s="2"/>
@@ -5405,7 +5222,7 @@
     </x:row>
     <x:row r="47" ht="51.95000076293945" customHeight="1">
       <x:c r="A47" s="2" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B47" s="2"/>
       <x:c r="C47" s="2"/>
@@ -5413,7 +5230,7 @@
       <x:c r="E47" s="2"/>
       <x:c r="F47" s="2"/>
       <x:c r="G47" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H47" s="2"/>
       <x:c r="I47" s="2"/>
@@ -5423,7 +5240,7 @@
     </x:row>
     <x:row r="48" ht="51.95000076293945" customHeight="1">
       <x:c r="A48" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B48" s="2"/>
       <x:c r="C48" s="2"/>
@@ -5431,7 +5248,7 @@
       <x:c r="E48" s="2"/>
       <x:c r="F48" s="2"/>
       <x:c r="G48" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H48" s="2"/>
       <x:c r="I48" s="2"/>
@@ -5441,7 +5258,7 @@
     </x:row>
     <x:row r="49" ht="51.95000076293945" customHeight="1">
       <x:c r="A49" s="2" t="s">
-        <x:v>82</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B49" s="2"/>
       <x:c r="C49" s="2"/>
@@ -5449,7 +5266,7 @@
       <x:c r="E49" s="2"/>
       <x:c r="F49" s="2"/>
       <x:c r="G49" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H49" s="2"/>
       <x:c r="I49" s="2"/>
@@ -5459,7 +5276,7 @@
     </x:row>
     <x:row r="50" ht="51.95000076293945" customHeight="1">
       <x:c r="A50" s="2" t="s">
-        <x:v>83</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B50" s="2"/>
       <x:c r="C50" s="2"/>
@@ -5467,7 +5284,7 @@
       <x:c r="E50" s="2"/>
       <x:c r="F50" s="2"/>
       <x:c r="G50" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H50" s="2"/>
       <x:c r="I50" s="2"/>
@@ -5477,7 +5294,7 @@
     </x:row>
     <x:row r="51" ht="51.95000076293945" customHeight="1">
       <x:c r="A51" s="2" t="s">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B51" s="2"/>
       <x:c r="C51" s="2"/>
@@ -5485,7 +5302,7 @@
       <x:c r="E51" s="2"/>
       <x:c r="F51" s="2"/>
       <x:c r="G51" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H51" s="2"/>
       <x:c r="I51" s="2"/>
@@ -5495,7 +5312,7 @@
     </x:row>
     <x:row r="52" ht="51.95000076293945" customHeight="1">
       <x:c r="A52" s="2" t="s">
-        <x:v>85</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B52" s="2"/>
       <x:c r="C52" s="2"/>
@@ -5503,7 +5320,7 @@
       <x:c r="E52" s="2"/>
       <x:c r="F52" s="2"/>
       <x:c r="G52" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H52" s="2"/>
       <x:c r="I52" s="2"/>
@@ -5513,7 +5330,7 @@
     </x:row>
     <x:row r="53" ht="51.95000076293945" customHeight="1">
       <x:c r="A53" s="2" t="s">
-        <x:v>86</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B53" s="2"/>
       <x:c r="C53" s="2"/>
@@ -5521,7 +5338,7 @@
       <x:c r="E53" s="2"/>
       <x:c r="F53" s="2"/>
       <x:c r="G53" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H53" s="2"/>
       <x:c r="I53" s="2"/>
@@ -5531,7 +5348,7 @@
     </x:row>
     <x:row r="54" ht="51.95000076293945" customHeight="1">
       <x:c r="A54" s="2" t="s">
-        <x:v>87</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B54" s="2"/>
       <x:c r="C54" s="2"/>
@@ -5539,7 +5356,7 @@
       <x:c r="E54" s="2"/>
       <x:c r="F54" s="2"/>
       <x:c r="G54" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H54" s="2"/>
       <x:c r="I54" s="2"/>
@@ -5549,7 +5366,7 @@
     </x:row>
     <x:row r="55" ht="51.95000076293945" customHeight="1">
       <x:c r="A55" s="2" t="s">
-        <x:v>88</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B55" s="2"/>
       <x:c r="C55" s="2"/>
@@ -5557,7 +5374,7 @@
       <x:c r="E55" s="2"/>
       <x:c r="F55" s="2"/>
       <x:c r="G55" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H55" s="2"/>
       <x:c r="I55" s="2"/>
@@ -5567,7 +5384,7 @@
     </x:row>
     <x:row r="56" ht="51.95000076293945" customHeight="1">
       <x:c r="A56" s="2" t="s">
-        <x:v>89</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B56" s="2"/>
       <x:c r="C56" s="2"/>
@@ -5575,7 +5392,7 @@
       <x:c r="E56" s="2"/>
       <x:c r="F56" s="2"/>
       <x:c r="G56" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H56" s="2"/>
       <x:c r="I56" s="2"/>
@@ -5585,7 +5402,7 @@
     </x:row>
     <x:row r="57" ht="51.95000076293945" customHeight="1">
       <x:c r="A57" s="2" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B57" s="2"/>
       <x:c r="C57" s="2"/>
@@ -5593,7 +5410,7 @@
       <x:c r="E57" s="2"/>
       <x:c r="F57" s="2"/>
       <x:c r="G57" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H57" s="2"/>
       <x:c r="I57" s="2"/>
@@ -5603,7 +5420,7 @@
     </x:row>
     <x:row r="58" ht="51.95000076293945" customHeight="1">
       <x:c r="A58" s="2" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B58" s="2"/>
       <x:c r="C58" s="2"/>
@@ -5611,7 +5428,7 @@
       <x:c r="E58" s="2"/>
       <x:c r="F58" s="2"/>
       <x:c r="G58" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H58" s="2"/>
       <x:c r="I58" s="2"/>
@@ -5621,7 +5438,7 @@
     </x:row>
     <x:row r="59" ht="51.95000076293945" customHeight="1">
       <x:c r="A59" s="2" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B59" s="2"/>
       <x:c r="C59" s="2"/>
@@ -5629,7 +5446,7 @@
       <x:c r="E59" s="2"/>
       <x:c r="F59" s="2"/>
       <x:c r="G59" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H59" s="2"/>
       <x:c r="I59" s="2"/>
@@ -5639,7 +5456,7 @@
     </x:row>
     <x:row r="60" ht="51.95000076293945" customHeight="1">
       <x:c r="A60" s="2" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B60" s="2"/>
       <x:c r="C60" s="2"/>
@@ -5647,7 +5464,7 @@
       <x:c r="E60" s="2"/>
       <x:c r="F60" s="2"/>
       <x:c r="G60" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H60" s="2"/>
       <x:c r="I60" s="2"/>
@@ -5657,7 +5474,7 @@
     </x:row>
     <x:row r="61" ht="51.95000076293945" customHeight="1">
       <x:c r="A61" s="2" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B61" s="2"/>
       <x:c r="C61" s="2"/>
@@ -5665,7 +5482,7 @@
       <x:c r="E61" s="2"/>
       <x:c r="F61" s="2"/>
       <x:c r="G61" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H61" s="2"/>
       <x:c r="I61" s="2"/>
@@ -5675,7 +5492,7 @@
     </x:row>
     <x:row r="62" ht="51.95000076293945" customHeight="1">
       <x:c r="A62" s="2" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B62" s="2"/>
       <x:c r="C62" s="2"/>
@@ -5683,7 +5500,7 @@
       <x:c r="E62" s="2"/>
       <x:c r="F62" s="2"/>
       <x:c r="G62" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H62" s="2"/>
       <x:c r="I62" s="2"/>
@@ -5693,7 +5510,7 @@
     </x:row>
     <x:row r="63" ht="51.95000076293945" customHeight="1">
       <x:c r="A63" s="2" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B63" s="2"/>
       <x:c r="C63" s="2"/>
@@ -5701,7 +5518,7 @@
       <x:c r="E63" s="2"/>
       <x:c r="F63" s="2"/>
       <x:c r="G63" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H63" s="2"/>
       <x:c r="I63" s="2"/>
@@ -5711,7 +5528,7 @@
     </x:row>
     <x:row r="64" ht="51.95000076293945" customHeight="1">
       <x:c r="A64" s="2" t="s">
-        <x:v>97</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B64" s="2"/>
       <x:c r="C64" s="2"/>
@@ -5719,7 +5536,7 @@
       <x:c r="E64" s="2"/>
       <x:c r="F64" s="2"/>
       <x:c r="G64" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H64" s="2"/>
       <x:c r="I64" s="2"/>
@@ -5729,7 +5546,7 @@
     </x:row>
     <x:row r="65" ht="51.95000076293945" customHeight="1">
       <x:c r="A65" s="2" t="s">
-        <x:v>98</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B65" s="2"/>
       <x:c r="C65" s="2"/>
@@ -5737,7 +5554,7 @@
       <x:c r="E65" s="2"/>
       <x:c r="F65" s="2"/>
       <x:c r="G65" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H65" s="2"/>
       <x:c r="I65" s="2"/>
@@ -5747,7 +5564,7 @@
     </x:row>
     <x:row r="66" ht="51.95000076293945" customHeight="1">
       <x:c r="A66" s="2" t="s">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B66" s="2"/>
       <x:c r="C66" s="2"/>
@@ -5755,7 +5572,7 @@
       <x:c r="E66" s="2"/>
       <x:c r="F66" s="2"/>
       <x:c r="G66" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H66" s="2"/>
       <x:c r="I66" s="2"/>
@@ -5765,7 +5582,7 @@
     </x:row>
     <x:row r="67" ht="51.95000076293945" customHeight="1">
       <x:c r="A67" s="2" t="s">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B67" s="2"/>
       <x:c r="C67" s="2"/>
@@ -5773,7 +5590,7 @@
       <x:c r="E67" s="2"/>
       <x:c r="F67" s="2"/>
       <x:c r="G67" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H67" s="2"/>
       <x:c r="I67" s="2"/>
@@ -5783,7 +5600,7 @@
     </x:row>
     <x:row r="68" ht="51.95000076293945" customHeight="1">
       <x:c r="A68" s="2" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B68" s="2"/>
       <x:c r="C68" s="2"/>
@@ -5791,7 +5608,7 @@
       <x:c r="E68" s="2"/>
       <x:c r="F68" s="2"/>
       <x:c r="G68" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H68" s="2"/>
       <x:c r="I68" s="2"/>
@@ -5801,7 +5618,7 @@
     </x:row>
     <x:row r="69" ht="51.95000076293945" customHeight="1">
       <x:c r="A69" s="2" t="s">
-        <x:v>102</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B69" s="2"/>
       <x:c r="C69" s="2"/>
@@ -5809,7 +5626,7 @@
       <x:c r="E69" s="2"/>
       <x:c r="F69" s="2"/>
       <x:c r="G69" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H69" s="2"/>
       <x:c r="I69" s="2"/>
@@ -5819,7 +5636,7 @@
     </x:row>
     <x:row r="70" ht="51.95000076293945" customHeight="1">
       <x:c r="A70" s="2" t="s">
-        <x:v>103</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B70" s="2"/>
       <x:c r="C70" s="2"/>
@@ -5827,7 +5644,7 @@
       <x:c r="E70" s="2"/>
       <x:c r="F70" s="2"/>
       <x:c r="G70" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H70" s="2"/>
       <x:c r="I70" s="2"/>
@@ -5837,7 +5654,7 @@
     </x:row>
     <x:row r="71" ht="51.95000076293945" customHeight="1">
       <x:c r="A71" s="2" t="s">
-        <x:v>104</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B71" s="2"/>
       <x:c r="C71" s="2"/>
@@ -5845,7 +5662,7 @@
       <x:c r="E71" s="2"/>
       <x:c r="F71" s="2"/>
       <x:c r="G71" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H71" s="2"/>
       <x:c r="I71" s="2"/>
@@ -5855,7 +5672,7 @@
     </x:row>
     <x:row r="72" ht="51.95000076293945" customHeight="1">
       <x:c r="A72" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B72" s="2"/>
       <x:c r="C72" s="2"/>
@@ -5863,7 +5680,7 @@
       <x:c r="E72" s="2"/>
       <x:c r="F72" s="2"/>
       <x:c r="G72" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H72" s="2"/>
       <x:c r="I72" s="2"/>
@@ -5873,7 +5690,7 @@
     </x:row>
     <x:row r="73" ht="51.95000076293945" customHeight="1">
       <x:c r="A73" s="2" t="s">
-        <x:v>106</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B73" s="2"/>
       <x:c r="C73" s="2"/>
@@ -5881,7 +5698,7 @@
       <x:c r="E73" s="2"/>
       <x:c r="F73" s="2"/>
       <x:c r="G73" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H73" s="2"/>
       <x:c r="I73" s="2"/>
@@ -5891,7 +5708,7 @@
     </x:row>
     <x:row r="74" ht="51.95000076293945" customHeight="1">
       <x:c r="A74" s="2" t="s">
-        <x:v>107</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B74" s="2"/>
       <x:c r="C74" s="2"/>
@@ -5899,7 +5716,7 @@
       <x:c r="E74" s="2"/>
       <x:c r="F74" s="2"/>
       <x:c r="G74" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H74" s="2"/>
       <x:c r="I74" s="2"/>
@@ -5909,7 +5726,7 @@
     </x:row>
     <x:row r="75" ht="51.95000076293945" customHeight="1">
       <x:c r="A75" s="2" t="s">
-        <x:v>108</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B75" s="2"/>
       <x:c r="C75" s="2"/>
@@ -5917,7 +5734,7 @@
       <x:c r="E75" s="2"/>
       <x:c r="F75" s="2"/>
       <x:c r="G75" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H75" s="2"/>
       <x:c r="I75" s="2"/>
@@ -5927,7 +5744,7 @@
     </x:row>
     <x:row r="76" ht="51.95000076293945" customHeight="1">
       <x:c r="A76" s="2" t="s">
-        <x:v>109</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B76" s="2"/>
       <x:c r="C76" s="2"/>
@@ -5935,7 +5752,7 @@
       <x:c r="E76" s="2"/>
       <x:c r="F76" s="2"/>
       <x:c r="G76" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H76" s="2"/>
       <x:c r="I76" s="2"/>
@@ -5945,7 +5762,7 @@
     </x:row>
     <x:row r="77" ht="51.95000076293945" customHeight="1">
       <x:c r="A77" s="2" t="s">
-        <x:v>110</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B77" s="2"/>
       <x:c r="C77" s="2"/>
@@ -5953,7 +5770,7 @@
       <x:c r="E77" s="2"/>
       <x:c r="F77" s="2"/>
       <x:c r="G77" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H77" s="2"/>
       <x:c r="I77" s="2"/>
@@ -5963,7 +5780,7 @@
     </x:row>
     <x:row r="78" ht="51.95000076293945" customHeight="1">
       <x:c r="A78" s="2" t="s">
-        <x:v>111</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B78" s="2"/>
       <x:c r="C78" s="2"/>
@@ -5971,7 +5788,7 @@
       <x:c r="E78" s="2"/>
       <x:c r="F78" s="2"/>
       <x:c r="G78" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H78" s="2"/>
       <x:c r="I78" s="2"/>
@@ -5981,7 +5798,7 @@
     </x:row>
     <x:row r="79" ht="51.95000076293945" customHeight="1">
       <x:c r="A79" s="2" t="s">
-        <x:v>112</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B79" s="2"/>
       <x:c r="C79" s="2"/>
@@ -5989,7 +5806,7 @@
       <x:c r="E79" s="2"/>
       <x:c r="F79" s="2"/>
       <x:c r="G79" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H79" s="2"/>
       <x:c r="I79" s="2"/>
@@ -5999,7 +5816,7 @@
     </x:row>
     <x:row r="80" ht="51.95000076293945" customHeight="1">
       <x:c r="A80" s="2" t="s">
-        <x:v>113</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B80" s="2"/>
       <x:c r="C80" s="2"/>
@@ -6007,7 +5824,7 @@
       <x:c r="E80" s="2"/>
       <x:c r="F80" s="2"/>
       <x:c r="G80" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H80" s="2"/>
       <x:c r="I80" s="2"/>
@@ -6017,7 +5834,7 @@
     </x:row>
     <x:row r="81" ht="51.95000076293945" customHeight="1">
       <x:c r="A81" s="2" t="s">
-        <x:v>114</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B81" s="2"/>
       <x:c r="C81" s="2"/>
@@ -6025,7 +5842,7 @@
       <x:c r="E81" s="2"/>
       <x:c r="F81" s="2"/>
       <x:c r="G81" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H81" s="2"/>
       <x:c r="I81" s="2"/>
@@ -6035,7 +5852,7 @@
     </x:row>
     <x:row r="82" ht="51.95000076293945" customHeight="1">
       <x:c r="A82" s="2" t="s">
-        <x:v>115</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B82" s="2"/>
       <x:c r="C82" s="2"/>
@@ -6043,7 +5860,7 @@
       <x:c r="E82" s="2"/>
       <x:c r="F82" s="2"/>
       <x:c r="G82" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H82" s="2"/>
       <x:c r="I82" s="2"/>
@@ -6053,7 +5870,7 @@
     </x:row>
     <x:row r="83" ht="51.95000076293945" customHeight="1">
       <x:c r="A83" s="2" t="s">
-        <x:v>116</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B83" s="2"/>
       <x:c r="C83" s="2"/>
@@ -6061,7 +5878,7 @@
       <x:c r="E83" s="2"/>
       <x:c r="F83" s="2"/>
       <x:c r="G83" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H83" s="2"/>
       <x:c r="I83" s="2"/>
@@ -6071,7 +5888,7 @@
     </x:row>
     <x:row r="84" ht="51.95000076293945" customHeight="1">
       <x:c r="A84" s="2" t="s">
-        <x:v>117</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B84" s="2"/>
       <x:c r="C84" s="2"/>
@@ -6079,7 +5896,7 @@
       <x:c r="E84" s="2"/>
       <x:c r="F84" s="2"/>
       <x:c r="G84" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H84" s="2"/>
       <x:c r="I84" s="2"/>
@@ -6089,7 +5906,7 @@
     </x:row>
     <x:row r="85" ht="51.95000076293945" customHeight="1">
       <x:c r="A85" s="2" t="s">
-        <x:v>118</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B85" s="2"/>
       <x:c r="C85" s="2"/>
@@ -6097,7 +5914,7 @@
       <x:c r="E85" s="2"/>
       <x:c r="F85" s="2"/>
       <x:c r="G85" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H85" s="2"/>
       <x:c r="I85" s="2"/>
@@ -6107,7 +5924,7 @@
     </x:row>
     <x:row r="86" ht="51.95000076293945" customHeight="1">
       <x:c r="A86" s="2" t="s">
-        <x:v>119</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B86" s="2"/>
       <x:c r="C86" s="2"/>
@@ -6115,7 +5932,7 @@
       <x:c r="E86" s="2"/>
       <x:c r="F86" s="2"/>
       <x:c r="G86" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H86" s="2"/>
       <x:c r="I86" s="2"/>
@@ -6125,7 +5942,7 @@
     </x:row>
     <x:row r="87" ht="51.95000076293945" customHeight="1">
       <x:c r="A87" s="2" t="s">
-        <x:v>120</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B87" s="2"/>
       <x:c r="C87" s="2"/>
@@ -6133,7 +5950,7 @@
       <x:c r="E87" s="2"/>
       <x:c r="F87" s="2"/>
       <x:c r="G87" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H87" s="2"/>
       <x:c r="I87" s="2"/>
@@ -6143,7 +5960,7 @@
     </x:row>
     <x:row r="88" ht="51.95000076293945" customHeight="1">
       <x:c r="A88" s="2" t="s">
-        <x:v>121</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B88" s="2"/>
       <x:c r="C88" s="2"/>
@@ -6151,7 +5968,7 @@
       <x:c r="E88" s="2"/>
       <x:c r="F88" s="2"/>
       <x:c r="G88" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H88" s="2"/>
       <x:c r="I88" s="2"/>
@@ -6161,7 +5978,7 @@
     </x:row>
     <x:row r="89" ht="51.95000076293945" customHeight="1">
       <x:c r="A89" s="2" t="s">
-        <x:v>122</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B89" s="2"/>
       <x:c r="C89" s="2"/>
@@ -6169,7 +5986,7 @@
       <x:c r="E89" s="2"/>
       <x:c r="F89" s="2"/>
       <x:c r="G89" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H89" s="2"/>
       <x:c r="I89" s="2"/>
@@ -6179,7 +5996,7 @@
     </x:row>
     <x:row r="90" ht="51.95000076293945" customHeight="1">
       <x:c r="A90" s="2" t="s">
-        <x:v>123</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B90" s="2"/>
       <x:c r="C90" s="2"/>
@@ -6187,7 +6004,7 @@
       <x:c r="E90" s="2"/>
       <x:c r="F90" s="2"/>
       <x:c r="G90" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H90" s="2"/>
       <x:c r="I90" s="2"/>
@@ -6197,7 +6014,7 @@
     </x:row>
     <x:row r="91" ht="51.95000076293945" customHeight="1">
       <x:c r="A91" s="2" t="s">
-        <x:v>124</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B91" s="2"/>
       <x:c r="C91" s="2"/>
@@ -6205,7 +6022,7 @@
       <x:c r="E91" s="2"/>
       <x:c r="F91" s="2"/>
       <x:c r="G91" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H91" s="2"/>
       <x:c r="I91" s="2"/>
@@ -6215,7 +6032,7 @@
     </x:row>
     <x:row r="92" ht="51.95000076293945" customHeight="1">
       <x:c r="A92" s="2" t="s">
-        <x:v>125</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B92" s="2"/>
       <x:c r="C92" s="2"/>
@@ -6223,7 +6040,7 @@
       <x:c r="E92" s="2"/>
       <x:c r="F92" s="2"/>
       <x:c r="G92" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H92" s="2"/>
       <x:c r="I92" s="2"/>
@@ -6233,7 +6050,7 @@
     </x:row>
     <x:row r="93" ht="51.95000076293945" customHeight="1">
       <x:c r="A93" s="2" t="s">
-        <x:v>126</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B93" s="2"/>
       <x:c r="C93" s="2"/>
@@ -6241,7 +6058,7 @@
       <x:c r="E93" s="2"/>
       <x:c r="F93" s="2"/>
       <x:c r="G93" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H93" s="2"/>
       <x:c r="I93" s="2"/>
@@ -6251,7 +6068,7 @@
     </x:row>
     <x:row r="94" ht="51.95000076293945" customHeight="1">
       <x:c r="A94" s="2" t="s">
-        <x:v>127</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B94" s="2"/>
       <x:c r="C94" s="2"/>
@@ -6259,7 +6076,7 @@
       <x:c r="E94" s="2"/>
       <x:c r="F94" s="2"/>
       <x:c r="G94" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H94" s="2"/>
       <x:c r="I94" s="2"/>
@@ -6269,7 +6086,7 @@
     </x:row>
     <x:row r="95" ht="51.95000076293945" customHeight="1">
       <x:c r="A95" s="2" t="s">
-        <x:v>128</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B95" s="2"/>
       <x:c r="C95" s="2"/>
@@ -6277,7 +6094,7 @@
       <x:c r="E95" s="2"/>
       <x:c r="F95" s="2"/>
       <x:c r="G95" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H95" s="2"/>
       <x:c r="I95" s="2"/>
@@ -6287,7 +6104,7 @@
     </x:row>
     <x:row r="96" ht="51.95000076293945" customHeight="1">
       <x:c r="A96" s="2" t="s">
-        <x:v>129</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B96" s="2"/>
       <x:c r="C96" s="2"/>
@@ -6295,7 +6112,7 @@
       <x:c r="E96" s="2"/>
       <x:c r="F96" s="2"/>
       <x:c r="G96" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H96" s="2"/>
       <x:c r="I96" s="2"/>
@@ -6305,7 +6122,7 @@
     </x:row>
     <x:row r="97" ht="51.95000076293945" customHeight="1">
       <x:c r="A97" s="2" t="s">
-        <x:v>130</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B97" s="2"/>
       <x:c r="C97" s="2"/>
@@ -6313,7 +6130,7 @@
       <x:c r="E97" s="2"/>
       <x:c r="F97" s="2"/>
       <x:c r="G97" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H97" s="2"/>
       <x:c r="I97" s="2"/>
@@ -6323,7 +6140,7 @@
     </x:row>
     <x:row r="98" ht="51.95000076293945" customHeight="1">
       <x:c r="A98" s="2" t="s">
-        <x:v>131</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B98" s="2"/>
       <x:c r="C98" s="2"/>
@@ -6331,7 +6148,7 @@
       <x:c r="E98" s="2"/>
       <x:c r="F98" s="2"/>
       <x:c r="G98" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H98" s="2"/>
       <x:c r="I98" s="2"/>
@@ -6341,7 +6158,7 @@
     </x:row>
     <x:row r="99" ht="51.95000076293945" customHeight="1">
       <x:c r="A99" s="2" t="s">
-        <x:v>132</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B99" s="2"/>
       <x:c r="C99" s="2"/>
@@ -6349,7 +6166,7 @@
       <x:c r="E99" s="2"/>
       <x:c r="F99" s="2"/>
       <x:c r="G99" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H99" s="2"/>
       <x:c r="I99" s="2"/>
@@ -6359,7 +6176,7 @@
     </x:row>
     <x:row r="100" ht="51.95000076293945" customHeight="1">
       <x:c r="A100" s="2" t="s">
-        <x:v>133</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B100" s="2"/>
       <x:c r="C100" s="2"/>
@@ -6367,7 +6184,7 @@
       <x:c r="E100" s="2"/>
       <x:c r="F100" s="2"/>
       <x:c r="G100" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H100" s="2"/>
       <x:c r="I100" s="2"/>
@@ -6377,7 +6194,7 @@
     </x:row>
     <x:row r="101" ht="51.95000076293945" customHeight="1">
       <x:c r="A101" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B101" s="2"/>
       <x:c r="C101" s="2"/>
@@ -6385,7 +6202,7 @@
       <x:c r="E101" s="2"/>
       <x:c r="F101" s="2"/>
       <x:c r="G101" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H101" s="2"/>
       <x:c r="I101" s="2"/>
@@ -6395,7 +6212,7 @@
     </x:row>
     <x:row r="102" ht="51.95000076293945" customHeight="1">
       <x:c r="A102" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B102" s="2"/>
       <x:c r="C102" s="2"/>
@@ -6403,7 +6220,7 @@
       <x:c r="E102" s="2"/>
       <x:c r="F102" s="2"/>
       <x:c r="G102" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H102" s="2"/>
       <x:c r="I102" s="2"/>
@@ -6413,7 +6230,7 @@
     </x:row>
     <x:row r="103" ht="51.95000076293945" customHeight="1">
       <x:c r="A103" s="2" t="s">
-        <x:v>136</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B103" s="2"/>
       <x:c r="C103" s="2"/>
@@ -6421,7 +6238,7 @@
       <x:c r="E103" s="2"/>
       <x:c r="F103" s="2"/>
       <x:c r="G103" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H103" s="2"/>
       <x:c r="I103" s="2"/>
@@ -6431,7 +6248,7 @@
     </x:row>
     <x:row r="104" ht="51.95000076293945" customHeight="1">
       <x:c r="A104" s="2" t="s">
-        <x:v>137</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B104" s="2"/>
       <x:c r="C104" s="2"/>
@@ -6439,7 +6256,7 @@
       <x:c r="E104" s="2"/>
       <x:c r="F104" s="2"/>
       <x:c r="G104" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H104" s="2"/>
       <x:c r="I104" s="2"/>
@@ -6449,7 +6266,7 @@
     </x:row>
     <x:row r="105" ht="51.95000076293945" customHeight="1">
       <x:c r="A105" s="2" t="s">
-        <x:v>138</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B105" s="2"/>
       <x:c r="C105" s="2"/>
@@ -6457,7 +6274,7 @@
       <x:c r="E105" s="2"/>
       <x:c r="F105" s="2"/>
       <x:c r="G105" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H105" s="2"/>
       <x:c r="I105" s="2"/>
@@ -6467,7 +6284,7 @@
     </x:row>
     <x:row r="106" ht="51.95000076293945" customHeight="1">
       <x:c r="A106" s="2" t="s">
-        <x:v>139</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B106" s="2"/>
       <x:c r="C106" s="2"/>
@@ -6475,7 +6292,7 @@
       <x:c r="E106" s="2"/>
       <x:c r="F106" s="2"/>
       <x:c r="G106" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H106" s="2"/>
       <x:c r="I106" s="2"/>
@@ -6485,7 +6302,7 @@
     </x:row>
     <x:row r="107" ht="51.95000076293945" customHeight="1">
       <x:c r="A107" s="2" t="s">
-        <x:v>140</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B107" s="2"/>
       <x:c r="C107" s="2"/>
@@ -6493,7 +6310,7 @@
       <x:c r="E107" s="2"/>
       <x:c r="F107" s="2"/>
       <x:c r="G107" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H107" s="2"/>
       <x:c r="I107" s="2"/>
@@ -6503,7 +6320,7 @@
     </x:row>
     <x:row r="108" ht="51.95000076293945" customHeight="1">
       <x:c r="A108" s="2" t="s">
-        <x:v>141</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B108" s="2"/>
       <x:c r="C108" s="2"/>
@@ -6511,7 +6328,7 @@
       <x:c r="E108" s="2"/>
       <x:c r="F108" s="2"/>
       <x:c r="G108" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H108" s="2"/>
       <x:c r="I108" s="2"/>
@@ -6521,7 +6338,7 @@
     </x:row>
     <x:row r="109" ht="51.95000076293945" customHeight="1">
       <x:c r="A109" s="2" t="s">
-        <x:v>142</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B109" s="2"/>
       <x:c r="C109" s="2"/>
@@ -6529,7 +6346,7 @@
       <x:c r="E109" s="2"/>
       <x:c r="F109" s="2"/>
       <x:c r="G109" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H109" s="2"/>
       <x:c r="I109" s="2"/>
@@ -6539,7 +6356,7 @@
     </x:row>
     <x:row r="110" ht="51.95000076293945" customHeight="1">
       <x:c r="A110" s="2" t="s">
-        <x:v>143</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B110" s="2"/>
       <x:c r="C110" s="2"/>
@@ -6547,7 +6364,7 @@
       <x:c r="E110" s="2"/>
       <x:c r="F110" s="2"/>
       <x:c r="G110" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H110" s="2"/>
       <x:c r="I110" s="2"/>
@@ -6557,7 +6374,7 @@
     </x:row>
     <x:row r="111" ht="51.95000076293945" customHeight="1">
       <x:c r="A111" s="2" t="s">
-        <x:v>144</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B111" s="2"/>
       <x:c r="C111" s="2"/>
@@ -6565,7 +6382,7 @@
       <x:c r="E111" s="2"/>
       <x:c r="F111" s="2"/>
       <x:c r="G111" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H111" s="2"/>
       <x:c r="I111" s="2"/>
@@ -6575,7 +6392,7 @@
     </x:row>
     <x:row r="112" ht="51.95000076293945" customHeight="1">
       <x:c r="A112" s="2" t="s">
-        <x:v>145</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B112" s="2"/>
       <x:c r="C112" s="2"/>
@@ -6583,7 +6400,7 @@
       <x:c r="E112" s="2"/>
       <x:c r="F112" s="2"/>
       <x:c r="G112" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H112" s="2"/>
       <x:c r="I112" s="2"/>
@@ -6593,7 +6410,7 @@
     </x:row>
     <x:row r="113" ht="51.95000076293945" customHeight="1">
       <x:c r="A113" s="2" t="s">
-        <x:v>146</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B113" s="2"/>
       <x:c r="C113" s="2"/>
@@ -6601,7 +6418,7 @@
       <x:c r="E113" s="2"/>
       <x:c r="F113" s="2"/>
       <x:c r="G113" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H113" s="2"/>
       <x:c r="I113" s="2"/>
@@ -6611,7 +6428,7 @@
     </x:row>
     <x:row r="114" ht="51.95000076293945" customHeight="1">
       <x:c r="A114" s="2" t="s">
-        <x:v>147</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B114" s="2"/>
       <x:c r="C114" s="2"/>
@@ -6619,7 +6436,7 @@
       <x:c r="E114" s="2"/>
       <x:c r="F114" s="2"/>
       <x:c r="G114" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H114" s="2"/>
       <x:c r="I114" s="2"/>
@@ -6629,7 +6446,7 @@
     </x:row>
     <x:row r="115" ht="51.95000076293945" customHeight="1">
       <x:c r="A115" s="2" t="s">
-        <x:v>148</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B115" s="2"/>
       <x:c r="C115" s="2"/>
@@ -6637,7 +6454,7 @@
       <x:c r="E115" s="2"/>
       <x:c r="F115" s="2"/>
       <x:c r="G115" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H115" s="2"/>
       <x:c r="I115" s="2"/>
@@ -6647,7 +6464,7 @@
     </x:row>
     <x:row r="116" ht="51.95000076293945" customHeight="1">
       <x:c r="A116" s="2" t="s">
-        <x:v>149</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B116" s="2"/>
       <x:c r="C116" s="2"/>
@@ -6655,7 +6472,7 @@
       <x:c r="E116" s="2"/>
       <x:c r="F116" s="2"/>
       <x:c r="G116" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H116" s="2"/>
       <x:c r="I116" s="2"/>
@@ -6665,7 +6482,7 @@
     </x:row>
     <x:row r="117" ht="51.95000076293945" customHeight="1">
       <x:c r="A117" s="2" t="s">
-        <x:v>150</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B117" s="2"/>
       <x:c r="C117" s="2"/>
@@ -6673,7 +6490,7 @@
       <x:c r="E117" s="2"/>
       <x:c r="F117" s="2"/>
       <x:c r="G117" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H117" s="2"/>
       <x:c r="I117" s="2"/>
@@ -6683,7 +6500,7 @@
     </x:row>
     <x:row r="118" ht="51.95000076293945" customHeight="1">
       <x:c r="A118" s="2" t="s">
-        <x:v>151</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="B118" s="2"/>
       <x:c r="C118" s="2"/>
@@ -6691,7 +6508,7 @@
       <x:c r="E118" s="2"/>
       <x:c r="F118" s="2"/>
       <x:c r="G118" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H118" s="2"/>
       <x:c r="I118" s="2"/>
@@ -6701,7 +6518,7 @@
     </x:row>
     <x:row r="119" ht="51.95000076293945" customHeight="1">
       <x:c r="A119" s="2" t="s">
-        <x:v>152</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B119" s="2"/>
       <x:c r="C119" s="2"/>
@@ -6709,7 +6526,7 @@
       <x:c r="E119" s="2"/>
       <x:c r="F119" s="2"/>
       <x:c r="G119" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H119" s="2"/>
       <x:c r="I119" s="2"/>
@@ -6719,7 +6536,7 @@
     </x:row>
     <x:row r="120" ht="51.95000076293945" customHeight="1">
       <x:c r="A120" s="2" t="s">
-        <x:v>153</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B120" s="2"/>
       <x:c r="C120" s="2"/>
@@ -6727,7 +6544,7 @@
       <x:c r="E120" s="2"/>
       <x:c r="F120" s="2"/>
       <x:c r="G120" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H120" s="2"/>
       <x:c r="I120" s="2"/>
@@ -6737,7 +6554,7 @@
     </x:row>
     <x:row r="121" ht="51.95000076293945" customHeight="1">
       <x:c r="A121" s="2" t="s">
-        <x:v>154</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="B121" s="2"/>
       <x:c r="C121" s="2"/>
@@ -6745,7 +6562,7 @@
       <x:c r="E121" s="2"/>
       <x:c r="F121" s="2"/>
       <x:c r="G121" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H121" s="2"/>
       <x:c r="I121" s="2"/>
@@ -6755,7 +6572,7 @@
     </x:row>
     <x:row r="122" ht="51.95000076293945" customHeight="1">
       <x:c r="A122" s="2" t="s">
-        <x:v>155</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B122" s="2"/>
       <x:c r="C122" s="2"/>
@@ -6763,7 +6580,7 @@
       <x:c r="E122" s="2"/>
       <x:c r="F122" s="2"/>
       <x:c r="G122" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H122" s="2"/>
       <x:c r="I122" s="2"/>
@@ -6773,7 +6590,7 @@
     </x:row>
     <x:row r="123" ht="51.95000076293945" customHeight="1">
       <x:c r="A123" s="2" t="s">
-        <x:v>156</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B123" s="2"/>
       <x:c r="C123" s="2"/>
@@ -6781,7 +6598,7 @@
       <x:c r="E123" s="2"/>
       <x:c r="F123" s="2"/>
       <x:c r="G123" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H123" s="2"/>
       <x:c r="I123" s="2"/>
@@ -6791,7 +6608,7 @@
     </x:row>
     <x:row r="124" ht="51.95000076293945" customHeight="1">
       <x:c r="A124" s="2" t="s">
-        <x:v>157</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B124" s="2"/>
       <x:c r="C124" s="2"/>
@@ -6799,7 +6616,7 @@
       <x:c r="E124" s="2"/>
       <x:c r="F124" s="2"/>
       <x:c r="G124" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H124" s="2"/>
       <x:c r="I124" s="2"/>
@@ -6809,7 +6626,7 @@
     </x:row>
     <x:row r="125" ht="51.95000076293945" customHeight="1">
       <x:c r="A125" s="2" t="s">
-        <x:v>158</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B125" s="2"/>
       <x:c r="C125" s="2"/>
@@ -6817,7 +6634,7 @@
       <x:c r="E125" s="2"/>
       <x:c r="F125" s="2"/>
       <x:c r="G125" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H125" s="2"/>
       <x:c r="I125" s="2"/>
@@ -6827,7 +6644,7 @@
     </x:row>
     <x:row r="126" ht="51.95000076293945" customHeight="1">
       <x:c r="A126" s="2" t="s">
-        <x:v>159</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B126" s="2"/>
       <x:c r="C126" s="2"/>
@@ -6835,7 +6652,7 @@
       <x:c r="E126" s="2"/>
       <x:c r="F126" s="2"/>
       <x:c r="G126" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H126" s="2"/>
       <x:c r="I126" s="2"/>
@@ -6845,7 +6662,7 @@
     </x:row>
     <x:row r="127" ht="51.95000076293945" customHeight="1">
       <x:c r="A127" s="2" t="s">
-        <x:v>160</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B127" s="2"/>
       <x:c r="C127" s="2"/>
@@ -6853,7 +6670,7 @@
       <x:c r="E127" s="2"/>
       <x:c r="F127" s="2"/>
       <x:c r="G127" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H127" s="2"/>
       <x:c r="I127" s="2"/>
@@ -6863,7 +6680,7 @@
     </x:row>
     <x:row r="128" ht="51.95000076293945" customHeight="1">
       <x:c r="A128" s="2" t="s">
-        <x:v>161</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B128" s="2"/>
       <x:c r="C128" s="2"/>
@@ -6871,7 +6688,7 @@
       <x:c r="E128" s="2"/>
       <x:c r="F128" s="2"/>
       <x:c r="G128" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H128" s="2"/>
       <x:c r="I128" s="2"/>
@@ -6881,7 +6698,7 @@
     </x:row>
     <x:row r="129" ht="51.95000076293945" customHeight="1">
       <x:c r="A129" s="2" t="s">
-        <x:v>162</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B129" s="2"/>
       <x:c r="C129" s="2"/>
@@ -6889,7 +6706,7 @@
       <x:c r="E129" s="2"/>
       <x:c r="F129" s="2"/>
       <x:c r="G129" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H129" s="2"/>
       <x:c r="I129" s="2"/>
@@ -6899,7 +6716,7 @@
     </x:row>
     <x:row r="130" ht="51.95000076293945" customHeight="1">
       <x:c r="A130" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="B130" s="2"/>
       <x:c r="C130" s="2"/>
@@ -6907,7 +6724,7 @@
       <x:c r="E130" s="2"/>
       <x:c r="F130" s="2"/>
       <x:c r="G130" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H130" s="2"/>
       <x:c r="I130" s="2"/>
@@ -6917,7 +6734,7 @@
     </x:row>
     <x:row r="131" ht="51.95000076293945" customHeight="1">
       <x:c r="A131" s="2" t="s">
-        <x:v>164</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B131" s="2"/>
       <x:c r="C131" s="2"/>
@@ -6925,7 +6742,7 @@
       <x:c r="E131" s="2"/>
       <x:c r="F131" s="2"/>
       <x:c r="G131" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H131" s="2"/>
       <x:c r="I131" s="2"/>
@@ -6935,7 +6752,7 @@
     </x:row>
     <x:row r="132" ht="51.95000076293945" customHeight="1">
       <x:c r="A132" s="2" t="s">
-        <x:v>165</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B132" s="2"/>
       <x:c r="C132" s="2"/>
@@ -6943,7 +6760,7 @@
       <x:c r="E132" s="2"/>
       <x:c r="F132" s="2"/>
       <x:c r="G132" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H132" s="2"/>
       <x:c r="I132" s="2"/>
@@ -6953,7 +6770,7 @@
     </x:row>
     <x:row r="133" ht="51.95000076293945" customHeight="1">
       <x:c r="A133" s="2" t="s">
-        <x:v>166</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B133" s="2"/>
       <x:c r="C133" s="2"/>
@@ -6961,7 +6778,7 @@
       <x:c r="E133" s="2"/>
       <x:c r="F133" s="2"/>
       <x:c r="G133" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H133" s="2"/>
       <x:c r="I133" s="2"/>
@@ -6971,7 +6788,7 @@
     </x:row>
     <x:row r="134" ht="51.95000076293945" customHeight="1">
       <x:c r="A134" s="2" t="s">
-        <x:v>167</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B134" s="2"/>
       <x:c r="C134" s="2"/>
@@ -6979,7 +6796,7 @@
       <x:c r="E134" s="2"/>
       <x:c r="F134" s="2"/>
       <x:c r="G134" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H134" s="2"/>
       <x:c r="I134" s="2"/>
@@ -6989,7 +6806,7 @@
     </x:row>
     <x:row r="135" ht="51.95000076293945" customHeight="1">
       <x:c r="A135" s="2" t="s">
-        <x:v>168</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B135" s="2"/>
       <x:c r="C135" s="2"/>
@@ -6997,7 +6814,7 @@
       <x:c r="E135" s="2"/>
       <x:c r="F135" s="2"/>
       <x:c r="G135" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H135" s="2"/>
       <x:c r="I135" s="2"/>
@@ -7007,7 +6824,7 @@
     </x:row>
     <x:row r="136" ht="51.95000076293945" customHeight="1">
       <x:c r="A136" s="2" t="s">
-        <x:v>169</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B136" s="2"/>
       <x:c r="C136" s="2"/>
@@ -7015,7 +6832,7 @@
       <x:c r="E136" s="2"/>
       <x:c r="F136" s="2"/>
       <x:c r="G136" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H136" s="2"/>
       <x:c r="I136" s="2"/>
@@ -7025,7 +6842,7 @@
     </x:row>
     <x:row r="137" ht="51.95000076293945" customHeight="1">
       <x:c r="A137" s="2" t="s">
-        <x:v>170</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B137" s="2"/>
       <x:c r="C137" s="2"/>
@@ -7033,7 +6850,7 @@
       <x:c r="E137" s="2"/>
       <x:c r="F137" s="2"/>
       <x:c r="G137" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H137" s="2"/>
       <x:c r="I137" s="2"/>
@@ -7043,7 +6860,7 @@
     </x:row>
     <x:row r="138" ht="51.95000076293945" customHeight="1">
       <x:c r="A138" s="2" t="s">
-        <x:v>171</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B138" s="2"/>
       <x:c r="C138" s="2"/>
@@ -7051,7 +6868,7 @@
       <x:c r="E138" s="2"/>
       <x:c r="F138" s="2"/>
       <x:c r="G138" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H138" s="2"/>
       <x:c r="I138" s="2"/>
@@ -7061,7 +6878,7 @@
     </x:row>
     <x:row r="139" ht="51.95000076293945" customHeight="1">
       <x:c r="A139" s="2" t="s">
-        <x:v>172</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="B139" s="2"/>
       <x:c r="C139" s="2"/>
@@ -7069,7 +6886,7 @@
       <x:c r="E139" s="2"/>
       <x:c r="F139" s="2"/>
       <x:c r="G139" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H139" s="2"/>
       <x:c r="I139" s="2"/>
@@ -7079,7 +6896,7 @@
     </x:row>
     <x:row r="140" ht="51.95000076293945" customHeight="1">
       <x:c r="A140" s="2" t="s">
-        <x:v>173</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="B140" s="2"/>
       <x:c r="C140" s="2"/>
@@ -7087,7 +6904,7 @@
       <x:c r="E140" s="2"/>
       <x:c r="F140" s="2"/>
       <x:c r="G140" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H140" s="2"/>
       <x:c r="I140" s="2"/>
@@ -7097,7 +6914,7 @@
     </x:row>
     <x:row r="141" ht="51.95000076293945" customHeight="1">
       <x:c r="A141" s="2" t="s">
-        <x:v>174</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B141" s="2"/>
       <x:c r="C141" s="2"/>
@@ -7105,7 +6922,7 @@
       <x:c r="E141" s="2"/>
       <x:c r="F141" s="2"/>
       <x:c r="G141" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H141" s="2"/>
       <x:c r="I141" s="2"/>
@@ -7115,7 +6932,7 @@
     </x:row>
     <x:row r="142" ht="51.95000076293945" customHeight="1">
       <x:c r="A142" s="2" t="s">
-        <x:v>175</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B142" s="2"/>
       <x:c r="C142" s="2"/>
@@ -7123,7 +6940,7 @@
       <x:c r="E142" s="2"/>
       <x:c r="F142" s="2"/>
       <x:c r="G142" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H142" s="2"/>
       <x:c r="I142" s="2"/>
@@ -7133,7 +6950,7 @@
     </x:row>
     <x:row r="143" ht="51.95000076293945" customHeight="1">
       <x:c r="A143" s="2" t="s">
-        <x:v>176</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="B143" s="2"/>
       <x:c r="C143" s="2"/>
@@ -7141,7 +6958,7 @@
       <x:c r="E143" s="2"/>
       <x:c r="F143" s="2"/>
       <x:c r="G143" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H143" s="2"/>
       <x:c r="I143" s="2"/>
@@ -7151,7 +6968,7 @@
     </x:row>
     <x:row r="144" ht="51.95000076293945" customHeight="1">
       <x:c r="A144" s="2" t="s">
-        <x:v>177</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B144" s="2"/>
       <x:c r="C144" s="2"/>
@@ -7159,7 +6976,7 @@
       <x:c r="E144" s="2"/>
       <x:c r="F144" s="2"/>
       <x:c r="G144" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H144" s="2"/>
       <x:c r="I144" s="2"/>
@@ -7169,7 +6986,7 @@
     </x:row>
     <x:row r="145" ht="51.95000076293945" customHeight="1">
       <x:c r="A145" s="2" t="s">
-        <x:v>178</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="B145" s="2"/>
       <x:c r="C145" s="2"/>
@@ -7177,7 +6994,7 @@
       <x:c r="E145" s="2"/>
       <x:c r="F145" s="2"/>
       <x:c r="G145" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H145" s="2"/>
       <x:c r="I145" s="2"/>
@@ -7187,7 +7004,7 @@
     </x:row>
     <x:row r="146" ht="51.95000076293945" customHeight="1">
       <x:c r="A146" s="2" t="s">
-        <x:v>179</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B146" s="2"/>
       <x:c r="C146" s="2"/>
@@ -7195,7 +7012,7 @@
       <x:c r="E146" s="2"/>
       <x:c r="F146" s="2"/>
       <x:c r="G146" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H146" s="2"/>
       <x:c r="I146" s="2"/>
@@ -7205,7 +7022,7 @@
     </x:row>
     <x:row r="147" ht="51.95000076293945" customHeight="1">
       <x:c r="A147" s="2" t="s">
-        <x:v>180</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="B147" s="2"/>
       <x:c r="C147" s="2"/>
@@ -7213,7 +7030,7 @@
       <x:c r="E147" s="2"/>
       <x:c r="F147" s="2"/>
       <x:c r="G147" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H147" s="2"/>
       <x:c r="I147" s="2"/>
@@ -7223,7 +7040,7 @@
     </x:row>
     <x:row r="148" ht="51.95000076293945" customHeight="1">
       <x:c r="A148" s="2" t="s">
-        <x:v>181</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B148" s="2"/>
       <x:c r="C148" s="2"/>
@@ -7231,7 +7048,7 @@
       <x:c r="E148" s="2"/>
       <x:c r="F148" s="2"/>
       <x:c r="G148" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H148" s="2"/>
       <x:c r="I148" s="2"/>
@@ -7241,7 +7058,7 @@
     </x:row>
     <x:row r="149" ht="51.95000076293945" customHeight="1">
       <x:c r="A149" s="2" t="s">
-        <x:v>182</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B149" s="2"/>
       <x:c r="C149" s="2"/>
@@ -7249,7 +7066,7 @@
       <x:c r="E149" s="2"/>
       <x:c r="F149" s="2"/>
       <x:c r="G149" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H149" s="2"/>
       <x:c r="I149" s="2"/>
@@ -7259,7 +7076,7 @@
     </x:row>
     <x:row r="150" ht="51.95000076293945" customHeight="1">
       <x:c r="A150" s="2" t="s">
-        <x:v>183</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B150" s="2"/>
       <x:c r="C150" s="2"/>
@@ -7267,7 +7084,7 @@
       <x:c r="E150" s="2"/>
       <x:c r="F150" s="2"/>
       <x:c r="G150" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H150" s="2"/>
       <x:c r="I150" s="2"/>
@@ -7277,7 +7094,7 @@
     </x:row>
     <x:row r="151" ht="51.95000076293945" customHeight="1">
       <x:c r="A151" s="2" t="s">
-        <x:v>184</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B151" s="2"/>
       <x:c r="C151" s="2"/>
@@ -7285,7 +7102,7 @@
       <x:c r="E151" s="2"/>
       <x:c r="F151" s="2"/>
       <x:c r="G151" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H151" s="2"/>
       <x:c r="I151" s="2"/>
@@ -7295,7 +7112,7 @@
     </x:row>
     <x:row r="152" ht="51.95000076293945" customHeight="1">
       <x:c r="A152" s="2" t="s">
-        <x:v>185</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B152" s="2"/>
       <x:c r="C152" s="2"/>
@@ -7303,7 +7120,7 @@
       <x:c r="E152" s="2"/>
       <x:c r="F152" s="2"/>
       <x:c r="G152" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H152" s="2"/>
       <x:c r="I152" s="2"/>
@@ -7313,7 +7130,7 @@
     </x:row>
     <x:row r="153" ht="51.95000076293945" customHeight="1">
       <x:c r="A153" s="2" t="s">
-        <x:v>186</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="B153" s="2"/>
       <x:c r="C153" s="2"/>
@@ -7321,7 +7138,7 @@
       <x:c r="E153" s="2"/>
       <x:c r="F153" s="2"/>
       <x:c r="G153" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H153" s="2"/>
       <x:c r="I153" s="2"/>
@@ -7331,7 +7148,7 @@
     </x:row>
     <x:row r="154" ht="51.95000076293945" customHeight="1">
       <x:c r="A154" s="2" t="s">
-        <x:v>187</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B154" s="2"/>
       <x:c r="C154" s="2"/>
@@ -7339,7 +7156,7 @@
       <x:c r="E154" s="2"/>
       <x:c r="F154" s="2"/>
       <x:c r="G154" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H154" s="2"/>
       <x:c r="I154" s="2"/>
@@ -7349,7 +7166,7 @@
     </x:row>
     <x:row r="155" ht="51.95000076293945" customHeight="1">
       <x:c r="A155" s="2" t="s">
-        <x:v>188</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="B155" s="2"/>
       <x:c r="C155" s="2"/>
@@ -7357,7 +7174,7 @@
       <x:c r="E155" s="2"/>
       <x:c r="F155" s="2"/>
       <x:c r="G155" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H155" s="2"/>
       <x:c r="I155" s="2"/>
@@ -7367,7 +7184,7 @@
     </x:row>
     <x:row r="156" ht="51.95000076293945" customHeight="1">
       <x:c r="A156" s="2" t="s">
-        <x:v>189</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="B156" s="2"/>
       <x:c r="C156" s="2"/>
@@ -7375,7 +7192,7 @@
       <x:c r="E156" s="2"/>
       <x:c r="F156" s="2"/>
       <x:c r="G156" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H156" s="2"/>
       <x:c r="I156" s="2"/>
@@ -7385,7 +7202,7 @@
     </x:row>
     <x:row r="157" ht="51.95000076293945" customHeight="1">
       <x:c r="A157" s="2" t="s">
-        <x:v>190</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B157" s="2"/>
       <x:c r="C157" s="2"/>
@@ -7393,7 +7210,7 @@
       <x:c r="E157" s="2"/>
       <x:c r="F157" s="2"/>
       <x:c r="G157" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H157" s="2"/>
       <x:c r="I157" s="2"/>
@@ -7403,7 +7220,7 @@
     </x:row>
     <x:row r="158" ht="51.95000076293945" customHeight="1">
       <x:c r="A158" s="2" t="s">
-        <x:v>191</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B158" s="2"/>
       <x:c r="C158" s="2"/>
@@ -7411,7 +7228,7 @@
       <x:c r="E158" s="2"/>
       <x:c r="F158" s="2"/>
       <x:c r="G158" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H158" s="2"/>
       <x:c r="I158" s="2"/>
@@ -7421,7 +7238,7 @@
     </x:row>
     <x:row r="159" ht="51.95000076293945" customHeight="1">
       <x:c r="A159" s="2" t="s">
-        <x:v>192</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="B159" s="2"/>
       <x:c r="C159" s="2"/>
@@ -7429,7 +7246,7 @@
       <x:c r="E159" s="2"/>
       <x:c r="F159" s="2"/>
       <x:c r="G159" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H159" s="2"/>
       <x:c r="I159" s="2"/>
@@ -7439,7 +7256,7 @@
     </x:row>
     <x:row r="160" ht="51.95000076293945" customHeight="1">
       <x:c r="A160" s="2" t="s">
-        <x:v>193</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B160" s="2"/>
       <x:c r="C160" s="2"/>
@@ -7447,7 +7264,7 @@
       <x:c r="E160" s="2"/>
       <x:c r="F160" s="2"/>
       <x:c r="G160" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H160" s="2"/>
       <x:c r="I160" s="2"/>
@@ -7457,7 +7274,7 @@
     </x:row>
     <x:row r="161" ht="51.95000076293945" customHeight="1">
       <x:c r="A161" s="2" t="s">
-        <x:v>194</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="B161" s="2"/>
       <x:c r="C161" s="2"/>
@@ -7465,7 +7282,7 @@
       <x:c r="E161" s="2"/>
       <x:c r="F161" s="2"/>
       <x:c r="G161" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H161" s="2"/>
       <x:c r="I161" s="2"/>
@@ -7475,7 +7292,7 @@
     </x:row>
     <x:row r="162" ht="51.95000076293945" customHeight="1">
       <x:c r="A162" s="2" t="s">
-        <x:v>195</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B162" s="2"/>
       <x:c r="C162" s="2"/>
@@ -7483,7 +7300,7 @@
       <x:c r="E162" s="2"/>
       <x:c r="F162" s="2"/>
       <x:c r="G162" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H162" s="2"/>
       <x:c r="I162" s="2"/>
@@ -7493,7 +7310,7 @@
     </x:row>
     <x:row r="163" ht="51.95000076293945" customHeight="1">
       <x:c r="A163" s="2" t="s">
-        <x:v>196</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B163" s="2"/>
       <x:c r="C163" s="2"/>
@@ -7501,7 +7318,7 @@
       <x:c r="E163" s="2"/>
       <x:c r="F163" s="2"/>
       <x:c r="G163" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H163" s="2"/>
       <x:c r="I163" s="2"/>
@@ -7511,7 +7328,7 @@
     </x:row>
     <x:row r="164" ht="51.95000076293945" customHeight="1">
       <x:c r="A164" s="2" t="s">
-        <x:v>197</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B164" s="2"/>
       <x:c r="C164" s="2"/>
@@ -7519,7 +7336,7 @@
       <x:c r="E164" s="2"/>
       <x:c r="F164" s="2"/>
       <x:c r="G164" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H164" s="2"/>
       <x:c r="I164" s="2"/>
@@ -7529,7 +7346,7 @@
     </x:row>
     <x:row r="165" ht="51.95000076293945" customHeight="1">
       <x:c r="A165" s="2" t="s">
-        <x:v>198</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B165" s="2"/>
       <x:c r="C165" s="2"/>
@@ -7537,7 +7354,7 @@
       <x:c r="E165" s="2"/>
       <x:c r="F165" s="2"/>
       <x:c r="G165" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H165" s="2"/>
       <x:c r="I165" s="2"/>
@@ -7547,7 +7364,7 @@
     </x:row>
     <x:row r="166" ht="51.95000076293945" customHeight="1">
       <x:c r="A166" s="2" t="s">
-        <x:v>199</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B166" s="2"/>
       <x:c r="C166" s="2"/>
@@ -7555,7 +7372,7 @@
       <x:c r="E166" s="2"/>
       <x:c r="F166" s="2"/>
       <x:c r="G166" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H166" s="2"/>
       <x:c r="I166" s="2"/>
@@ -7565,7 +7382,7 @@
     </x:row>
     <x:row r="167" ht="51.95000076293945" customHeight="1">
       <x:c r="A167" s="2" t="s">
-        <x:v>200</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B167" s="2"/>
       <x:c r="C167" s="2"/>
@@ -7573,7 +7390,7 @@
       <x:c r="E167" s="2"/>
       <x:c r="F167" s="2"/>
       <x:c r="G167" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H167" s="2"/>
       <x:c r="I167" s="2"/>
@@ -7583,7 +7400,7 @@
     </x:row>
     <x:row r="168" ht="51.95000076293945" customHeight="1">
       <x:c r="A168" s="2" t="s">
-        <x:v>201</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B168" s="2"/>
       <x:c r="C168" s="2"/>
@@ -7591,7 +7408,7 @@
       <x:c r="E168" s="2"/>
       <x:c r="F168" s="2"/>
       <x:c r="G168" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H168" s="2"/>
       <x:c r="I168" s="2"/>
@@ -7601,7 +7418,7 @@
     </x:row>
     <x:row r="169" ht="51.95000076293945" customHeight="1">
       <x:c r="A169" s="2" t="s">
-        <x:v>202</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="B169" s="2"/>
       <x:c r="C169" s="2"/>
@@ -7609,7 +7426,7 @@
       <x:c r="E169" s="2"/>
       <x:c r="F169" s="2"/>
       <x:c r="G169" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H169" s="2"/>
       <x:c r="I169" s="2"/>
@@ -7619,7 +7436,7 @@
     </x:row>
     <x:row r="170" ht="51.95000076293945" customHeight="1">
       <x:c r="A170" s="2" t="s">
-        <x:v>203</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B170" s="2"/>
       <x:c r="C170" s="2"/>
@@ -7627,7 +7444,7 @@
       <x:c r="E170" s="2"/>
       <x:c r="F170" s="2"/>
       <x:c r="G170" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H170" s="2"/>
       <x:c r="I170" s="2"/>
@@ -7637,7 +7454,7 @@
     </x:row>
     <x:row r="171" ht="51.95000076293945" customHeight="1">
       <x:c r="A171" s="2" t="s">
-        <x:v>204</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B171" s="2"/>
       <x:c r="C171" s="2"/>
@@ -7645,7 +7462,7 @@
       <x:c r="E171" s="2"/>
       <x:c r="F171" s="2"/>
       <x:c r="G171" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H171" s="2"/>
       <x:c r="I171" s="2"/>
@@ -7655,7 +7472,7 @@
     </x:row>
     <x:row r="172" ht="51.95000076293945" customHeight="1">
       <x:c r="A172" s="2" t="s">
-        <x:v>205</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="B172" s="2"/>
       <x:c r="C172" s="2"/>
@@ -7663,7 +7480,7 @@
       <x:c r="E172" s="2"/>
       <x:c r="F172" s="2"/>
       <x:c r="G172" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H172" s="2"/>
       <x:c r="I172" s="2"/>
@@ -7673,7 +7490,7 @@
     </x:row>
     <x:row r="173" ht="51.95000076293945" customHeight="1">
       <x:c r="A173" s="2" t="s">
-        <x:v>206</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B173" s="2"/>
       <x:c r="C173" s="2"/>
@@ -7681,7 +7498,7 @@
       <x:c r="E173" s="2"/>
       <x:c r="F173" s="2"/>
       <x:c r="G173" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H173" s="2"/>
       <x:c r="I173" s="2"/>
@@ -7691,7 +7508,7 @@
     </x:row>
     <x:row r="174" ht="51.95000076293945" customHeight="1">
       <x:c r="A174" s="2" t="s">
-        <x:v>207</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B174" s="2"/>
       <x:c r="C174" s="2"/>
@@ -7699,7 +7516,7 @@
       <x:c r="E174" s="2"/>
       <x:c r="F174" s="2"/>
       <x:c r="G174" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H174" s="2"/>
       <x:c r="I174" s="2"/>
@@ -7709,7 +7526,7 @@
     </x:row>
     <x:row r="175" ht="51.95000076293945" customHeight="1">
       <x:c r="A175" s="2" t="s">
-        <x:v>208</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B175" s="2"/>
       <x:c r="C175" s="2"/>
@@ -7717,7 +7534,7 @@
       <x:c r="E175" s="2"/>
       <x:c r="F175" s="2"/>
       <x:c r="G175" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H175" s="2"/>
       <x:c r="I175" s="2"/>
@@ -7727,7 +7544,7 @@
     </x:row>
     <x:row r="176" ht="51.95000076293945" customHeight="1">
       <x:c r="A176" s="2" t="s">
-        <x:v>209</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B176" s="2"/>
       <x:c r="C176" s="2"/>
@@ -7735,7 +7552,7 @@
       <x:c r="E176" s="2"/>
       <x:c r="F176" s="2"/>
       <x:c r="G176" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H176" s="2"/>
       <x:c r="I176" s="2"/>
@@ -7745,7 +7562,7 @@
     </x:row>
     <x:row r="177" ht="51.95000076293945" customHeight="1">
       <x:c r="A177" s="2" t="s">
-        <x:v>210</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B177" s="2"/>
       <x:c r="C177" s="2"/>
@@ -7753,7 +7570,7 @@
       <x:c r="E177" s="2"/>
       <x:c r="F177" s="2"/>
       <x:c r="G177" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H177" s="2"/>
       <x:c r="I177" s="2"/>
@@ -7763,7 +7580,7 @@
     </x:row>
     <x:row r="178" ht="51.95000076293945" customHeight="1">
       <x:c r="A178" s="2" t="s">
-        <x:v>211</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B178" s="2"/>
       <x:c r="C178" s="2"/>
@@ -7771,7 +7588,7 @@
       <x:c r="E178" s="2"/>
       <x:c r="F178" s="2"/>
       <x:c r="G178" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H178" s="2"/>
       <x:c r="I178" s="2"/>
@@ -7781,7 +7598,7 @@
     </x:row>
     <x:row r="179" ht="51.95000076293945" customHeight="1">
       <x:c r="A179" s="2" t="s">
-        <x:v>212</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B179" s="2"/>
       <x:c r="C179" s="2"/>
@@ -7789,7 +7606,7 @@
       <x:c r="E179" s="2"/>
       <x:c r="F179" s="2"/>
       <x:c r="G179" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H179" s="2"/>
       <x:c r="I179" s="2"/>
@@ -7799,7 +7616,7 @@
     </x:row>
     <x:row r="180" ht="51.95000076293945" customHeight="1">
       <x:c r="A180" s="2" t="s">
-        <x:v>213</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B180" s="2"/>
       <x:c r="C180" s="2"/>
@@ -7807,7 +7624,7 @@
       <x:c r="E180" s="2"/>
       <x:c r="F180" s="2"/>
       <x:c r="G180" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H180" s="2"/>
       <x:c r="I180" s="2"/>
@@ -7817,7 +7634,7 @@
     </x:row>
     <x:row r="181" ht="51.95000076293945" customHeight="1">
       <x:c r="A181" s="2" t="s">
-        <x:v>214</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B181" s="2"/>
       <x:c r="C181" s="2"/>
@@ -7825,7 +7642,7 @@
       <x:c r="E181" s="2"/>
       <x:c r="F181" s="2"/>
       <x:c r="G181" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H181" s="2"/>
       <x:c r="I181" s="2"/>
@@ -7835,7 +7652,7 @@
     </x:row>
     <x:row r="182" ht="51.95000076293945" customHeight="1">
       <x:c r="A182" s="2" t="s">
-        <x:v>215</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B182" s="2"/>
       <x:c r="C182" s="2"/>
@@ -7843,7 +7660,7 @@
       <x:c r="E182" s="2"/>
       <x:c r="F182" s="2"/>
       <x:c r="G182" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H182" s="2"/>
       <x:c r="I182" s="2"/>
@@ -7853,7 +7670,7 @@
     </x:row>
     <x:row r="183" ht="51.95000076293945" customHeight="1">
       <x:c r="A183" s="2" t="s">
-        <x:v>216</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B183" s="2"/>
       <x:c r="C183" s="2"/>
@@ -7861,7 +7678,7 @@
       <x:c r="E183" s="2"/>
       <x:c r="F183" s="2"/>
       <x:c r="G183" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H183" s="2"/>
       <x:c r="I183" s="2"/>
@@ -7871,7 +7688,7 @@
     </x:row>
     <x:row r="184" ht="51.95000076293945" customHeight="1">
       <x:c r="A184" s="2" t="s">
-        <x:v>217</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B184" s="2"/>
       <x:c r="C184" s="2"/>
@@ -7879,7 +7696,7 @@
       <x:c r="E184" s="2"/>
       <x:c r="F184" s="2"/>
       <x:c r="G184" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H184" s="2"/>
       <x:c r="I184" s="2"/>
@@ -7889,7 +7706,7 @@
     </x:row>
     <x:row r="185" ht="51.95000076293945" customHeight="1">
       <x:c r="A185" s="2" t="s">
-        <x:v>218</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="B185" s="2"/>
       <x:c r="C185" s="2"/>
@@ -7897,7 +7714,7 @@
       <x:c r="E185" s="2"/>
       <x:c r="F185" s="2"/>
       <x:c r="G185" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H185" s="2"/>
       <x:c r="I185" s="2"/>
@@ -7907,7 +7724,7 @@
     </x:row>
     <x:row r="186" ht="51.95000076293945" customHeight="1">
       <x:c r="A186" s="2" t="s">
-        <x:v>219</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B186" s="2"/>
       <x:c r="C186" s="2"/>
@@ -7915,7 +7732,7 @@
       <x:c r="E186" s="2"/>
       <x:c r="F186" s="2"/>
       <x:c r="G186" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H186" s="2"/>
       <x:c r="I186" s="2"/>
@@ -7925,7 +7742,7 @@
     </x:row>
     <x:row r="187" ht="51.95000076293945" customHeight="1">
       <x:c r="A187" s="2" t="s">
-        <x:v>220</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="B187" s="2"/>
       <x:c r="C187" s="2"/>
@@ -7933,7 +7750,7 @@
       <x:c r="E187" s="2"/>
       <x:c r="F187" s="2"/>
       <x:c r="G187" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H187" s="2"/>
       <x:c r="I187" s="2"/>
@@ -7943,7 +7760,7 @@
     </x:row>
     <x:row r="188" ht="51.95000076293945" customHeight="1">
       <x:c r="A188" s="2" t="s">
-        <x:v>221</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B188" s="2"/>
       <x:c r="C188" s="2"/>
@@ -7951,7 +7768,7 @@
       <x:c r="E188" s="2"/>
       <x:c r="F188" s="2"/>
       <x:c r="G188" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H188" s="2"/>
       <x:c r="I188" s="2"/>
@@ -7961,7 +7778,7 @@
     </x:row>
     <x:row r="189" ht="51.95000076293945" customHeight="1">
       <x:c r="A189" s="2" t="s">
-        <x:v>222</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B189" s="2"/>
       <x:c r="C189" s="2"/>
@@ -7969,7 +7786,7 @@
       <x:c r="E189" s="2"/>
       <x:c r="F189" s="2"/>
       <x:c r="G189" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H189" s="2"/>
       <x:c r="I189" s="2"/>
@@ -7979,7 +7796,7 @@
     </x:row>
     <x:row r="190" ht="51.95000076293945" customHeight="1">
       <x:c r="A190" s="2" t="s">
-        <x:v>223</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B190" s="2"/>
       <x:c r="C190" s="2"/>
@@ -7987,7 +7804,7 @@
       <x:c r="E190" s="2"/>
       <x:c r="F190" s="2"/>
       <x:c r="G190" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H190" s="2"/>
       <x:c r="I190" s="2"/>
@@ -7997,7 +7814,7 @@
     </x:row>
     <x:row r="191" ht="51.95000076293945" customHeight="1">
       <x:c r="A191" s="2" t="s">
-        <x:v>224</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="B191" s="2"/>
       <x:c r="C191" s="2"/>
@@ -8005,7 +7822,7 @@
       <x:c r="E191" s="2"/>
       <x:c r="F191" s="2"/>
       <x:c r="G191" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H191" s="2"/>
       <x:c r="I191" s="2"/>
@@ -8015,7 +7832,7 @@
     </x:row>
     <x:row r="192" ht="51.95000076293945" customHeight="1">
       <x:c r="A192" s="2" t="s">
-        <x:v>225</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="B192" s="2"/>
       <x:c r="C192" s="2"/>
@@ -8023,7 +7840,7 @@
       <x:c r="E192" s="2"/>
       <x:c r="F192" s="2"/>
       <x:c r="G192" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H192" s="2"/>
       <x:c r="I192" s="2"/>
@@ -8033,7 +7850,7 @@
     </x:row>
     <x:row r="193" ht="51.95000076293945" customHeight="1">
       <x:c r="A193" s="2" t="s">
-        <x:v>226</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B193" s="2"/>
       <x:c r="C193" s="2"/>
@@ -8041,7 +7858,7 @@
       <x:c r="E193" s="2"/>
       <x:c r="F193" s="2"/>
       <x:c r="G193" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H193" s="2"/>
       <x:c r="I193" s="2"/>
@@ -8051,7 +7868,7 @@
     </x:row>
     <x:row r="194" ht="51.95000076293945" customHeight="1">
       <x:c r="A194" s="2" t="s">
-        <x:v>227</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B194" s="2"/>
       <x:c r="C194" s="2"/>
@@ -8059,7 +7876,7 @@
       <x:c r="E194" s="2"/>
       <x:c r="F194" s="2"/>
       <x:c r="G194" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H194" s="2"/>
       <x:c r="I194" s="2"/>
@@ -8069,7 +7886,7 @@
     </x:row>
     <x:row r="195" ht="51.95000076293945" customHeight="1">
       <x:c r="A195" s="2" t="s">
-        <x:v>228</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B195" s="2"/>
       <x:c r="C195" s="2"/>
@@ -8077,7 +7894,7 @@
       <x:c r="E195" s="2"/>
       <x:c r="F195" s="2"/>
       <x:c r="G195" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H195" s="2"/>
       <x:c r="I195" s="2"/>
@@ -8087,7 +7904,7 @@
     </x:row>
     <x:row r="196" ht="51.95000076293945" customHeight="1">
       <x:c r="A196" s="2" t="s">
-        <x:v>229</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B196" s="2"/>
       <x:c r="C196" s="2"/>
@@ -8095,7 +7912,7 @@
       <x:c r="E196" s="2"/>
       <x:c r="F196" s="2"/>
       <x:c r="G196" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H196" s="2"/>
       <x:c r="I196" s="2"/>
@@ -8105,7 +7922,7 @@
     </x:row>
     <x:row r="197" ht="51.95000076293945" customHeight="1">
       <x:c r="A197" s="2" t="s">
-        <x:v>230</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B197" s="2"/>
       <x:c r="C197" s="2"/>
@@ -8113,7 +7930,7 @@
       <x:c r="E197" s="2"/>
       <x:c r="F197" s="2"/>
       <x:c r="G197" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H197" s="2"/>
       <x:c r="I197" s="2"/>
@@ -8123,7 +7940,7 @@
     </x:row>
     <x:row r="198" ht="51.95000076293945" customHeight="1">
       <x:c r="A198" s="2" t="s">
-        <x:v>231</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B198" s="2"/>
       <x:c r="C198" s="2"/>
@@ -8131,7 +7948,7 @@
       <x:c r="E198" s="2"/>
       <x:c r="F198" s="2"/>
       <x:c r="G198" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H198" s="2"/>
       <x:c r="I198" s="2"/>
@@ -8141,7 +7958,7 @@
     </x:row>
     <x:row r="199" ht="51.95000076293945" customHeight="1">
       <x:c r="A199" s="2" t="s">
-        <x:v>232</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B199" s="2"/>
       <x:c r="C199" s="2"/>
@@ -8149,7 +7966,7 @@
       <x:c r="E199" s="2"/>
       <x:c r="F199" s="2"/>
       <x:c r="G199" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H199" s="2"/>
       <x:c r="I199" s="2"/>
@@ -8159,7 +7976,7 @@
     </x:row>
     <x:row r="200" ht="51.95000076293945" customHeight="1">
       <x:c r="A200" s="2" t="s">
-        <x:v>233</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B200" s="2"/>
       <x:c r="C200" s="2"/>
@@ -8167,7 +7984,7 @@
       <x:c r="E200" s="2"/>
       <x:c r="F200" s="2"/>
       <x:c r="G200" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H200" s="2"/>
       <x:c r="I200" s="2"/>
@@ -8177,7 +7994,7 @@
     </x:row>
     <x:row r="201" ht="51.95000076293945" customHeight="1">
       <x:c r="A201" s="2" t="s">
-        <x:v>234</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="B201" s="2"/>
       <x:c r="C201" s="2"/>
@@ -8185,7 +8002,7 @@
       <x:c r="E201" s="2"/>
       <x:c r="F201" s="2"/>
       <x:c r="G201" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H201" s="2"/>
       <x:c r="I201" s="2"/>
@@ -8195,7 +8012,7 @@
     </x:row>
     <x:row r="202" ht="51.95000076293945" customHeight="1">
       <x:c r="A202" s="2" t="s">
-        <x:v>235</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B202" s="2"/>
       <x:c r="C202" s="2"/>
@@ -8203,7 +8020,7 @@
       <x:c r="E202" s="2"/>
       <x:c r="F202" s="2"/>
       <x:c r="G202" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H202" s="2"/>
       <x:c r="I202" s="2"/>
@@ -8213,7 +8030,7 @@
     </x:row>
     <x:row r="203" ht="51.95000076293945" customHeight="1">
       <x:c r="A203" s="2" t="s">
-        <x:v>236</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="B203" s="2"/>
       <x:c r="C203" s="2"/>
@@ -8221,7 +8038,7 @@
       <x:c r="E203" s="2"/>
       <x:c r="F203" s="2"/>
       <x:c r="G203" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H203" s="2"/>
       <x:c r="I203" s="2"/>
@@ -8257,7 +8074,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03794a68a9db4c9a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R984a9d77e40b4968"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8280,7 +8097,7 @@
   <x:sheetData>
     <x:row r="1" ht="18" customHeight="1">
       <x:c r="A1" s="7" t="s">
-        <x:v>237</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="B1" s="8"/>
       <x:c r="C1" s="8"/>
@@ -8294,39 +8111,39 @@
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
       <x:c r="A3" s="3" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="D3" s="3" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="E3" s="3" t="s">
         <x:v>238</x:v>
       </x:c>
-      <x:c r="C3" s="3" t="s">
+      <x:c r="F3" s="3" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="D3" s="3" t="s">
+      <x:c r="G3" s="3" t="s">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="E3" s="3" t="s">
+      <x:c r="H3" s="3" t="s">
         <x:v>241</x:v>
       </x:c>
-      <x:c r="F3" s="3" t="s">
+      <x:c r="I3" s="3" t="s">
         <x:v>242</x:v>
       </x:c>
-      <x:c r="G3" s="3" t="s">
+      <x:c r="J3" s="3" t="s">
         <x:v>243</x:v>
-      </x:c>
-      <x:c r="H3" s="3" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="I3" s="3" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="J3" s="3" t="s">
-        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="57.95000076293945" customHeight="1">
       <x:c r="A4" s="2" t="s">
-        <x:v>247</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B4" s="2"/>
       <x:c r="C4" s="2"/>
@@ -8340,7 +8157,7 @@
     </x:row>
     <x:row r="5" ht="57.95000076293945" customHeight="1">
       <x:c r="A5" s="2" t="s">
-        <x:v>248</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B5" s="2"/>
       <x:c r="C5" s="2"/>
@@ -8354,7 +8171,7 @@
     </x:row>
     <x:row r="6" ht="57.95000076293945" customHeight="1">
       <x:c r="A6" s="2" t="s">
-        <x:v>249</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B6" s="2"/>
       <x:c r="C6" s="2"/>
@@ -8368,7 +8185,7 @@
     </x:row>
     <x:row r="7" ht="57.95000076293945" customHeight="1">
       <x:c r="A7" s="2" t="s">
-        <x:v>250</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B7" s="2"/>
       <x:c r="C7" s="2"/>
@@ -8382,7 +8199,7 @@
     </x:row>
     <x:row r="8" ht="57.95000076293945" customHeight="1">
       <x:c r="A8" s="2" t="s">
-        <x:v>251</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B8" s="2"/>
       <x:c r="C8" s="2"/>
@@ -8396,7 +8213,7 @@
     </x:row>
     <x:row r="9" ht="57.95000076293945" customHeight="1">
       <x:c r="A9" s="2" t="s">
-        <x:v>252</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B9" s="2"/>
       <x:c r="C9" s="2"/>
@@ -8410,7 +8227,7 @@
     </x:row>
     <x:row r="10" ht="57.95000076293945" customHeight="1">
       <x:c r="A10" s="2" t="s">
-        <x:v>253</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="B10" s="2"/>
       <x:c r="C10" s="2"/>
@@ -8424,7 +8241,7 @@
     </x:row>
     <x:row r="11" ht="57.95000076293945" customHeight="1">
       <x:c r="A11" s="2" t="s">
-        <x:v>254</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="B11" s="2"/>
       <x:c r="C11" s="2"/>
@@ -8438,7 +8255,7 @@
     </x:row>
     <x:row r="12" ht="57.95000076293945" customHeight="1">
       <x:c r="A12" s="2" t="s">
-        <x:v>255</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B12" s="2"/>
       <x:c r="C12" s="2"/>
@@ -8452,7 +8269,7 @@
     </x:row>
     <x:row r="13" ht="57.95000076293945" customHeight="1">
       <x:c r="A13" s="2" t="s">
-        <x:v>256</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="B13" s="2"/>
       <x:c r="C13" s="2"/>
@@ -8466,7 +8283,7 @@
     </x:row>
     <x:row r="14" ht="57.95000076293945" customHeight="1">
       <x:c r="A14" s="2" t="s">
-        <x:v>257</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B14" s="2"/>
       <x:c r="C14" s="2"/>
@@ -8480,7 +8297,7 @@
     </x:row>
     <x:row r="15" ht="57.95000076293945" customHeight="1">
       <x:c r="A15" s="2" t="s">
-        <x:v>258</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B15" s="2"/>
       <x:c r="C15" s="2"/>
@@ -8494,7 +8311,7 @@
     </x:row>
     <x:row r="16" ht="57.95000076293945" customHeight="1">
       <x:c r="A16" s="2" t="s">
-        <x:v>259</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B16" s="2"/>
       <x:c r="C16" s="2"/>
@@ -8508,7 +8325,7 @@
     </x:row>
     <x:row r="17" ht="57.95000076293945" customHeight="1">
       <x:c r="A17" s="2" t="s">
-        <x:v>260</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="B17" s="2"/>
       <x:c r="C17" s="2"/>
@@ -8522,7 +8339,7 @@
     </x:row>
     <x:row r="18" ht="57.95000076293945" customHeight="1">
       <x:c r="A18" s="2" t="s">
-        <x:v>261</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B18" s="2"/>
       <x:c r="C18" s="2"/>
@@ -8536,7 +8353,7 @@
     </x:row>
     <x:row r="19" ht="57.95000076293945" customHeight="1">
       <x:c r="A19" s="2" t="s">
-        <x:v>262</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="B19" s="2"/>
       <x:c r="C19" s="2"/>
@@ -8550,7 +8367,7 @@
     </x:row>
     <x:row r="20" ht="57.95000076293945" customHeight="1">
       <x:c r="A20" s="2" t="s">
-        <x:v>263</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B20" s="2"/>
       <x:c r="C20" s="2"/>
@@ -8564,7 +8381,7 @@
     </x:row>
     <x:row r="21" ht="57.95000076293945" customHeight="1">
       <x:c r="A21" s="2" t="s">
-        <x:v>264</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B21" s="2"/>
       <x:c r="C21" s="2"/>
@@ -8578,7 +8395,7 @@
     </x:row>
     <x:row r="22" ht="57.95000076293945" customHeight="1">
       <x:c r="A22" s="2" t="s">
-        <x:v>265</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B22" s="2"/>
       <x:c r="C22" s="2"/>
@@ -8592,7 +8409,7 @@
     </x:row>
     <x:row r="23" ht="57.95000076293945" customHeight="1">
       <x:c r="A23" s="2" t="s">
-        <x:v>266</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="B23" s="2"/>
       <x:c r="C23" s="2"/>
@@ -8606,7 +8423,7 @@
     </x:row>
     <x:row r="24" ht="57.95000076293945" customHeight="1">
       <x:c r="A24" s="2" t="s">
-        <x:v>267</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="B24" s="2"/>
       <x:c r="C24" s="2"/>
@@ -8620,7 +8437,7 @@
     </x:row>
     <x:row r="25" ht="57.95000076293945" customHeight="1">
       <x:c r="A25" s="2" t="s">
-        <x:v>268</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="B25" s="2"/>
       <x:c r="C25" s="2"/>
@@ -8634,7 +8451,7 @@
     </x:row>
     <x:row r="26" ht="57.95000076293945" customHeight="1">
       <x:c r="A26" s="2" t="s">
-        <x:v>269</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="B26" s="2"/>
       <x:c r="C26" s="2"/>
@@ -8648,7 +8465,7 @@
     </x:row>
     <x:row r="27" ht="57.95000076293945" customHeight="1">
       <x:c r="A27" s="2" t="s">
-        <x:v>270</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B27" s="2"/>
       <x:c r="C27" s="2"/>
@@ -8662,7 +8479,7 @@
     </x:row>
     <x:row r="28" ht="57.95000076293945" customHeight="1">
       <x:c r="A28" s="2" t="s">
-        <x:v>271</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="B28" s="2"/>
       <x:c r="C28" s="2"/>
@@ -8676,7 +8493,7 @@
     </x:row>
     <x:row r="29" ht="57.95000076293945" customHeight="1">
       <x:c r="A29" s="2" t="s">
-        <x:v>272</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B29" s="2"/>
       <x:c r="C29" s="2"/>
@@ -8690,7 +8507,7 @@
     </x:row>
     <x:row r="30" ht="57.95000076293945" customHeight="1">
       <x:c r="A30" s="2" t="s">
-        <x:v>273</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="B30" s="2"/>
       <x:c r="C30" s="2"/>
@@ -8704,7 +8521,7 @@
     </x:row>
     <x:row r="31" ht="57.95000076293945" customHeight="1">
       <x:c r="A31" s="2" t="s">
-        <x:v>274</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="B31" s="2"/>
       <x:c r="C31" s="2"/>
@@ -8718,7 +8535,7 @@
     </x:row>
     <x:row r="32" ht="57.95000076293945" customHeight="1">
       <x:c r="A32" s="2" t="s">
-        <x:v>275</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="B32" s="2"/>
       <x:c r="C32" s="2"/>
@@ -8732,7 +8549,7 @@
     </x:row>
     <x:row r="33" ht="57.95000076293945" customHeight="1">
       <x:c r="A33" s="2" t="s">
-        <x:v>276</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="B33" s="2"/>
       <x:c r="C33" s="2"/>
@@ -8746,7 +8563,7 @@
     </x:row>
     <x:row r="34" ht="57.95000076293945" customHeight="1">
       <x:c r="A34" s="2" t="s">
-        <x:v>277</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="B34" s="2"/>
       <x:c r="C34" s="2"/>
@@ -8760,7 +8577,7 @@
     </x:row>
     <x:row r="35" ht="57.95000076293945" customHeight="1">
       <x:c r="A35" s="2" t="s">
-        <x:v>278</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B35" s="2"/>
       <x:c r="C35" s="2"/>
@@ -8774,7 +8591,7 @@
     </x:row>
     <x:row r="36" ht="57.95000076293945" customHeight="1">
       <x:c r="A36" s="2" t="s">
-        <x:v>279</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="B36" s="2"/>
       <x:c r="C36" s="2"/>
@@ -8788,7 +8605,7 @@
     </x:row>
     <x:row r="37" ht="57.95000076293945" customHeight="1">
       <x:c r="A37" s="2" t="s">
-        <x:v>280</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B37" s="2"/>
       <x:c r="C37" s="2"/>
@@ -8802,7 +8619,7 @@
     </x:row>
     <x:row r="38" ht="57.95000076293945" customHeight="1">
       <x:c r="A38" s="2" t="s">
-        <x:v>281</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B38" s="2"/>
       <x:c r="C38" s="2"/>
@@ -8816,7 +8633,7 @@
     </x:row>
     <x:row r="39" ht="57.95000076293945" customHeight="1">
       <x:c r="A39" s="2" t="s">
-        <x:v>282</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="B39" s="2"/>
       <x:c r="C39" s="2"/>
@@ -8830,7 +8647,7 @@
     </x:row>
     <x:row r="40" ht="57.95000076293945" customHeight="1">
       <x:c r="A40" s="2" t="s">
-        <x:v>283</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="B40" s="2"/>
       <x:c r="C40" s="2"/>
@@ -8844,7 +8661,7 @@
     </x:row>
     <x:row r="41" ht="57.95000076293945" customHeight="1">
       <x:c r="A41" s="2" t="s">
-        <x:v>284</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="B41" s="2"/>
       <x:c r="C41" s="2"/>
@@ -8858,7 +8675,7 @@
     </x:row>
     <x:row r="42" ht="57.95000076293945" customHeight="1">
       <x:c r="A42" s="2" t="s">
-        <x:v>285</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B42" s="2"/>
       <x:c r="C42" s="2"/>
@@ -8872,7 +8689,7 @@
     </x:row>
     <x:row r="43" ht="57.95000076293945" customHeight="1">
       <x:c r="A43" s="2" t="s">
-        <x:v>286</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="B43" s="2"/>
       <x:c r="C43" s="2"/>
@@ -8886,7 +8703,7 @@
     </x:row>
     <x:row r="44" ht="57.95000076293945" customHeight="1">
       <x:c r="A44" s="2" t="s">
-        <x:v>287</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="B44" s="2"/>
       <x:c r="C44" s="2"/>
@@ -8900,7 +8717,7 @@
     </x:row>
     <x:row r="45" ht="57.95000076293945" customHeight="1">
       <x:c r="A45" s="2" t="s">
-        <x:v>288</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B45" s="2"/>
       <x:c r="C45" s="2"/>
@@ -8914,7 +8731,7 @@
     </x:row>
     <x:row r="46" ht="57.95000076293945" customHeight="1">
       <x:c r="A46" s="2" t="s">
-        <x:v>289</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="B46" s="2"/>
       <x:c r="C46" s="2"/>
@@ -8928,7 +8745,7 @@
     </x:row>
     <x:row r="47" ht="57.95000076293945" customHeight="1">
       <x:c r="A47" s="2" t="s">
-        <x:v>290</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="B47" s="2"/>
       <x:c r="C47" s="2"/>
@@ -8942,7 +8759,7 @@
     </x:row>
     <x:row r="48" ht="57.95000076293945" customHeight="1">
       <x:c r="A48" s="2" t="s">
-        <x:v>291</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B48" s="2"/>
       <x:c r="C48" s="2"/>
@@ -8956,7 +8773,7 @@
     </x:row>
     <x:row r="49" ht="57.95000076293945" customHeight="1">
       <x:c r="A49" s="2" t="s">
-        <x:v>292</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="B49" s="2"/>
       <x:c r="C49" s="2"/>
@@ -8970,7 +8787,7 @@
     </x:row>
     <x:row r="50" ht="57.95000076293945" customHeight="1">
       <x:c r="A50" s="2" t="s">
-        <x:v>293</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="B50" s="2"/>
       <x:c r="C50" s="2"/>
@@ -8984,7 +8801,7 @@
     </x:row>
     <x:row r="51" ht="57.95000076293945" customHeight="1">
       <x:c r="A51" s="2" t="s">
-        <x:v>294</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="B51" s="2"/>
       <x:c r="C51" s="2"/>
@@ -8998,7 +8815,7 @@
     </x:row>
     <x:row r="52" ht="57.95000076293945" customHeight="1">
       <x:c r="A52" s="2" t="s">
-        <x:v>295</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B52" s="2"/>
       <x:c r="C52" s="2"/>
@@ -9012,7 +8829,7 @@
     </x:row>
     <x:row r="53" ht="57.95000076293945" customHeight="1">
       <x:c r="A53" s="2" t="s">
-        <x:v>296</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="B53" s="2"/>
       <x:c r="C53" s="2"/>
@@ -9026,7 +8843,7 @@
     </x:row>
     <x:row r="54" ht="57.95000076293945" customHeight="1">
       <x:c r="A54" s="2" t="s">
-        <x:v>297</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B54" s="2"/>
       <x:c r="C54" s="2"/>
@@ -9040,7 +8857,7 @@
     </x:row>
     <x:row r="55" ht="57.95000076293945" customHeight="1">
       <x:c r="A55" s="2" t="s">
-        <x:v>298</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="B55" s="2"/>
       <x:c r="C55" s="2"/>
@@ -9054,7 +8871,7 @@
     </x:row>
     <x:row r="56" ht="57.95000076293945" customHeight="1">
       <x:c r="A56" s="2" t="s">
-        <x:v>299</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="B56" s="2"/>
       <x:c r="C56" s="2"/>
@@ -9068,7 +8885,7 @@
     </x:row>
     <x:row r="57" ht="57.95000076293945" customHeight="1">
       <x:c r="A57" s="2" t="s">
-        <x:v>300</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="B57" s="2"/>
       <x:c r="C57" s="2"/>
@@ -9082,7 +8899,7 @@
     </x:row>
     <x:row r="58" ht="57.95000076293945" customHeight="1">
       <x:c r="A58" s="2" t="s">
-        <x:v>301</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="B58" s="2"/>
       <x:c r="C58" s="2"/>
@@ -9096,7 +8913,7 @@
     </x:row>
     <x:row r="59" ht="57.95000076293945" customHeight="1">
       <x:c r="A59" s="2" t="s">
-        <x:v>302</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="B59" s="2"/>
       <x:c r="C59" s="2"/>
@@ -9110,7 +8927,7 @@
     </x:row>
     <x:row r="60" ht="57.95000076293945" customHeight="1">
       <x:c r="A60" s="2" t="s">
-        <x:v>303</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="B60" s="2"/>
       <x:c r="C60" s="2"/>
@@ -9124,7 +8941,7 @@
     </x:row>
     <x:row r="61" ht="57.95000076293945" customHeight="1">
       <x:c r="A61" s="2" t="s">
-        <x:v>304</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="B61" s="2"/>
       <x:c r="C61" s="2"/>
@@ -9138,7 +8955,7 @@
     </x:row>
     <x:row r="62" ht="57.95000076293945" customHeight="1">
       <x:c r="A62" s="2" t="s">
-        <x:v>305</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="B62" s="2"/>
       <x:c r="C62" s="2"/>
@@ -9152,7 +8969,7 @@
     </x:row>
     <x:row r="63" ht="57.95000076293945" customHeight="1">
       <x:c r="A63" s="2" t="s">
-        <x:v>306</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="B63" s="2"/>
       <x:c r="C63" s="2"/>
@@ -9166,7 +8983,7 @@
     </x:row>
     <x:row r="64" ht="57.95000076293945" customHeight="1">
       <x:c r="A64" s="2" t="s">
-        <x:v>307</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="B64" s="2"/>
       <x:c r="C64" s="2"/>
@@ -9180,7 +8997,7 @@
     </x:row>
     <x:row r="65" ht="57.95000076293945" customHeight="1">
       <x:c r="A65" s="2" t="s">
-        <x:v>308</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="B65" s="2"/>
       <x:c r="C65" s="2"/>
@@ -9194,7 +9011,7 @@
     </x:row>
     <x:row r="66" ht="57.95000076293945" customHeight="1">
       <x:c r="A66" s="2" t="s">
-        <x:v>309</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="B66" s="2"/>
       <x:c r="C66" s="2"/>
@@ -9208,7 +9025,7 @@
     </x:row>
     <x:row r="67" ht="57.95000076293945" customHeight="1">
       <x:c r="A67" s="2" t="s">
-        <x:v>310</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="B67" s="2"/>
       <x:c r="C67" s="2"/>
@@ -9222,7 +9039,7 @@
     </x:row>
     <x:row r="68" ht="57.95000076293945" customHeight="1">
       <x:c r="A68" s="2" t="s">
-        <x:v>311</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="B68" s="2"/>
       <x:c r="C68" s="2"/>
@@ -9236,7 +9053,7 @@
     </x:row>
     <x:row r="69" ht="57.95000076293945" customHeight="1">
       <x:c r="A69" s="2" t="s">
-        <x:v>312</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="B69" s="2"/>
       <x:c r="C69" s="2"/>
@@ -9250,7 +9067,7 @@
     </x:row>
     <x:row r="70" ht="57.95000076293945" customHeight="1">
       <x:c r="A70" s="2" t="s">
-        <x:v>313</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="B70" s="2"/>
       <x:c r="C70" s="2"/>
@@ -9264,7 +9081,7 @@
     </x:row>
     <x:row r="71" ht="57.95000076293945" customHeight="1">
       <x:c r="A71" s="2" t="s">
-        <x:v>314</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="B71" s="2"/>
       <x:c r="C71" s="2"/>
@@ -9278,7 +9095,7 @@
     </x:row>
     <x:row r="72" ht="57.95000076293945" customHeight="1">
       <x:c r="A72" s="2" t="s">
-        <x:v>315</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="B72" s="2"/>
       <x:c r="C72" s="2"/>
@@ -9292,7 +9109,7 @@
     </x:row>
     <x:row r="73" ht="57.95000076293945" customHeight="1">
       <x:c r="A73" s="2" t="s">
-        <x:v>316</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="B73" s="2"/>
       <x:c r="C73" s="2"/>
@@ -9306,7 +9123,7 @@
     </x:row>
     <x:row r="74" ht="57.95000076293945" customHeight="1">
       <x:c r="A74" s="2" t="s">
-        <x:v>317</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="B74" s="2"/>
       <x:c r="C74" s="2"/>
@@ -9320,7 +9137,7 @@
     </x:row>
     <x:row r="75" ht="57.95000076293945" customHeight="1">
       <x:c r="A75" s="2" t="s">
-        <x:v>318</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="B75" s="2"/>
       <x:c r="C75" s="2"/>
@@ -9334,7 +9151,7 @@
     </x:row>
     <x:row r="76" ht="57.95000076293945" customHeight="1">
       <x:c r="A76" s="2" t="s">
-        <x:v>319</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B76" s="2"/>
       <x:c r="C76" s="2"/>
@@ -9348,7 +9165,7 @@
     </x:row>
     <x:row r="77" ht="57.95000076293945" customHeight="1">
       <x:c r="A77" s="2" t="s">
-        <x:v>320</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="B77" s="2"/>
       <x:c r="C77" s="2"/>
@@ -9362,7 +9179,7 @@
     </x:row>
     <x:row r="78" ht="57.95000076293945" customHeight="1">
       <x:c r="A78" s="2" t="s">
-        <x:v>321</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="B78" s="2"/>
       <x:c r="C78" s="2"/>
@@ -9376,7 +9193,7 @@
     </x:row>
     <x:row r="79" ht="57.95000076293945" customHeight="1">
       <x:c r="A79" s="2" t="s">
-        <x:v>322</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="B79" s="2"/>
       <x:c r="C79" s="2"/>
@@ -9390,7 +9207,7 @@
     </x:row>
     <x:row r="80" ht="57.95000076293945" customHeight="1">
       <x:c r="A80" s="2" t="s">
-        <x:v>323</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="B80" s="2"/>
       <x:c r="C80" s="2"/>
@@ -9404,7 +9221,7 @@
     </x:row>
     <x:row r="81" ht="57.95000076293945" customHeight="1">
       <x:c r="A81" s="2" t="s">
-        <x:v>324</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="B81" s="2"/>
       <x:c r="C81" s="2"/>
@@ -9418,7 +9235,7 @@
     </x:row>
     <x:row r="82" ht="57.95000076293945" customHeight="1">
       <x:c r="A82" s="2" t="s">
-        <x:v>325</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="B82" s="2"/>
       <x:c r="C82" s="2"/>
@@ -9432,7 +9249,7 @@
     </x:row>
     <x:row r="83" ht="57.95000076293945" customHeight="1">
       <x:c r="A83" s="2" t="s">
-        <x:v>326</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="B83" s="2"/>
       <x:c r="C83" s="2"/>
@@ -9446,7 +9263,7 @@
     </x:row>
     <x:row r="84" ht="57.95000076293945" customHeight="1">
       <x:c r="A84" s="2" t="s">
-        <x:v>327</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="B84" s="2"/>
       <x:c r="C84" s="2"/>
@@ -9460,7 +9277,7 @@
     </x:row>
     <x:row r="85" ht="57.95000076293945" customHeight="1">
       <x:c r="A85" s="2" t="s">
-        <x:v>328</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="B85" s="2"/>
       <x:c r="C85" s="2"/>
@@ -9474,7 +9291,7 @@
     </x:row>
     <x:row r="86" ht="57.95000076293945" customHeight="1">
       <x:c r="A86" s="2" t="s">
-        <x:v>329</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="B86" s="2"/>
       <x:c r="C86" s="2"/>
@@ -9488,7 +9305,7 @@
     </x:row>
     <x:row r="87" ht="57.95000076293945" customHeight="1">
       <x:c r="A87" s="2" t="s">
-        <x:v>330</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="B87" s="2"/>
       <x:c r="C87" s="2"/>
@@ -9502,7 +9319,7 @@
     </x:row>
     <x:row r="88" ht="57.95000076293945" customHeight="1">
       <x:c r="A88" s="2" t="s">
-        <x:v>331</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="B88" s="2"/>
       <x:c r="C88" s="2"/>
@@ -9516,7 +9333,7 @@
     </x:row>
     <x:row r="89" ht="57.95000076293945" customHeight="1">
       <x:c r="A89" s="2" t="s">
-        <x:v>332</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B89" s="2"/>
       <x:c r="C89" s="2"/>
@@ -9530,7 +9347,7 @@
     </x:row>
     <x:row r="90" ht="57.95000076293945" customHeight="1">
       <x:c r="A90" s="2" t="s">
-        <x:v>333</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="B90" s="2"/>
       <x:c r="C90" s="2"/>
@@ -9544,7 +9361,7 @@
     </x:row>
     <x:row r="91" ht="57.95000076293945" customHeight="1">
       <x:c r="A91" s="2" t="s">
-        <x:v>334</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="B91" s="2"/>
       <x:c r="C91" s="2"/>
@@ -9558,7 +9375,7 @@
     </x:row>
     <x:row r="92" ht="57.95000076293945" customHeight="1">
       <x:c r="A92" s="2" t="s">
-        <x:v>335</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="B92" s="2"/>
       <x:c r="C92" s="2"/>
@@ -9572,7 +9389,7 @@
     </x:row>
     <x:row r="93" ht="57.95000076293945" customHeight="1">
       <x:c r="A93" s="2" t="s">
-        <x:v>336</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="B93" s="2"/>
       <x:c r="C93" s="2"/>
@@ -9586,7 +9403,7 @@
     </x:row>
     <x:row r="94" ht="57.95000076293945" customHeight="1">
       <x:c r="A94" s="2" t="s">
-        <x:v>337</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="B94" s="2"/>
       <x:c r="C94" s="2"/>
@@ -9600,7 +9417,7 @@
     </x:row>
     <x:row r="95" ht="57.95000076293945" customHeight="1">
       <x:c r="A95" s="2" t="s">
-        <x:v>338</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B95" s="2"/>
       <x:c r="C95" s="2"/>
@@ -9614,7 +9431,7 @@
     </x:row>
     <x:row r="96" ht="57.95000076293945" customHeight="1">
       <x:c r="A96" s="2" t="s">
-        <x:v>339</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="B96" s="2"/>
       <x:c r="C96" s="2"/>
@@ -9628,7 +9445,7 @@
     </x:row>
     <x:row r="97" ht="57.95000076293945" customHeight="1">
       <x:c r="A97" s="2" t="s">
-        <x:v>340</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="B97" s="2"/>
       <x:c r="C97" s="2"/>
@@ -9642,7 +9459,7 @@
     </x:row>
     <x:row r="98" ht="57.95000076293945" customHeight="1">
       <x:c r="A98" s="2" t="s">
-        <x:v>341</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="B98" s="2"/>
       <x:c r="C98" s="2"/>
@@ -9656,7 +9473,7 @@
     </x:row>
     <x:row r="99" ht="57.95000076293945" customHeight="1">
       <x:c r="A99" s="2" t="s">
-        <x:v>342</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="B99" s="2"/>
       <x:c r="C99" s="2"/>
@@ -9670,7 +9487,7 @@
     </x:row>
     <x:row r="100" ht="57.95000076293945" customHeight="1">
       <x:c r="A100" s="2" t="s">
-        <x:v>343</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="B100" s="2"/>
       <x:c r="C100" s="2"/>
@@ -9684,7 +9501,7 @@
     </x:row>
     <x:row r="101" ht="57.95000076293945" customHeight="1">
       <x:c r="A101" s="2" t="s">
-        <x:v>344</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="B101" s="2"/>
       <x:c r="C101" s="2"/>
@@ -9698,7 +9515,7 @@
     </x:row>
     <x:row r="102" ht="57.95000076293945" customHeight="1">
       <x:c r="A102" s="2" t="s">
-        <x:v>345</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="B102" s="2"/>
       <x:c r="C102" s="2"/>
@@ -9712,7 +9529,7 @@
     </x:row>
     <x:row r="103" ht="57.95000076293945" customHeight="1">
       <x:c r="A103" s="2" t="s">
-        <x:v>346</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="B103" s="2"/>
       <x:c r="C103" s="2"/>
@@ -9748,7 +9565,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb081017c3004e4d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R638cc16f1f834bd6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9765,8 +9582,8 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="18" customHeight="1">
-      <x:c r="A1" s="7" t="s">
-        <x:v>347</x:v>
+      <x:c r="A1" s="7" t="str">
+        <x:v>UAT Sign-Off</x:v>
       </x:c>
       <x:c r="B1" s="8"/>
       <x:c r="C1" s="8"/>
@@ -9776,27 +9593,27 @@
     </x:row>
     <x:row r="3" ht="15" customHeight="1">
       <x:c r="A3" s="3" t="s">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="B3" s="3" t="s">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="D3" s="3" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="E3" s="3" t="s">
         <x:v>348</x:v>
       </x:c>
-      <x:c r="B3" s="3" t="s">
+      <x:c r="F3" s="3" t="s">
         <x:v>349</x:v>
       </x:c>
-      <x:c r="C3" s="3" t="s">
-        <x:v>350</x:v>
-      </x:c>
-      <x:c r="D3" s="3" t="s">
-        <x:v>351</x:v>
-      </x:c>
-      <x:c r="E3" s="3" t="s">
-        <x:v>352</x:v>
-      </x:c>
-      <x:c r="F3" s="3" t="s">
-        <x:v>353</x:v>
-      </x:c>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
-      <x:c r="A4" s="2" t="s">
-        <x:v>354</x:v>
+      <x:c r="A4" s="2" t="str">
+        <x:v>Business Owner</x:v>
       </x:c>
       <x:c r="B4" s="2"/>
       <x:c r="C4" s="2"/>
@@ -9805,8 +9622,8 @@
       <x:c r="F4" s="2"/>
     </x:row>
     <x:row r="5" ht="48" customHeight="1">
-      <x:c r="A5" s="2" t="s">
-        <x:v>355</x:v>
+      <x:c r="A5" s="2" t="str">
+        <x:v>Engineering Owner</x:v>
       </x:c>
       <x:c r="B5" s="2"/>
       <x:c r="C5" s="2"/>
@@ -9815,8 +9632,8 @@
       <x:c r="F5" s="2"/>
     </x:row>
     <x:row r="6" ht="48" customHeight="1">
-      <x:c r="A6" s="2" t="s">
-        <x:v>356</x:v>
+      <x:c r="A6" s="2" t="str">
+        <x:v>QA / UAT Coordinator</x:v>
       </x:c>
       <x:c r="B6" s="2"/>
       <x:c r="C6" s="2"/>
@@ -9825,8 +9642,8 @@
       <x:c r="F6" s="2"/>
     </x:row>
     <x:row r="7" ht="48" customHeight="1">
-      <x:c r="A7" s="2" t="s">
-        <x:v>357</x:v>
+      <x:c r="A7" s="2" t="str">
+        <x:v>Downstream Consumer</x:v>
       </x:c>
       <x:c r="B7" s="2"/>
       <x:c r="C7" s="2"/>
@@ -9835,98 +9652,92 @@
       <x:c r="F7" s="2"/>
     </x:row>
     <x:row r="8" ht="48" customHeight="1">
-      <x:c r="A8" s="2" t="s">
-        <x:v>358</x:v>
-      </x:c>
-      <x:c r="B8" s="2"/>
-      <x:c r="C8" s="2"/>
-      <x:c r="D8" s="6"/>
-      <x:c r="E8" s="2"/>
-      <x:c r="F8" s="2"/>
+      <x:c r="A8"/>
+      <x:c r="B8"/>
+      <x:c r="C8"/>
+      <x:c r="D8"/>
+      <x:c r="E8"/>
+      <x:c r="F8"/>
     </x:row>
     <x:row r="9" ht="48" customHeight="1">
-      <x:c r="A9" s="2" t="s">
-        <x:v>359</x:v>
-      </x:c>
-      <x:c r="B9" s="2"/>
-      <x:c r="C9" s="2"/>
-      <x:c r="D9" s="6"/>
-      <x:c r="E9" s="2"/>
-      <x:c r="F9" s="2"/>
+      <x:c r="A9"/>
+      <x:c r="B9"/>
+      <x:c r="C9"/>
+      <x:c r="D9"/>
+      <x:c r="E9"/>
+      <x:c r="F9"/>
     </x:row>
     <x:row r="10" ht="48" customHeight="1">
-      <x:c r="A10" s="2" t="s">
-        <x:v>360</x:v>
-      </x:c>
-      <x:c r="B10" s="2"/>
-      <x:c r="C10" s="2"/>
-      <x:c r="D10" s="6"/>
-      <x:c r="E10" s="2"/>
-      <x:c r="F10" s="2"/>
+      <x:c r="A10"/>
+      <x:c r="B10"/>
+      <x:c r="C10"/>
+      <x:c r="D10"/>
+      <x:c r="E10"/>
+      <x:c r="F10"/>
     </x:row>
     <x:row r="11" ht="48" customHeight="1">
-      <x:c r="A11" s="2"/>
-      <x:c r="B11" s="2"/>
-      <x:c r="C11" s="2"/>
-      <x:c r="D11" s="6"/>
-      <x:c r="E11" s="2"/>
-      <x:c r="F11" s="2"/>
+      <x:c r="A11"/>
+      <x:c r="B11"/>
+      <x:c r="C11"/>
+      <x:c r="D11"/>
+      <x:c r="E11"/>
+      <x:c r="F11"/>
     </x:row>
     <x:row r="12" ht="48" customHeight="1">
-      <x:c r="A12" s="2"/>
-      <x:c r="B12" s="2"/>
-      <x:c r="C12" s="2"/>
-      <x:c r="D12" s="6"/>
-      <x:c r="E12" s="2"/>
-      <x:c r="F12" s="2"/>
+      <x:c r="A12"/>
+      <x:c r="B12"/>
+      <x:c r="C12"/>
+      <x:c r="D12"/>
+      <x:c r="E12"/>
+      <x:c r="F12"/>
     </x:row>
     <x:row r="13" ht="48" customHeight="1">
-      <x:c r="A13" s="9"/>
-      <x:c r="B13" s="8"/>
-      <x:c r="C13" s="8"/>
-      <x:c r="D13" s="8"/>
-      <x:c r="E13" s="8"/>
-      <x:c r="F13" s="8"/>
+      <x:c r="A13"/>
+      <x:c r="B13"/>
+      <x:c r="C13"/>
+      <x:c r="D13"/>
+      <x:c r="E13"/>
+      <x:c r="F13"/>
     </x:row>
     <x:row r="14" ht="48" customHeight="1">
-      <x:c r="A14" s="9"/>
-      <x:c r="B14" s="8"/>
-      <x:c r="C14" s="8"/>
-      <x:c r="D14" s="8"/>
-      <x:c r="E14" s="8"/>
-      <x:c r="F14" s="8"/>
+      <x:c r="A14"/>
+      <x:c r="B14"/>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
+      <x:c r="E14"/>
+      <x:c r="F14"/>
     </x:row>
     <x:row r="15" ht="48" customHeight="1">
-      <x:c r="A15" s="8"/>
-      <x:c r="B15" s="8"/>
-      <x:c r="C15" s="8"/>
-      <x:c r="D15" s="8"/>
-      <x:c r="E15" s="8"/>
-      <x:c r="F15" s="8"/>
+      <x:c r="A15"/>
+      <x:c r="B15"/>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
+      <x:c r="E15"/>
+      <x:c r="F15"/>
     </x:row>
     <x:row r="16" ht="48" customHeight="1">
-      <x:c r="A16" s="8"/>
-      <x:c r="B16" s="8"/>
-      <x:c r="C16" s="8"/>
-      <x:c r="D16" s="8"/>
-      <x:c r="E16" s="8"/>
-      <x:c r="F16" s="8"/>
+      <x:c r="A16"/>
+      <x:c r="B16"/>
+      <x:c r="C16"/>
+      <x:c r="D16"/>
+      <x:c r="E16"/>
+      <x:c r="F16"/>
     </x:row>
     <x:row r="17" ht="48" customHeight="1">
-      <x:c r="A17" s="8"/>
-      <x:c r="B17" s="8"/>
-      <x:c r="C17" s="8"/>
-      <x:c r="D17" s="8"/>
-      <x:c r="E17" s="8"/>
-      <x:c r="F17" s="8"/>
+      <x:c r="A17"/>
+      <x:c r="B17"/>
+      <x:c r="C17"/>
+      <x:c r="D17"/>
+      <x:c r="E17"/>
+      <x:c r="F17"/>
     </x:row>
     <x:row r="18" ht="48" customHeight="1">
-      <x:c r="A18" s="8"/>
-      <x:c r="B18" s="8"/>
-      <x:c r="C18" s="8"/>
-      <x:c r="D18" s="8"/>
-      <x:c r="E18" s="8"/>
-      <x:c r="F18" s="8"/>
+      <x:c r="A18"/>
+      <x:c r="B18"/>
+      <x:c r="C18"/>
+      <x:c r="D18"/>
+      <x:c r="E18"/>
+      <x:c r="F18"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -9944,7 +9755,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb42d033168564858"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R667f92f44dda4393"/>
   </x:tableParts>
 </x:worksheet>
 </file>